--- a/planning/youtube_kikaku_pipeline.xlsx
+++ b/planning/youtube_kikaku_pipeline.xlsx
@@ -10,7 +10,7 @@
     <sheet name="STEP1検証（ゆうこさん調べ）" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'①企画一覧・審査'!$A$5:$W$205</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'①企画一覧・審査'!$A$5:$W$105</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -1126,7 +1126,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W205"/>
+  <dimension ref="A1:W105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" style="35" min="1" max="1"/>
@@ -6263,3708 +6263,8 @@
         <v/>
       </c>
     </row>
-    <row r="106" ht="18" customHeight="1" s="35">
-      <c r="A106" s="84">
-        <f>IF(C106="","",ROW()-5)</f>
-        <v/>
-      </c>
-      <c r="B106" s="85" t="n"/>
-      <c r="C106" s="86" t="n"/>
-      <c r="D106" s="86" t="n"/>
-      <c r="E106" s="85" t="n"/>
-      <c r="F106" s="86" t="n"/>
-      <c r="G106" s="86" t="n"/>
-      <c r="H106" s="86" t="n"/>
-      <c r="I106" s="86" t="n"/>
-      <c r="J106" s="85" t="n"/>
-      <c r="K106" s="85" t="n"/>
-      <c r="L106" s="85" t="n"/>
-      <c r="M106" s="85" t="n"/>
-      <c r="N106" s="85" t="n"/>
-      <c r="O106" s="85" t="n"/>
-      <c r="P106" s="84">
-        <f>IF(C106="","",IF(OR(E106="",E106="未検証"),"① STEP1待ち",IF(E106="不通過","✕ STEP1不通過",IF(OR(G106="",H106=""),"② STEP2-3 未記入",IF(COUNTIF(J106:O106,"×")&gt;0,"✕ ボツ候補",IF(COUNTA(J106:O106)&lt;6,"③ STEP4 審査待ち",IF(COUNTIF(J106:O106,"△")&gt;0,"△ 修正して再審査","◎ 候補リスト")))))))</f>
-        <v/>
-      </c>
-      <c r="Q106" s="85" t="n"/>
-      <c r="R106" s="85" t="n"/>
-      <c r="S106" s="85" t="n"/>
-      <c r="T106" s="84">
-        <f>IF(COUNT(Q106:S106)&lt;3,"",Q106+(11-R106)+S106)</f>
-        <v/>
-      </c>
-      <c r="U106" s="85" t="n"/>
-      <c r="V106" s="86" t="n"/>
-      <c r="W106" s="87">
-        <f>IF(AND(P106="◎ 候補リスト",U106&lt;&gt;"ボツ",U106&lt;&gt;"制作済み",T106&lt;&gt;"",OR('②候補ランキング'!$C$5="すべて",B106='②候補ランキング'!$C$5)),IF('②候補ランキング'!$C$4="ワクワク",Q106,IF('②候補ランキング'!$C$4="手軽さ",11-R106,IF('②候補ランキング'!$C$4="確信度",S106,T106)))*1000+T106+(1000-A106)/10000,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="107" ht="18" customHeight="1" s="35">
-      <c r="A107" s="84">
-        <f>IF(C107="","",ROW()-5)</f>
-        <v/>
-      </c>
-      <c r="B107" s="85" t="n"/>
-      <c r="C107" s="86" t="n"/>
-      <c r="D107" s="86" t="n"/>
-      <c r="E107" s="85" t="n"/>
-      <c r="F107" s="86" t="n"/>
-      <c r="G107" s="86" t="n"/>
-      <c r="H107" s="86" t="n"/>
-      <c r="I107" s="86" t="n"/>
-      <c r="J107" s="85" t="n"/>
-      <c r="K107" s="85" t="n"/>
-      <c r="L107" s="85" t="n"/>
-      <c r="M107" s="85" t="n"/>
-      <c r="N107" s="85" t="n"/>
-      <c r="O107" s="85" t="n"/>
-      <c r="P107" s="84">
-        <f>IF(C107="","",IF(OR(E107="",E107="未検証"),"① STEP1待ち",IF(E107="不通過","✕ STEP1不通過",IF(OR(G107="",H107=""),"② STEP2-3 未記入",IF(COUNTIF(J107:O107,"×")&gt;0,"✕ ボツ候補",IF(COUNTA(J107:O107)&lt;6,"③ STEP4 審査待ち",IF(COUNTIF(J107:O107,"△")&gt;0,"△ 修正して再審査","◎ 候補リスト")))))))</f>
-        <v/>
-      </c>
-      <c r="Q107" s="85" t="n"/>
-      <c r="R107" s="85" t="n"/>
-      <c r="S107" s="85" t="n"/>
-      <c r="T107" s="84">
-        <f>IF(COUNT(Q107:S107)&lt;3,"",Q107+(11-R107)+S107)</f>
-        <v/>
-      </c>
-      <c r="U107" s="85" t="n"/>
-      <c r="V107" s="86" t="n"/>
-      <c r="W107" s="87">
-        <f>IF(AND(P107="◎ 候補リスト",U107&lt;&gt;"ボツ",U107&lt;&gt;"制作済み",T107&lt;&gt;"",OR('②候補ランキング'!$C$5="すべて",B107='②候補ランキング'!$C$5)),IF('②候補ランキング'!$C$4="ワクワク",Q107,IF('②候補ランキング'!$C$4="手軽さ",11-R107,IF('②候補ランキング'!$C$4="確信度",S107,T107)))*1000+T107+(1000-A107)/10000,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="108" ht="18" customHeight="1" s="35">
-      <c r="A108" s="84">
-        <f>IF(C108="","",ROW()-5)</f>
-        <v/>
-      </c>
-      <c r="B108" s="85" t="n"/>
-      <c r="C108" s="86" t="n"/>
-      <c r="D108" s="86" t="n"/>
-      <c r="E108" s="85" t="n"/>
-      <c r="F108" s="86" t="n"/>
-      <c r="G108" s="86" t="n"/>
-      <c r="H108" s="86" t="n"/>
-      <c r="I108" s="86" t="n"/>
-      <c r="J108" s="85" t="n"/>
-      <c r="K108" s="85" t="n"/>
-      <c r="L108" s="85" t="n"/>
-      <c r="M108" s="85" t="n"/>
-      <c r="N108" s="85" t="n"/>
-      <c r="O108" s="85" t="n"/>
-      <c r="P108" s="84">
-        <f>IF(C108="","",IF(OR(E108="",E108="未検証"),"① STEP1待ち",IF(E108="不通過","✕ STEP1不通過",IF(OR(G108="",H108=""),"② STEP2-3 未記入",IF(COUNTIF(J108:O108,"×")&gt;0,"✕ ボツ候補",IF(COUNTA(J108:O108)&lt;6,"③ STEP4 審査待ち",IF(COUNTIF(J108:O108,"△")&gt;0,"△ 修正して再審査","◎ 候補リスト")))))))</f>
-        <v/>
-      </c>
-      <c r="Q108" s="85" t="n"/>
-      <c r="R108" s="85" t="n"/>
-      <c r="S108" s="85" t="n"/>
-      <c r="T108" s="84">
-        <f>IF(COUNT(Q108:S108)&lt;3,"",Q108+(11-R108)+S108)</f>
-        <v/>
-      </c>
-      <c r="U108" s="85" t="n"/>
-      <c r="V108" s="86" t="n"/>
-      <c r="W108" s="87">
-        <f>IF(AND(P108="◎ 候補リスト",U108&lt;&gt;"ボツ",U108&lt;&gt;"制作済み",T108&lt;&gt;"",OR('②候補ランキング'!$C$5="すべて",B108='②候補ランキング'!$C$5)),IF('②候補ランキング'!$C$4="ワクワク",Q108,IF('②候補ランキング'!$C$4="手軽さ",11-R108,IF('②候補ランキング'!$C$4="確信度",S108,T108)))*1000+T108+(1000-A108)/10000,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="109" ht="18" customHeight="1" s="35">
-      <c r="A109" s="84">
-        <f>IF(C109="","",ROW()-5)</f>
-        <v/>
-      </c>
-      <c r="B109" s="85" t="n"/>
-      <c r="C109" s="86" t="n"/>
-      <c r="D109" s="86" t="n"/>
-      <c r="E109" s="85" t="n"/>
-      <c r="F109" s="86" t="n"/>
-      <c r="G109" s="86" t="n"/>
-      <c r="H109" s="86" t="n"/>
-      <c r="I109" s="86" t="n"/>
-      <c r="J109" s="85" t="n"/>
-      <c r="K109" s="85" t="n"/>
-      <c r="L109" s="85" t="n"/>
-      <c r="M109" s="85" t="n"/>
-      <c r="N109" s="85" t="n"/>
-      <c r="O109" s="85" t="n"/>
-      <c r="P109" s="84">
-        <f>IF(C109="","",IF(OR(E109="",E109="未検証"),"① STEP1待ち",IF(E109="不通過","✕ STEP1不通過",IF(OR(G109="",H109=""),"② STEP2-3 未記入",IF(COUNTIF(J109:O109,"×")&gt;0,"✕ ボツ候補",IF(COUNTA(J109:O109)&lt;6,"③ STEP4 審査待ち",IF(COUNTIF(J109:O109,"△")&gt;0,"△ 修正して再審査","◎ 候補リスト")))))))</f>
-        <v/>
-      </c>
-      <c r="Q109" s="85" t="n"/>
-      <c r="R109" s="85" t="n"/>
-      <c r="S109" s="85" t="n"/>
-      <c r="T109" s="84">
-        <f>IF(COUNT(Q109:S109)&lt;3,"",Q109+(11-R109)+S109)</f>
-        <v/>
-      </c>
-      <c r="U109" s="85" t="n"/>
-      <c r="V109" s="86" t="n"/>
-      <c r="W109" s="87">
-        <f>IF(AND(P109="◎ 候補リスト",U109&lt;&gt;"ボツ",U109&lt;&gt;"制作済み",T109&lt;&gt;"",OR('②候補ランキング'!$C$5="すべて",B109='②候補ランキング'!$C$5)),IF('②候補ランキング'!$C$4="ワクワク",Q109,IF('②候補ランキング'!$C$4="手軽さ",11-R109,IF('②候補ランキング'!$C$4="確信度",S109,T109)))*1000+T109+(1000-A109)/10000,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="110" ht="18" customHeight="1" s="35">
-      <c r="A110" s="84">
-        <f>IF(C110="","",ROW()-5)</f>
-        <v/>
-      </c>
-      <c r="B110" s="85" t="n"/>
-      <c r="C110" s="86" t="n"/>
-      <c r="D110" s="86" t="n"/>
-      <c r="E110" s="85" t="n"/>
-      <c r="F110" s="86" t="n"/>
-      <c r="G110" s="86" t="n"/>
-      <c r="H110" s="86" t="n"/>
-      <c r="I110" s="86" t="n"/>
-      <c r="J110" s="85" t="n"/>
-      <c r="K110" s="85" t="n"/>
-      <c r="L110" s="85" t="n"/>
-      <c r="M110" s="85" t="n"/>
-      <c r="N110" s="85" t="n"/>
-      <c r="O110" s="85" t="n"/>
-      <c r="P110" s="84">
-        <f>IF(C110="","",IF(OR(E110="",E110="未検証"),"① STEP1待ち",IF(E110="不通過","✕ STEP1不通過",IF(OR(G110="",H110=""),"② STEP2-3 未記入",IF(COUNTIF(J110:O110,"×")&gt;0,"✕ ボツ候補",IF(COUNTA(J110:O110)&lt;6,"③ STEP4 審査待ち",IF(COUNTIF(J110:O110,"△")&gt;0,"△ 修正して再審査","◎ 候補リスト")))))))</f>
-        <v/>
-      </c>
-      <c r="Q110" s="85" t="n"/>
-      <c r="R110" s="85" t="n"/>
-      <c r="S110" s="85" t="n"/>
-      <c r="T110" s="84">
-        <f>IF(COUNT(Q110:S110)&lt;3,"",Q110+(11-R110)+S110)</f>
-        <v/>
-      </c>
-      <c r="U110" s="85" t="n"/>
-      <c r="V110" s="86" t="n"/>
-      <c r="W110" s="87">
-        <f>IF(AND(P110="◎ 候補リスト",U110&lt;&gt;"ボツ",U110&lt;&gt;"制作済み",T110&lt;&gt;"",OR('②候補ランキング'!$C$5="すべて",B110='②候補ランキング'!$C$5)),IF('②候補ランキング'!$C$4="ワクワク",Q110,IF('②候補ランキング'!$C$4="手軽さ",11-R110,IF('②候補ランキング'!$C$4="確信度",S110,T110)))*1000+T110+(1000-A110)/10000,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="111" ht="18" customHeight="1" s="35">
-      <c r="A111" s="84">
-        <f>IF(C111="","",ROW()-5)</f>
-        <v/>
-      </c>
-      <c r="B111" s="85" t="n"/>
-      <c r="C111" s="86" t="n"/>
-      <c r="D111" s="86" t="n"/>
-      <c r="E111" s="85" t="n"/>
-      <c r="F111" s="86" t="n"/>
-      <c r="G111" s="86" t="n"/>
-      <c r="H111" s="86" t="n"/>
-      <c r="I111" s="86" t="n"/>
-      <c r="J111" s="85" t="n"/>
-      <c r="K111" s="85" t="n"/>
-      <c r="L111" s="85" t="n"/>
-      <c r="M111" s="85" t="n"/>
-      <c r="N111" s="85" t="n"/>
-      <c r="O111" s="85" t="n"/>
-      <c r="P111" s="84">
-        <f>IF(C111="","",IF(OR(E111="",E111="未検証"),"① STEP1待ち",IF(E111="不通過","✕ STEP1不通過",IF(OR(G111="",H111=""),"② STEP2-3 未記入",IF(COUNTIF(J111:O111,"×")&gt;0,"✕ ボツ候補",IF(COUNTA(J111:O111)&lt;6,"③ STEP4 審査待ち",IF(COUNTIF(J111:O111,"△")&gt;0,"△ 修正して再審査","◎ 候補リスト")))))))</f>
-        <v/>
-      </c>
-      <c r="Q111" s="85" t="n"/>
-      <c r="R111" s="85" t="n"/>
-      <c r="S111" s="85" t="n"/>
-      <c r="T111" s="84">
-        <f>IF(COUNT(Q111:S111)&lt;3,"",Q111+(11-R111)+S111)</f>
-        <v/>
-      </c>
-      <c r="U111" s="85" t="n"/>
-      <c r="V111" s="86" t="n"/>
-      <c r="W111" s="87">
-        <f>IF(AND(P111="◎ 候補リスト",U111&lt;&gt;"ボツ",U111&lt;&gt;"制作済み",T111&lt;&gt;"",OR('②候補ランキング'!$C$5="すべて",B111='②候補ランキング'!$C$5)),IF('②候補ランキング'!$C$4="ワクワク",Q111,IF('②候補ランキング'!$C$4="手軽さ",11-R111,IF('②候補ランキング'!$C$4="確信度",S111,T111)))*1000+T111+(1000-A111)/10000,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="112" ht="18" customHeight="1" s="35">
-      <c r="A112" s="84">
-        <f>IF(C112="","",ROW()-5)</f>
-        <v/>
-      </c>
-      <c r="B112" s="85" t="n"/>
-      <c r="C112" s="86" t="n"/>
-      <c r="D112" s="86" t="n"/>
-      <c r="E112" s="85" t="n"/>
-      <c r="F112" s="86" t="n"/>
-      <c r="G112" s="86" t="n"/>
-      <c r="H112" s="86" t="n"/>
-      <c r="I112" s="86" t="n"/>
-      <c r="J112" s="85" t="n"/>
-      <c r="K112" s="85" t="n"/>
-      <c r="L112" s="85" t="n"/>
-      <c r="M112" s="85" t="n"/>
-      <c r="N112" s="85" t="n"/>
-      <c r="O112" s="85" t="n"/>
-      <c r="P112" s="84">
-        <f>IF(C112="","",IF(OR(E112="",E112="未検証"),"① STEP1待ち",IF(E112="不通過","✕ STEP1不通過",IF(OR(G112="",H112=""),"② STEP2-3 未記入",IF(COUNTIF(J112:O112,"×")&gt;0,"✕ ボツ候補",IF(COUNTA(J112:O112)&lt;6,"③ STEP4 審査待ち",IF(COUNTIF(J112:O112,"△")&gt;0,"△ 修正して再審査","◎ 候補リスト")))))))</f>
-        <v/>
-      </c>
-      <c r="Q112" s="85" t="n"/>
-      <c r="R112" s="85" t="n"/>
-      <c r="S112" s="85" t="n"/>
-      <c r="T112" s="84">
-        <f>IF(COUNT(Q112:S112)&lt;3,"",Q112+(11-R112)+S112)</f>
-        <v/>
-      </c>
-      <c r="U112" s="85" t="n"/>
-      <c r="V112" s="86" t="n"/>
-      <c r="W112" s="87">
-        <f>IF(AND(P112="◎ 候補リスト",U112&lt;&gt;"ボツ",U112&lt;&gt;"制作済み",T112&lt;&gt;"",OR('②候補ランキング'!$C$5="すべて",B112='②候補ランキング'!$C$5)),IF('②候補ランキング'!$C$4="ワクワク",Q112,IF('②候補ランキング'!$C$4="手軽さ",11-R112,IF('②候補ランキング'!$C$4="確信度",S112,T112)))*1000+T112+(1000-A112)/10000,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="113" ht="18" customHeight="1" s="35">
-      <c r="A113" s="84">
-        <f>IF(C113="","",ROW()-5)</f>
-        <v/>
-      </c>
-      <c r="B113" s="85" t="n"/>
-      <c r="C113" s="86" t="n"/>
-      <c r="D113" s="86" t="n"/>
-      <c r="E113" s="85" t="n"/>
-      <c r="F113" s="86" t="n"/>
-      <c r="G113" s="86" t="n"/>
-      <c r="H113" s="86" t="n"/>
-      <c r="I113" s="86" t="n"/>
-      <c r="J113" s="85" t="n"/>
-      <c r="K113" s="85" t="n"/>
-      <c r="L113" s="85" t="n"/>
-      <c r="M113" s="85" t="n"/>
-      <c r="N113" s="85" t="n"/>
-      <c r="O113" s="85" t="n"/>
-      <c r="P113" s="84">
-        <f>IF(C113="","",IF(OR(E113="",E113="未検証"),"① STEP1待ち",IF(E113="不通過","✕ STEP1不通過",IF(OR(G113="",H113=""),"② STEP2-3 未記入",IF(COUNTIF(J113:O113,"×")&gt;0,"✕ ボツ候補",IF(COUNTA(J113:O113)&lt;6,"③ STEP4 審査待ち",IF(COUNTIF(J113:O113,"△")&gt;0,"△ 修正して再審査","◎ 候補リスト")))))))</f>
-        <v/>
-      </c>
-      <c r="Q113" s="85" t="n"/>
-      <c r="R113" s="85" t="n"/>
-      <c r="S113" s="85" t="n"/>
-      <c r="T113" s="84">
-        <f>IF(COUNT(Q113:S113)&lt;3,"",Q113+(11-R113)+S113)</f>
-        <v/>
-      </c>
-      <c r="U113" s="85" t="n"/>
-      <c r="V113" s="86" t="n"/>
-      <c r="W113" s="87">
-        <f>IF(AND(P113="◎ 候補リスト",U113&lt;&gt;"ボツ",U113&lt;&gt;"制作済み",T113&lt;&gt;"",OR('②候補ランキング'!$C$5="すべて",B113='②候補ランキング'!$C$5)),IF('②候補ランキング'!$C$4="ワクワク",Q113,IF('②候補ランキング'!$C$4="手軽さ",11-R113,IF('②候補ランキング'!$C$4="確信度",S113,T113)))*1000+T113+(1000-A113)/10000,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="114" ht="18" customHeight="1" s="35">
-      <c r="A114" s="84">
-        <f>IF(C114="","",ROW()-5)</f>
-        <v/>
-      </c>
-      <c r="B114" s="85" t="n"/>
-      <c r="C114" s="86" t="n"/>
-      <c r="D114" s="86" t="n"/>
-      <c r="E114" s="85" t="n"/>
-      <c r="F114" s="86" t="n"/>
-      <c r="G114" s="86" t="n"/>
-      <c r="H114" s="86" t="n"/>
-      <c r="I114" s="86" t="n"/>
-      <c r="J114" s="85" t="n"/>
-      <c r="K114" s="85" t="n"/>
-      <c r="L114" s="85" t="n"/>
-      <c r="M114" s="85" t="n"/>
-      <c r="N114" s="85" t="n"/>
-      <c r="O114" s="85" t="n"/>
-      <c r="P114" s="84">
-        <f>IF(C114="","",IF(OR(E114="",E114="未検証"),"① STEP1待ち",IF(E114="不通過","✕ STEP1不通過",IF(OR(G114="",H114=""),"② STEP2-3 未記入",IF(COUNTIF(J114:O114,"×")&gt;0,"✕ ボツ候補",IF(COUNTA(J114:O114)&lt;6,"③ STEP4 審査待ち",IF(COUNTIF(J114:O114,"△")&gt;0,"△ 修正して再審査","◎ 候補リスト")))))))</f>
-        <v/>
-      </c>
-      <c r="Q114" s="85" t="n"/>
-      <c r="R114" s="85" t="n"/>
-      <c r="S114" s="85" t="n"/>
-      <c r="T114" s="84">
-        <f>IF(COUNT(Q114:S114)&lt;3,"",Q114+(11-R114)+S114)</f>
-        <v/>
-      </c>
-      <c r="U114" s="85" t="n"/>
-      <c r="V114" s="86" t="n"/>
-      <c r="W114" s="87">
-        <f>IF(AND(P114="◎ 候補リスト",U114&lt;&gt;"ボツ",U114&lt;&gt;"制作済み",T114&lt;&gt;"",OR('②候補ランキング'!$C$5="すべて",B114='②候補ランキング'!$C$5)),IF('②候補ランキング'!$C$4="ワクワク",Q114,IF('②候補ランキング'!$C$4="手軽さ",11-R114,IF('②候補ランキング'!$C$4="確信度",S114,T114)))*1000+T114+(1000-A114)/10000,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="115" ht="18" customHeight="1" s="35">
-      <c r="A115" s="84">
-        <f>IF(C115="","",ROW()-5)</f>
-        <v/>
-      </c>
-      <c r="B115" s="85" t="n"/>
-      <c r="C115" s="86" t="n"/>
-      <c r="D115" s="86" t="n"/>
-      <c r="E115" s="85" t="n"/>
-      <c r="F115" s="86" t="n"/>
-      <c r="G115" s="86" t="n"/>
-      <c r="H115" s="86" t="n"/>
-      <c r="I115" s="86" t="n"/>
-      <c r="J115" s="85" t="n"/>
-      <c r="K115" s="85" t="n"/>
-      <c r="L115" s="85" t="n"/>
-      <c r="M115" s="85" t="n"/>
-      <c r="N115" s="85" t="n"/>
-      <c r="O115" s="85" t="n"/>
-      <c r="P115" s="84">
-        <f>IF(C115="","",IF(OR(E115="",E115="未検証"),"① STEP1待ち",IF(E115="不通過","✕ STEP1不通過",IF(OR(G115="",H115=""),"② STEP2-3 未記入",IF(COUNTIF(J115:O115,"×")&gt;0,"✕ ボツ候補",IF(COUNTA(J115:O115)&lt;6,"③ STEP4 審査待ち",IF(COUNTIF(J115:O115,"△")&gt;0,"△ 修正して再審査","◎ 候補リスト")))))))</f>
-        <v/>
-      </c>
-      <c r="Q115" s="85" t="n"/>
-      <c r="R115" s="85" t="n"/>
-      <c r="S115" s="85" t="n"/>
-      <c r="T115" s="84">
-        <f>IF(COUNT(Q115:S115)&lt;3,"",Q115+(11-R115)+S115)</f>
-        <v/>
-      </c>
-      <c r="U115" s="85" t="n"/>
-      <c r="V115" s="86" t="n"/>
-      <c r="W115" s="87">
-        <f>IF(AND(P115="◎ 候補リスト",U115&lt;&gt;"ボツ",U115&lt;&gt;"制作済み",T115&lt;&gt;"",OR('②候補ランキング'!$C$5="すべて",B115='②候補ランキング'!$C$5)),IF('②候補ランキング'!$C$4="ワクワク",Q115,IF('②候補ランキング'!$C$4="手軽さ",11-R115,IF('②候補ランキング'!$C$4="確信度",S115,T115)))*1000+T115+(1000-A115)/10000,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="116" ht="18" customHeight="1" s="35">
-      <c r="A116" s="84">
-        <f>IF(C116="","",ROW()-5)</f>
-        <v/>
-      </c>
-      <c r="B116" s="85" t="n"/>
-      <c r="C116" s="86" t="n"/>
-      <c r="D116" s="86" t="n"/>
-      <c r="E116" s="85" t="n"/>
-      <c r="F116" s="86" t="n"/>
-      <c r="G116" s="86" t="n"/>
-      <c r="H116" s="86" t="n"/>
-      <c r="I116" s="86" t="n"/>
-      <c r="J116" s="85" t="n"/>
-      <c r="K116" s="85" t="n"/>
-      <c r="L116" s="85" t="n"/>
-      <c r="M116" s="85" t="n"/>
-      <c r="N116" s="85" t="n"/>
-      <c r="O116" s="85" t="n"/>
-      <c r="P116" s="84">
-        <f>IF(C116="","",IF(OR(E116="",E116="未検証"),"① STEP1待ち",IF(E116="不通過","✕ STEP1不通過",IF(OR(G116="",H116=""),"② STEP2-3 未記入",IF(COUNTIF(J116:O116,"×")&gt;0,"✕ ボツ候補",IF(COUNTA(J116:O116)&lt;6,"③ STEP4 審査待ち",IF(COUNTIF(J116:O116,"△")&gt;0,"△ 修正して再審査","◎ 候補リスト")))))))</f>
-        <v/>
-      </c>
-      <c r="Q116" s="85" t="n"/>
-      <c r="R116" s="85" t="n"/>
-      <c r="S116" s="85" t="n"/>
-      <c r="T116" s="84">
-        <f>IF(COUNT(Q116:S116)&lt;3,"",Q116+(11-R116)+S116)</f>
-        <v/>
-      </c>
-      <c r="U116" s="85" t="n"/>
-      <c r="V116" s="86" t="n"/>
-      <c r="W116" s="87">
-        <f>IF(AND(P116="◎ 候補リスト",U116&lt;&gt;"ボツ",U116&lt;&gt;"制作済み",T116&lt;&gt;"",OR('②候補ランキング'!$C$5="すべて",B116='②候補ランキング'!$C$5)),IF('②候補ランキング'!$C$4="ワクワク",Q116,IF('②候補ランキング'!$C$4="手軽さ",11-R116,IF('②候補ランキング'!$C$4="確信度",S116,T116)))*1000+T116+(1000-A116)/10000,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="117" ht="18" customHeight="1" s="35">
-      <c r="A117" s="84">
-        <f>IF(C117="","",ROW()-5)</f>
-        <v/>
-      </c>
-      <c r="B117" s="85" t="n"/>
-      <c r="C117" s="86" t="n"/>
-      <c r="D117" s="86" t="n"/>
-      <c r="E117" s="85" t="n"/>
-      <c r="F117" s="86" t="n"/>
-      <c r="G117" s="86" t="n"/>
-      <c r="H117" s="86" t="n"/>
-      <c r="I117" s="86" t="n"/>
-      <c r="J117" s="85" t="n"/>
-      <c r="K117" s="85" t="n"/>
-      <c r="L117" s="85" t="n"/>
-      <c r="M117" s="85" t="n"/>
-      <c r="N117" s="85" t="n"/>
-      <c r="O117" s="85" t="n"/>
-      <c r="P117" s="84">
-        <f>IF(C117="","",IF(OR(E117="",E117="未検証"),"① STEP1待ち",IF(E117="不通過","✕ STEP1不通過",IF(OR(G117="",H117=""),"② STEP2-3 未記入",IF(COUNTIF(J117:O117,"×")&gt;0,"✕ ボツ候補",IF(COUNTA(J117:O117)&lt;6,"③ STEP4 審査待ち",IF(COUNTIF(J117:O117,"△")&gt;0,"△ 修正して再審査","◎ 候補リスト")))))))</f>
-        <v/>
-      </c>
-      <c r="Q117" s="85" t="n"/>
-      <c r="R117" s="85" t="n"/>
-      <c r="S117" s="85" t="n"/>
-      <c r="T117" s="84">
-        <f>IF(COUNT(Q117:S117)&lt;3,"",Q117+(11-R117)+S117)</f>
-        <v/>
-      </c>
-      <c r="U117" s="85" t="n"/>
-      <c r="V117" s="86" t="n"/>
-      <c r="W117" s="87">
-        <f>IF(AND(P117="◎ 候補リスト",U117&lt;&gt;"ボツ",U117&lt;&gt;"制作済み",T117&lt;&gt;"",OR('②候補ランキング'!$C$5="すべて",B117='②候補ランキング'!$C$5)),IF('②候補ランキング'!$C$4="ワクワク",Q117,IF('②候補ランキング'!$C$4="手軽さ",11-R117,IF('②候補ランキング'!$C$4="確信度",S117,T117)))*1000+T117+(1000-A117)/10000,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="118" ht="18" customHeight="1" s="35">
-      <c r="A118" s="84">
-        <f>IF(C118="","",ROW()-5)</f>
-        <v/>
-      </c>
-      <c r="B118" s="85" t="n"/>
-      <c r="C118" s="86" t="n"/>
-      <c r="D118" s="86" t="n"/>
-      <c r="E118" s="85" t="n"/>
-      <c r="F118" s="86" t="n"/>
-      <c r="G118" s="86" t="n"/>
-      <c r="H118" s="86" t="n"/>
-      <c r="I118" s="86" t="n"/>
-      <c r="J118" s="85" t="n"/>
-      <c r="K118" s="85" t="n"/>
-      <c r="L118" s="85" t="n"/>
-      <c r="M118" s="85" t="n"/>
-      <c r="N118" s="85" t="n"/>
-      <c r="O118" s="85" t="n"/>
-      <c r="P118" s="84">
-        <f>IF(C118="","",IF(OR(E118="",E118="未検証"),"① STEP1待ち",IF(E118="不通過","✕ STEP1不通過",IF(OR(G118="",H118=""),"② STEP2-3 未記入",IF(COUNTIF(J118:O118,"×")&gt;0,"✕ ボツ候補",IF(COUNTA(J118:O118)&lt;6,"③ STEP4 審査待ち",IF(COUNTIF(J118:O118,"△")&gt;0,"△ 修正して再審査","◎ 候補リスト")))))))</f>
-        <v/>
-      </c>
-      <c r="Q118" s="85" t="n"/>
-      <c r="R118" s="85" t="n"/>
-      <c r="S118" s="85" t="n"/>
-      <c r="T118" s="84">
-        <f>IF(COUNT(Q118:S118)&lt;3,"",Q118+(11-R118)+S118)</f>
-        <v/>
-      </c>
-      <c r="U118" s="85" t="n"/>
-      <c r="V118" s="86" t="n"/>
-      <c r="W118" s="87">
-        <f>IF(AND(P118="◎ 候補リスト",U118&lt;&gt;"ボツ",U118&lt;&gt;"制作済み",T118&lt;&gt;"",OR('②候補ランキング'!$C$5="すべて",B118='②候補ランキング'!$C$5)),IF('②候補ランキング'!$C$4="ワクワク",Q118,IF('②候補ランキング'!$C$4="手軽さ",11-R118,IF('②候補ランキング'!$C$4="確信度",S118,T118)))*1000+T118+(1000-A118)/10000,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="119" ht="18" customHeight="1" s="35">
-      <c r="A119" s="84">
-        <f>IF(C119="","",ROW()-5)</f>
-        <v/>
-      </c>
-      <c r="B119" s="85" t="n"/>
-      <c r="C119" s="86" t="n"/>
-      <c r="D119" s="86" t="n"/>
-      <c r="E119" s="85" t="n"/>
-      <c r="F119" s="86" t="n"/>
-      <c r="G119" s="86" t="n"/>
-      <c r="H119" s="86" t="n"/>
-      <c r="I119" s="86" t="n"/>
-      <c r="J119" s="85" t="n"/>
-      <c r="K119" s="85" t="n"/>
-      <c r="L119" s="85" t="n"/>
-      <c r="M119" s="85" t="n"/>
-      <c r="N119" s="85" t="n"/>
-      <c r="O119" s="85" t="n"/>
-      <c r="P119" s="84">
-        <f>IF(C119="","",IF(OR(E119="",E119="未検証"),"① STEP1待ち",IF(E119="不通過","✕ STEP1不通過",IF(OR(G119="",H119=""),"② STEP2-3 未記入",IF(COUNTIF(J119:O119,"×")&gt;0,"✕ ボツ候補",IF(COUNTA(J119:O119)&lt;6,"③ STEP4 審査待ち",IF(COUNTIF(J119:O119,"△")&gt;0,"△ 修正して再審査","◎ 候補リスト")))))))</f>
-        <v/>
-      </c>
-      <c r="Q119" s="85" t="n"/>
-      <c r="R119" s="85" t="n"/>
-      <c r="S119" s="85" t="n"/>
-      <c r="T119" s="84">
-        <f>IF(COUNT(Q119:S119)&lt;3,"",Q119+(11-R119)+S119)</f>
-        <v/>
-      </c>
-      <c r="U119" s="85" t="n"/>
-      <c r="V119" s="86" t="n"/>
-      <c r="W119" s="87">
-        <f>IF(AND(P119="◎ 候補リスト",U119&lt;&gt;"ボツ",U119&lt;&gt;"制作済み",T119&lt;&gt;"",OR('②候補ランキング'!$C$5="すべて",B119='②候補ランキング'!$C$5)),IF('②候補ランキング'!$C$4="ワクワク",Q119,IF('②候補ランキング'!$C$4="手軽さ",11-R119,IF('②候補ランキング'!$C$4="確信度",S119,T119)))*1000+T119+(1000-A119)/10000,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="120" ht="18" customHeight="1" s="35">
-      <c r="A120" s="84">
-        <f>IF(C120="","",ROW()-5)</f>
-        <v/>
-      </c>
-      <c r="B120" s="85" t="n"/>
-      <c r="C120" s="86" t="n"/>
-      <c r="D120" s="86" t="n"/>
-      <c r="E120" s="85" t="n"/>
-      <c r="F120" s="86" t="n"/>
-      <c r="G120" s="86" t="n"/>
-      <c r="H120" s="86" t="n"/>
-      <c r="I120" s="86" t="n"/>
-      <c r="J120" s="85" t="n"/>
-      <c r="K120" s="85" t="n"/>
-      <c r="L120" s="85" t="n"/>
-      <c r="M120" s="85" t="n"/>
-      <c r="N120" s="85" t="n"/>
-      <c r="O120" s="85" t="n"/>
-      <c r="P120" s="84">
-        <f>IF(C120="","",IF(OR(E120="",E120="未検証"),"① STEP1待ち",IF(E120="不通過","✕ STEP1不通過",IF(OR(G120="",H120=""),"② STEP2-3 未記入",IF(COUNTIF(J120:O120,"×")&gt;0,"✕ ボツ候補",IF(COUNTA(J120:O120)&lt;6,"③ STEP4 審査待ち",IF(COUNTIF(J120:O120,"△")&gt;0,"△ 修正して再審査","◎ 候補リスト")))))))</f>
-        <v/>
-      </c>
-      <c r="Q120" s="85" t="n"/>
-      <c r="R120" s="85" t="n"/>
-      <c r="S120" s="85" t="n"/>
-      <c r="T120" s="84">
-        <f>IF(COUNT(Q120:S120)&lt;3,"",Q120+(11-R120)+S120)</f>
-        <v/>
-      </c>
-      <c r="U120" s="85" t="n"/>
-      <c r="V120" s="86" t="n"/>
-      <c r="W120" s="87">
-        <f>IF(AND(P120="◎ 候補リスト",U120&lt;&gt;"ボツ",U120&lt;&gt;"制作済み",T120&lt;&gt;"",OR('②候補ランキング'!$C$5="すべて",B120='②候補ランキング'!$C$5)),IF('②候補ランキング'!$C$4="ワクワク",Q120,IF('②候補ランキング'!$C$4="手軽さ",11-R120,IF('②候補ランキング'!$C$4="確信度",S120,T120)))*1000+T120+(1000-A120)/10000,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="121" ht="18" customHeight="1" s="35">
-      <c r="A121" s="84">
-        <f>IF(C121="","",ROW()-5)</f>
-        <v/>
-      </c>
-      <c r="B121" s="85" t="n"/>
-      <c r="C121" s="86" t="n"/>
-      <c r="D121" s="86" t="n"/>
-      <c r="E121" s="85" t="n"/>
-      <c r="F121" s="86" t="n"/>
-      <c r="G121" s="86" t="n"/>
-      <c r="H121" s="86" t="n"/>
-      <c r="I121" s="86" t="n"/>
-      <c r="J121" s="85" t="n"/>
-      <c r="K121" s="85" t="n"/>
-      <c r="L121" s="85" t="n"/>
-      <c r="M121" s="85" t="n"/>
-      <c r="N121" s="85" t="n"/>
-      <c r="O121" s="85" t="n"/>
-      <c r="P121" s="84">
-        <f>IF(C121="","",IF(OR(E121="",E121="未検証"),"① STEP1待ち",IF(E121="不通過","✕ STEP1不通過",IF(OR(G121="",H121=""),"② STEP2-3 未記入",IF(COUNTIF(J121:O121,"×")&gt;0,"✕ ボツ候補",IF(COUNTA(J121:O121)&lt;6,"③ STEP4 審査待ち",IF(COUNTIF(J121:O121,"△")&gt;0,"△ 修正して再審査","◎ 候補リスト")))))))</f>
-        <v/>
-      </c>
-      <c r="Q121" s="85" t="n"/>
-      <c r="R121" s="85" t="n"/>
-      <c r="S121" s="85" t="n"/>
-      <c r="T121" s="84">
-        <f>IF(COUNT(Q121:S121)&lt;3,"",Q121+(11-R121)+S121)</f>
-        <v/>
-      </c>
-      <c r="U121" s="85" t="n"/>
-      <c r="V121" s="86" t="n"/>
-      <c r="W121" s="87">
-        <f>IF(AND(P121="◎ 候補リスト",U121&lt;&gt;"ボツ",U121&lt;&gt;"制作済み",T121&lt;&gt;"",OR('②候補ランキング'!$C$5="すべて",B121='②候補ランキング'!$C$5)),IF('②候補ランキング'!$C$4="ワクワク",Q121,IF('②候補ランキング'!$C$4="手軽さ",11-R121,IF('②候補ランキング'!$C$4="確信度",S121,T121)))*1000+T121+(1000-A121)/10000,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="122" ht="18" customHeight="1" s="35">
-      <c r="A122" s="84">
-        <f>IF(C122="","",ROW()-5)</f>
-        <v/>
-      </c>
-      <c r="B122" s="85" t="n"/>
-      <c r="C122" s="86" t="n"/>
-      <c r="D122" s="86" t="n"/>
-      <c r="E122" s="85" t="n"/>
-      <c r="F122" s="86" t="n"/>
-      <c r="G122" s="86" t="n"/>
-      <c r="H122" s="86" t="n"/>
-      <c r="I122" s="86" t="n"/>
-      <c r="J122" s="85" t="n"/>
-      <c r="K122" s="85" t="n"/>
-      <c r="L122" s="85" t="n"/>
-      <c r="M122" s="85" t="n"/>
-      <c r="N122" s="85" t="n"/>
-      <c r="O122" s="85" t="n"/>
-      <c r="P122" s="84">
-        <f>IF(C122="","",IF(OR(E122="",E122="未検証"),"① STEP1待ち",IF(E122="不通過","✕ STEP1不通過",IF(OR(G122="",H122=""),"② STEP2-3 未記入",IF(COUNTIF(J122:O122,"×")&gt;0,"✕ ボツ候補",IF(COUNTA(J122:O122)&lt;6,"③ STEP4 審査待ち",IF(COUNTIF(J122:O122,"△")&gt;0,"△ 修正して再審査","◎ 候補リスト")))))))</f>
-        <v/>
-      </c>
-      <c r="Q122" s="85" t="n"/>
-      <c r="R122" s="85" t="n"/>
-      <c r="S122" s="85" t="n"/>
-      <c r="T122" s="84">
-        <f>IF(COUNT(Q122:S122)&lt;3,"",Q122+(11-R122)+S122)</f>
-        <v/>
-      </c>
-      <c r="U122" s="85" t="n"/>
-      <c r="V122" s="86" t="n"/>
-      <c r="W122" s="87">
-        <f>IF(AND(P122="◎ 候補リスト",U122&lt;&gt;"ボツ",U122&lt;&gt;"制作済み",T122&lt;&gt;"",OR('②候補ランキング'!$C$5="すべて",B122='②候補ランキング'!$C$5)),IF('②候補ランキング'!$C$4="ワクワク",Q122,IF('②候補ランキング'!$C$4="手軽さ",11-R122,IF('②候補ランキング'!$C$4="確信度",S122,T122)))*1000+T122+(1000-A122)/10000,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="123" ht="18" customHeight="1" s="35">
-      <c r="A123" s="84">
-        <f>IF(C123="","",ROW()-5)</f>
-        <v/>
-      </c>
-      <c r="B123" s="85" t="n"/>
-      <c r="C123" s="86" t="n"/>
-      <c r="D123" s="86" t="n"/>
-      <c r="E123" s="85" t="n"/>
-      <c r="F123" s="86" t="n"/>
-      <c r="G123" s="86" t="n"/>
-      <c r="H123" s="86" t="n"/>
-      <c r="I123" s="86" t="n"/>
-      <c r="J123" s="85" t="n"/>
-      <c r="K123" s="85" t="n"/>
-      <c r="L123" s="85" t="n"/>
-      <c r="M123" s="85" t="n"/>
-      <c r="N123" s="85" t="n"/>
-      <c r="O123" s="85" t="n"/>
-      <c r="P123" s="84">
-        <f>IF(C123="","",IF(OR(E123="",E123="未検証"),"① STEP1待ち",IF(E123="不通過","✕ STEP1不通過",IF(OR(G123="",H123=""),"② STEP2-3 未記入",IF(COUNTIF(J123:O123,"×")&gt;0,"✕ ボツ候補",IF(COUNTA(J123:O123)&lt;6,"③ STEP4 審査待ち",IF(COUNTIF(J123:O123,"△")&gt;0,"△ 修正して再審査","◎ 候補リスト")))))))</f>
-        <v/>
-      </c>
-      <c r="Q123" s="85" t="n"/>
-      <c r="R123" s="85" t="n"/>
-      <c r="S123" s="85" t="n"/>
-      <c r="T123" s="84">
-        <f>IF(COUNT(Q123:S123)&lt;3,"",Q123+(11-R123)+S123)</f>
-        <v/>
-      </c>
-      <c r="U123" s="85" t="n"/>
-      <c r="V123" s="86" t="n"/>
-      <c r="W123" s="87">
-        <f>IF(AND(P123="◎ 候補リスト",U123&lt;&gt;"ボツ",U123&lt;&gt;"制作済み",T123&lt;&gt;"",OR('②候補ランキング'!$C$5="すべて",B123='②候補ランキング'!$C$5)),IF('②候補ランキング'!$C$4="ワクワク",Q123,IF('②候補ランキング'!$C$4="手軽さ",11-R123,IF('②候補ランキング'!$C$4="確信度",S123,T123)))*1000+T123+(1000-A123)/10000,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="124" ht="18" customHeight="1" s="35">
-      <c r="A124" s="84">
-        <f>IF(C124="","",ROW()-5)</f>
-        <v/>
-      </c>
-      <c r="B124" s="85" t="n"/>
-      <c r="C124" s="86" t="n"/>
-      <c r="D124" s="86" t="n"/>
-      <c r="E124" s="85" t="n"/>
-      <c r="F124" s="86" t="n"/>
-      <c r="G124" s="86" t="n"/>
-      <c r="H124" s="86" t="n"/>
-      <c r="I124" s="86" t="n"/>
-      <c r="J124" s="85" t="n"/>
-      <c r="K124" s="85" t="n"/>
-      <c r="L124" s="85" t="n"/>
-      <c r="M124" s="85" t="n"/>
-      <c r="N124" s="85" t="n"/>
-      <c r="O124" s="85" t="n"/>
-      <c r="P124" s="84">
-        <f>IF(C124="","",IF(OR(E124="",E124="未検証"),"① STEP1待ち",IF(E124="不通過","✕ STEP1不通過",IF(OR(G124="",H124=""),"② STEP2-3 未記入",IF(COUNTIF(J124:O124,"×")&gt;0,"✕ ボツ候補",IF(COUNTA(J124:O124)&lt;6,"③ STEP4 審査待ち",IF(COUNTIF(J124:O124,"△")&gt;0,"△ 修正して再審査","◎ 候補リスト")))))))</f>
-        <v/>
-      </c>
-      <c r="Q124" s="85" t="n"/>
-      <c r="R124" s="85" t="n"/>
-      <c r="S124" s="85" t="n"/>
-      <c r="T124" s="84">
-        <f>IF(COUNT(Q124:S124)&lt;3,"",Q124+(11-R124)+S124)</f>
-        <v/>
-      </c>
-      <c r="U124" s="85" t="n"/>
-      <c r="V124" s="86" t="n"/>
-      <c r="W124" s="87">
-        <f>IF(AND(P124="◎ 候補リスト",U124&lt;&gt;"ボツ",U124&lt;&gt;"制作済み",T124&lt;&gt;"",OR('②候補ランキング'!$C$5="すべて",B124='②候補ランキング'!$C$5)),IF('②候補ランキング'!$C$4="ワクワク",Q124,IF('②候補ランキング'!$C$4="手軽さ",11-R124,IF('②候補ランキング'!$C$4="確信度",S124,T124)))*1000+T124+(1000-A124)/10000,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="125" ht="18" customHeight="1" s="35">
-      <c r="A125" s="84">
-        <f>IF(C125="","",ROW()-5)</f>
-        <v/>
-      </c>
-      <c r="B125" s="85" t="n"/>
-      <c r="C125" s="86" t="n"/>
-      <c r="D125" s="86" t="n"/>
-      <c r="E125" s="85" t="n"/>
-      <c r="F125" s="86" t="n"/>
-      <c r="G125" s="86" t="n"/>
-      <c r="H125" s="86" t="n"/>
-      <c r="I125" s="86" t="n"/>
-      <c r="J125" s="85" t="n"/>
-      <c r="K125" s="85" t="n"/>
-      <c r="L125" s="85" t="n"/>
-      <c r="M125" s="85" t="n"/>
-      <c r="N125" s="85" t="n"/>
-      <c r="O125" s="85" t="n"/>
-      <c r="P125" s="84">
-        <f>IF(C125="","",IF(OR(E125="",E125="未検証"),"① STEP1待ち",IF(E125="不通過","✕ STEP1不通過",IF(OR(G125="",H125=""),"② STEP2-3 未記入",IF(COUNTIF(J125:O125,"×")&gt;0,"✕ ボツ候補",IF(COUNTA(J125:O125)&lt;6,"③ STEP4 審査待ち",IF(COUNTIF(J125:O125,"△")&gt;0,"△ 修正して再審査","◎ 候補リスト")))))))</f>
-        <v/>
-      </c>
-      <c r="Q125" s="85" t="n"/>
-      <c r="R125" s="85" t="n"/>
-      <c r="S125" s="85" t="n"/>
-      <c r="T125" s="84">
-        <f>IF(COUNT(Q125:S125)&lt;3,"",Q125+(11-R125)+S125)</f>
-        <v/>
-      </c>
-      <c r="U125" s="85" t="n"/>
-      <c r="V125" s="86" t="n"/>
-      <c r="W125" s="87">
-        <f>IF(AND(P125="◎ 候補リスト",U125&lt;&gt;"ボツ",U125&lt;&gt;"制作済み",T125&lt;&gt;"",OR('②候補ランキング'!$C$5="すべて",B125='②候補ランキング'!$C$5)),IF('②候補ランキング'!$C$4="ワクワク",Q125,IF('②候補ランキング'!$C$4="手軽さ",11-R125,IF('②候補ランキング'!$C$4="確信度",S125,T125)))*1000+T125+(1000-A125)/10000,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="126" ht="18" customHeight="1" s="35">
-      <c r="A126" s="84">
-        <f>IF(C126="","",ROW()-5)</f>
-        <v/>
-      </c>
-      <c r="B126" s="85" t="n"/>
-      <c r="C126" s="86" t="n"/>
-      <c r="D126" s="86" t="n"/>
-      <c r="E126" s="85" t="n"/>
-      <c r="F126" s="86" t="n"/>
-      <c r="G126" s="86" t="n"/>
-      <c r="H126" s="86" t="n"/>
-      <c r="I126" s="86" t="n"/>
-      <c r="J126" s="85" t="n"/>
-      <c r="K126" s="85" t="n"/>
-      <c r="L126" s="85" t="n"/>
-      <c r="M126" s="85" t="n"/>
-      <c r="N126" s="85" t="n"/>
-      <c r="O126" s="85" t="n"/>
-      <c r="P126" s="84">
-        <f>IF(C126="","",IF(OR(E126="",E126="未検証"),"① STEP1待ち",IF(E126="不通過","✕ STEP1不通過",IF(OR(G126="",H126=""),"② STEP2-3 未記入",IF(COUNTIF(J126:O126,"×")&gt;0,"✕ ボツ候補",IF(COUNTA(J126:O126)&lt;6,"③ STEP4 審査待ち",IF(COUNTIF(J126:O126,"△")&gt;0,"△ 修正して再審査","◎ 候補リスト")))))))</f>
-        <v/>
-      </c>
-      <c r="Q126" s="85" t="n"/>
-      <c r="R126" s="85" t="n"/>
-      <c r="S126" s="85" t="n"/>
-      <c r="T126" s="84">
-        <f>IF(COUNT(Q126:S126)&lt;3,"",Q126+(11-R126)+S126)</f>
-        <v/>
-      </c>
-      <c r="U126" s="85" t="n"/>
-      <c r="V126" s="86" t="n"/>
-      <c r="W126" s="87">
-        <f>IF(AND(P126="◎ 候補リスト",U126&lt;&gt;"ボツ",U126&lt;&gt;"制作済み",T126&lt;&gt;"",OR('②候補ランキング'!$C$5="すべて",B126='②候補ランキング'!$C$5)),IF('②候補ランキング'!$C$4="ワクワク",Q126,IF('②候補ランキング'!$C$4="手軽さ",11-R126,IF('②候補ランキング'!$C$4="確信度",S126,T126)))*1000+T126+(1000-A126)/10000,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="127" ht="18" customHeight="1" s="35">
-      <c r="A127" s="84">
-        <f>IF(C127="","",ROW()-5)</f>
-        <v/>
-      </c>
-      <c r="B127" s="85" t="n"/>
-      <c r="C127" s="86" t="n"/>
-      <c r="D127" s="86" t="n"/>
-      <c r="E127" s="85" t="n"/>
-      <c r="F127" s="86" t="n"/>
-      <c r="G127" s="86" t="n"/>
-      <c r="H127" s="86" t="n"/>
-      <c r="I127" s="86" t="n"/>
-      <c r="J127" s="85" t="n"/>
-      <c r="K127" s="85" t="n"/>
-      <c r="L127" s="85" t="n"/>
-      <c r="M127" s="85" t="n"/>
-      <c r="N127" s="85" t="n"/>
-      <c r="O127" s="85" t="n"/>
-      <c r="P127" s="84">
-        <f>IF(C127="","",IF(OR(E127="",E127="未検証"),"① STEP1待ち",IF(E127="不通過","✕ STEP1不通過",IF(OR(G127="",H127=""),"② STEP2-3 未記入",IF(COUNTIF(J127:O127,"×")&gt;0,"✕ ボツ候補",IF(COUNTA(J127:O127)&lt;6,"③ STEP4 審査待ち",IF(COUNTIF(J127:O127,"△")&gt;0,"△ 修正して再審査","◎ 候補リスト")))))))</f>
-        <v/>
-      </c>
-      <c r="Q127" s="85" t="n"/>
-      <c r="R127" s="85" t="n"/>
-      <c r="S127" s="85" t="n"/>
-      <c r="T127" s="84">
-        <f>IF(COUNT(Q127:S127)&lt;3,"",Q127+(11-R127)+S127)</f>
-        <v/>
-      </c>
-      <c r="U127" s="85" t="n"/>
-      <c r="V127" s="86" t="n"/>
-      <c r="W127" s="87">
-        <f>IF(AND(P127="◎ 候補リスト",U127&lt;&gt;"ボツ",U127&lt;&gt;"制作済み",T127&lt;&gt;"",OR('②候補ランキング'!$C$5="すべて",B127='②候補ランキング'!$C$5)),IF('②候補ランキング'!$C$4="ワクワク",Q127,IF('②候補ランキング'!$C$4="手軽さ",11-R127,IF('②候補ランキング'!$C$4="確信度",S127,T127)))*1000+T127+(1000-A127)/10000,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="128" ht="18" customHeight="1" s="35">
-      <c r="A128" s="84">
-        <f>IF(C128="","",ROW()-5)</f>
-        <v/>
-      </c>
-      <c r="B128" s="85" t="n"/>
-      <c r="C128" s="86" t="n"/>
-      <c r="D128" s="86" t="n"/>
-      <c r="E128" s="85" t="n"/>
-      <c r="F128" s="86" t="n"/>
-      <c r="G128" s="86" t="n"/>
-      <c r="H128" s="86" t="n"/>
-      <c r="I128" s="86" t="n"/>
-      <c r="J128" s="85" t="n"/>
-      <c r="K128" s="85" t="n"/>
-      <c r="L128" s="85" t="n"/>
-      <c r="M128" s="85" t="n"/>
-      <c r="N128" s="85" t="n"/>
-      <c r="O128" s="85" t="n"/>
-      <c r="P128" s="84">
-        <f>IF(C128="","",IF(OR(E128="",E128="未検証"),"① STEP1待ち",IF(E128="不通過","✕ STEP1不通過",IF(OR(G128="",H128=""),"② STEP2-3 未記入",IF(COUNTIF(J128:O128,"×")&gt;0,"✕ ボツ候補",IF(COUNTA(J128:O128)&lt;6,"③ STEP4 審査待ち",IF(COUNTIF(J128:O128,"△")&gt;0,"△ 修正して再審査","◎ 候補リスト")))))))</f>
-        <v/>
-      </c>
-      <c r="Q128" s="85" t="n"/>
-      <c r="R128" s="85" t="n"/>
-      <c r="S128" s="85" t="n"/>
-      <c r="T128" s="84">
-        <f>IF(COUNT(Q128:S128)&lt;3,"",Q128+(11-R128)+S128)</f>
-        <v/>
-      </c>
-      <c r="U128" s="85" t="n"/>
-      <c r="V128" s="86" t="n"/>
-      <c r="W128" s="87">
-        <f>IF(AND(P128="◎ 候補リスト",U128&lt;&gt;"ボツ",U128&lt;&gt;"制作済み",T128&lt;&gt;"",OR('②候補ランキング'!$C$5="すべて",B128='②候補ランキング'!$C$5)),IF('②候補ランキング'!$C$4="ワクワク",Q128,IF('②候補ランキング'!$C$4="手軽さ",11-R128,IF('②候補ランキング'!$C$4="確信度",S128,T128)))*1000+T128+(1000-A128)/10000,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="129" ht="18" customHeight="1" s="35">
-      <c r="A129" s="84">
-        <f>IF(C129="","",ROW()-5)</f>
-        <v/>
-      </c>
-      <c r="B129" s="85" t="n"/>
-      <c r="C129" s="86" t="n"/>
-      <c r="D129" s="86" t="n"/>
-      <c r="E129" s="85" t="n"/>
-      <c r="F129" s="86" t="n"/>
-      <c r="G129" s="86" t="n"/>
-      <c r="H129" s="86" t="n"/>
-      <c r="I129" s="86" t="n"/>
-      <c r="J129" s="85" t="n"/>
-      <c r="K129" s="85" t="n"/>
-      <c r="L129" s="85" t="n"/>
-      <c r="M129" s="85" t="n"/>
-      <c r="N129" s="85" t="n"/>
-      <c r="O129" s="85" t="n"/>
-      <c r="P129" s="84">
-        <f>IF(C129="","",IF(OR(E129="",E129="未検証"),"① STEP1待ち",IF(E129="不通過","✕ STEP1不通過",IF(OR(G129="",H129=""),"② STEP2-3 未記入",IF(COUNTIF(J129:O129,"×")&gt;0,"✕ ボツ候補",IF(COUNTA(J129:O129)&lt;6,"③ STEP4 審査待ち",IF(COUNTIF(J129:O129,"△")&gt;0,"△ 修正して再審査","◎ 候補リスト")))))))</f>
-        <v/>
-      </c>
-      <c r="Q129" s="85" t="n"/>
-      <c r="R129" s="85" t="n"/>
-      <c r="S129" s="85" t="n"/>
-      <c r="T129" s="84">
-        <f>IF(COUNT(Q129:S129)&lt;3,"",Q129+(11-R129)+S129)</f>
-        <v/>
-      </c>
-      <c r="U129" s="85" t="n"/>
-      <c r="V129" s="86" t="n"/>
-      <c r="W129" s="87">
-        <f>IF(AND(P129="◎ 候補リスト",U129&lt;&gt;"ボツ",U129&lt;&gt;"制作済み",T129&lt;&gt;"",OR('②候補ランキング'!$C$5="すべて",B129='②候補ランキング'!$C$5)),IF('②候補ランキング'!$C$4="ワクワク",Q129,IF('②候補ランキング'!$C$4="手軽さ",11-R129,IF('②候補ランキング'!$C$4="確信度",S129,T129)))*1000+T129+(1000-A129)/10000,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="130" ht="18" customHeight="1" s="35">
-      <c r="A130" s="84">
-        <f>IF(C130="","",ROW()-5)</f>
-        <v/>
-      </c>
-      <c r="B130" s="85" t="n"/>
-      <c r="C130" s="86" t="n"/>
-      <c r="D130" s="86" t="n"/>
-      <c r="E130" s="85" t="n"/>
-      <c r="F130" s="86" t="n"/>
-      <c r="G130" s="86" t="n"/>
-      <c r="H130" s="86" t="n"/>
-      <c r="I130" s="86" t="n"/>
-      <c r="J130" s="85" t="n"/>
-      <c r="K130" s="85" t="n"/>
-      <c r="L130" s="85" t="n"/>
-      <c r="M130" s="85" t="n"/>
-      <c r="N130" s="85" t="n"/>
-      <c r="O130" s="85" t="n"/>
-      <c r="P130" s="84">
-        <f>IF(C130="","",IF(OR(E130="",E130="未検証"),"① STEP1待ち",IF(E130="不通過","✕ STEP1不通過",IF(OR(G130="",H130=""),"② STEP2-3 未記入",IF(COUNTIF(J130:O130,"×")&gt;0,"✕ ボツ候補",IF(COUNTA(J130:O130)&lt;6,"③ STEP4 審査待ち",IF(COUNTIF(J130:O130,"△")&gt;0,"△ 修正して再審査","◎ 候補リスト")))))))</f>
-        <v/>
-      </c>
-      <c r="Q130" s="85" t="n"/>
-      <c r="R130" s="85" t="n"/>
-      <c r="S130" s="85" t="n"/>
-      <c r="T130" s="84">
-        <f>IF(COUNT(Q130:S130)&lt;3,"",Q130+(11-R130)+S130)</f>
-        <v/>
-      </c>
-      <c r="U130" s="85" t="n"/>
-      <c r="V130" s="86" t="n"/>
-      <c r="W130" s="87">
-        <f>IF(AND(P130="◎ 候補リスト",U130&lt;&gt;"ボツ",U130&lt;&gt;"制作済み",T130&lt;&gt;"",OR('②候補ランキング'!$C$5="すべて",B130='②候補ランキング'!$C$5)),IF('②候補ランキング'!$C$4="ワクワク",Q130,IF('②候補ランキング'!$C$4="手軽さ",11-R130,IF('②候補ランキング'!$C$4="確信度",S130,T130)))*1000+T130+(1000-A130)/10000,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="131" ht="18" customHeight="1" s="35">
-      <c r="A131" s="84">
-        <f>IF(C131="","",ROW()-5)</f>
-        <v/>
-      </c>
-      <c r="B131" s="85" t="n"/>
-      <c r="C131" s="86" t="n"/>
-      <c r="D131" s="86" t="n"/>
-      <c r="E131" s="85" t="n"/>
-      <c r="F131" s="86" t="n"/>
-      <c r="G131" s="86" t="n"/>
-      <c r="H131" s="86" t="n"/>
-      <c r="I131" s="86" t="n"/>
-      <c r="J131" s="85" t="n"/>
-      <c r="K131" s="85" t="n"/>
-      <c r="L131" s="85" t="n"/>
-      <c r="M131" s="85" t="n"/>
-      <c r="N131" s="85" t="n"/>
-      <c r="O131" s="85" t="n"/>
-      <c r="P131" s="84">
-        <f>IF(C131="","",IF(OR(E131="",E131="未検証"),"① STEP1待ち",IF(E131="不通過","✕ STEP1不通過",IF(OR(G131="",H131=""),"② STEP2-3 未記入",IF(COUNTIF(J131:O131,"×")&gt;0,"✕ ボツ候補",IF(COUNTA(J131:O131)&lt;6,"③ STEP4 審査待ち",IF(COUNTIF(J131:O131,"△")&gt;0,"△ 修正して再審査","◎ 候補リスト")))))))</f>
-        <v/>
-      </c>
-      <c r="Q131" s="85" t="n"/>
-      <c r="R131" s="85" t="n"/>
-      <c r="S131" s="85" t="n"/>
-      <c r="T131" s="84">
-        <f>IF(COUNT(Q131:S131)&lt;3,"",Q131+(11-R131)+S131)</f>
-        <v/>
-      </c>
-      <c r="U131" s="85" t="n"/>
-      <c r="V131" s="86" t="n"/>
-      <c r="W131" s="87">
-        <f>IF(AND(P131="◎ 候補リスト",U131&lt;&gt;"ボツ",U131&lt;&gt;"制作済み",T131&lt;&gt;"",OR('②候補ランキング'!$C$5="すべて",B131='②候補ランキング'!$C$5)),IF('②候補ランキング'!$C$4="ワクワク",Q131,IF('②候補ランキング'!$C$4="手軽さ",11-R131,IF('②候補ランキング'!$C$4="確信度",S131,T131)))*1000+T131+(1000-A131)/10000,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="132" ht="18" customHeight="1" s="35">
-      <c r="A132" s="84">
-        <f>IF(C132="","",ROW()-5)</f>
-        <v/>
-      </c>
-      <c r="B132" s="85" t="n"/>
-      <c r="C132" s="86" t="n"/>
-      <c r="D132" s="86" t="n"/>
-      <c r="E132" s="85" t="n"/>
-      <c r="F132" s="86" t="n"/>
-      <c r="G132" s="86" t="n"/>
-      <c r="H132" s="86" t="n"/>
-      <c r="I132" s="86" t="n"/>
-      <c r="J132" s="85" t="n"/>
-      <c r="K132" s="85" t="n"/>
-      <c r="L132" s="85" t="n"/>
-      <c r="M132" s="85" t="n"/>
-      <c r="N132" s="85" t="n"/>
-      <c r="O132" s="85" t="n"/>
-      <c r="P132" s="84">
-        <f>IF(C132="","",IF(OR(E132="",E132="未検証"),"① STEP1待ち",IF(E132="不通過","✕ STEP1不通過",IF(OR(G132="",H132=""),"② STEP2-3 未記入",IF(COUNTIF(J132:O132,"×")&gt;0,"✕ ボツ候補",IF(COUNTA(J132:O132)&lt;6,"③ STEP4 審査待ち",IF(COUNTIF(J132:O132,"△")&gt;0,"△ 修正して再審査","◎ 候補リスト")))))))</f>
-        <v/>
-      </c>
-      <c r="Q132" s="85" t="n"/>
-      <c r="R132" s="85" t="n"/>
-      <c r="S132" s="85" t="n"/>
-      <c r="T132" s="84">
-        <f>IF(COUNT(Q132:S132)&lt;3,"",Q132+(11-R132)+S132)</f>
-        <v/>
-      </c>
-      <c r="U132" s="85" t="n"/>
-      <c r="V132" s="86" t="n"/>
-      <c r="W132" s="87">
-        <f>IF(AND(P132="◎ 候補リスト",U132&lt;&gt;"ボツ",U132&lt;&gt;"制作済み",T132&lt;&gt;"",OR('②候補ランキング'!$C$5="すべて",B132='②候補ランキング'!$C$5)),IF('②候補ランキング'!$C$4="ワクワク",Q132,IF('②候補ランキング'!$C$4="手軽さ",11-R132,IF('②候補ランキング'!$C$4="確信度",S132,T132)))*1000+T132+(1000-A132)/10000,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="133" ht="18" customHeight="1" s="35">
-      <c r="A133" s="84">
-        <f>IF(C133="","",ROW()-5)</f>
-        <v/>
-      </c>
-      <c r="B133" s="85" t="n"/>
-      <c r="C133" s="86" t="n"/>
-      <c r="D133" s="86" t="n"/>
-      <c r="E133" s="85" t="n"/>
-      <c r="F133" s="86" t="n"/>
-      <c r="G133" s="86" t="n"/>
-      <c r="H133" s="86" t="n"/>
-      <c r="I133" s="86" t="n"/>
-      <c r="J133" s="85" t="n"/>
-      <c r="K133" s="85" t="n"/>
-      <c r="L133" s="85" t="n"/>
-      <c r="M133" s="85" t="n"/>
-      <c r="N133" s="85" t="n"/>
-      <c r="O133" s="85" t="n"/>
-      <c r="P133" s="84">
-        <f>IF(C133="","",IF(OR(E133="",E133="未検証"),"① STEP1待ち",IF(E133="不通過","✕ STEP1不通過",IF(OR(G133="",H133=""),"② STEP2-3 未記入",IF(COUNTIF(J133:O133,"×")&gt;0,"✕ ボツ候補",IF(COUNTA(J133:O133)&lt;6,"③ STEP4 審査待ち",IF(COUNTIF(J133:O133,"△")&gt;0,"△ 修正して再審査","◎ 候補リスト")))))))</f>
-        <v/>
-      </c>
-      <c r="Q133" s="85" t="n"/>
-      <c r="R133" s="85" t="n"/>
-      <c r="S133" s="85" t="n"/>
-      <c r="T133" s="84">
-        <f>IF(COUNT(Q133:S133)&lt;3,"",Q133+(11-R133)+S133)</f>
-        <v/>
-      </c>
-      <c r="U133" s="85" t="n"/>
-      <c r="V133" s="86" t="n"/>
-      <c r="W133" s="87">
-        <f>IF(AND(P133="◎ 候補リスト",U133&lt;&gt;"ボツ",U133&lt;&gt;"制作済み",T133&lt;&gt;"",OR('②候補ランキング'!$C$5="すべて",B133='②候補ランキング'!$C$5)),IF('②候補ランキング'!$C$4="ワクワク",Q133,IF('②候補ランキング'!$C$4="手軽さ",11-R133,IF('②候補ランキング'!$C$4="確信度",S133,T133)))*1000+T133+(1000-A133)/10000,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="134" ht="18" customHeight="1" s="35">
-      <c r="A134" s="84">
-        <f>IF(C134="","",ROW()-5)</f>
-        <v/>
-      </c>
-      <c r="B134" s="85" t="n"/>
-      <c r="C134" s="86" t="n"/>
-      <c r="D134" s="86" t="n"/>
-      <c r="E134" s="85" t="n"/>
-      <c r="F134" s="86" t="n"/>
-      <c r="G134" s="86" t="n"/>
-      <c r="H134" s="86" t="n"/>
-      <c r="I134" s="86" t="n"/>
-      <c r="J134" s="85" t="n"/>
-      <c r="K134" s="85" t="n"/>
-      <c r="L134" s="85" t="n"/>
-      <c r="M134" s="85" t="n"/>
-      <c r="N134" s="85" t="n"/>
-      <c r="O134" s="85" t="n"/>
-      <c r="P134" s="84">
-        <f>IF(C134="","",IF(OR(E134="",E134="未検証"),"① STEP1待ち",IF(E134="不通過","✕ STEP1不通過",IF(OR(G134="",H134=""),"② STEP2-3 未記入",IF(COUNTIF(J134:O134,"×")&gt;0,"✕ ボツ候補",IF(COUNTA(J134:O134)&lt;6,"③ STEP4 審査待ち",IF(COUNTIF(J134:O134,"△")&gt;0,"△ 修正して再審査","◎ 候補リスト")))))))</f>
-        <v/>
-      </c>
-      <c r="Q134" s="85" t="n"/>
-      <c r="R134" s="85" t="n"/>
-      <c r="S134" s="85" t="n"/>
-      <c r="T134" s="84">
-        <f>IF(COUNT(Q134:S134)&lt;3,"",Q134+(11-R134)+S134)</f>
-        <v/>
-      </c>
-      <c r="U134" s="85" t="n"/>
-      <c r="V134" s="86" t="n"/>
-      <c r="W134" s="87">
-        <f>IF(AND(P134="◎ 候補リスト",U134&lt;&gt;"ボツ",U134&lt;&gt;"制作済み",T134&lt;&gt;"",OR('②候補ランキング'!$C$5="すべて",B134='②候補ランキング'!$C$5)),IF('②候補ランキング'!$C$4="ワクワク",Q134,IF('②候補ランキング'!$C$4="手軽さ",11-R134,IF('②候補ランキング'!$C$4="確信度",S134,T134)))*1000+T134+(1000-A134)/10000,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="135" ht="18" customHeight="1" s="35">
-      <c r="A135" s="84">
-        <f>IF(C135="","",ROW()-5)</f>
-        <v/>
-      </c>
-      <c r="B135" s="85" t="n"/>
-      <c r="C135" s="86" t="n"/>
-      <c r="D135" s="86" t="n"/>
-      <c r="E135" s="85" t="n"/>
-      <c r="F135" s="86" t="n"/>
-      <c r="G135" s="86" t="n"/>
-      <c r="H135" s="86" t="n"/>
-      <c r="I135" s="86" t="n"/>
-      <c r="J135" s="85" t="n"/>
-      <c r="K135" s="85" t="n"/>
-      <c r="L135" s="85" t="n"/>
-      <c r="M135" s="85" t="n"/>
-      <c r="N135" s="85" t="n"/>
-      <c r="O135" s="85" t="n"/>
-      <c r="P135" s="84">
-        <f>IF(C135="","",IF(OR(E135="",E135="未検証"),"① STEP1待ち",IF(E135="不通過","✕ STEP1不通過",IF(OR(G135="",H135=""),"② STEP2-3 未記入",IF(COUNTIF(J135:O135,"×")&gt;0,"✕ ボツ候補",IF(COUNTA(J135:O135)&lt;6,"③ STEP4 審査待ち",IF(COUNTIF(J135:O135,"△")&gt;0,"△ 修正して再審査","◎ 候補リスト")))))))</f>
-        <v/>
-      </c>
-      <c r="Q135" s="85" t="n"/>
-      <c r="R135" s="85" t="n"/>
-      <c r="S135" s="85" t="n"/>
-      <c r="T135" s="84">
-        <f>IF(COUNT(Q135:S135)&lt;3,"",Q135+(11-R135)+S135)</f>
-        <v/>
-      </c>
-      <c r="U135" s="85" t="n"/>
-      <c r="V135" s="86" t="n"/>
-      <c r="W135" s="87">
-        <f>IF(AND(P135="◎ 候補リスト",U135&lt;&gt;"ボツ",U135&lt;&gt;"制作済み",T135&lt;&gt;"",OR('②候補ランキング'!$C$5="すべて",B135='②候補ランキング'!$C$5)),IF('②候補ランキング'!$C$4="ワクワク",Q135,IF('②候補ランキング'!$C$4="手軽さ",11-R135,IF('②候補ランキング'!$C$4="確信度",S135,T135)))*1000+T135+(1000-A135)/10000,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="136" ht="18" customHeight="1" s="35">
-      <c r="A136" s="84">
-        <f>IF(C136="","",ROW()-5)</f>
-        <v/>
-      </c>
-      <c r="B136" s="85" t="n"/>
-      <c r="C136" s="86" t="n"/>
-      <c r="D136" s="86" t="n"/>
-      <c r="E136" s="85" t="n"/>
-      <c r="F136" s="86" t="n"/>
-      <c r="G136" s="86" t="n"/>
-      <c r="H136" s="86" t="n"/>
-      <c r="I136" s="86" t="n"/>
-      <c r="J136" s="85" t="n"/>
-      <c r="K136" s="85" t="n"/>
-      <c r="L136" s="85" t="n"/>
-      <c r="M136" s="85" t="n"/>
-      <c r="N136" s="85" t="n"/>
-      <c r="O136" s="85" t="n"/>
-      <c r="P136" s="84">
-        <f>IF(C136="","",IF(OR(E136="",E136="未検証"),"① STEP1待ち",IF(E136="不通過","✕ STEP1不通過",IF(OR(G136="",H136=""),"② STEP2-3 未記入",IF(COUNTIF(J136:O136,"×")&gt;0,"✕ ボツ候補",IF(COUNTA(J136:O136)&lt;6,"③ STEP4 審査待ち",IF(COUNTIF(J136:O136,"△")&gt;0,"△ 修正して再審査","◎ 候補リスト")))))))</f>
-        <v/>
-      </c>
-      <c r="Q136" s="85" t="n"/>
-      <c r="R136" s="85" t="n"/>
-      <c r="S136" s="85" t="n"/>
-      <c r="T136" s="84">
-        <f>IF(COUNT(Q136:S136)&lt;3,"",Q136+(11-R136)+S136)</f>
-        <v/>
-      </c>
-      <c r="U136" s="85" t="n"/>
-      <c r="V136" s="86" t="n"/>
-      <c r="W136" s="87">
-        <f>IF(AND(P136="◎ 候補リスト",U136&lt;&gt;"ボツ",U136&lt;&gt;"制作済み",T136&lt;&gt;"",OR('②候補ランキング'!$C$5="すべて",B136='②候補ランキング'!$C$5)),IF('②候補ランキング'!$C$4="ワクワク",Q136,IF('②候補ランキング'!$C$4="手軽さ",11-R136,IF('②候補ランキング'!$C$4="確信度",S136,T136)))*1000+T136+(1000-A136)/10000,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="137" ht="18" customHeight="1" s="35">
-      <c r="A137" s="84">
-        <f>IF(C137="","",ROW()-5)</f>
-        <v/>
-      </c>
-      <c r="B137" s="85" t="n"/>
-      <c r="C137" s="86" t="n"/>
-      <c r="D137" s="86" t="n"/>
-      <c r="E137" s="85" t="n"/>
-      <c r="F137" s="86" t="n"/>
-      <c r="G137" s="86" t="n"/>
-      <c r="H137" s="86" t="n"/>
-      <c r="I137" s="86" t="n"/>
-      <c r="J137" s="85" t="n"/>
-      <c r="K137" s="85" t="n"/>
-      <c r="L137" s="85" t="n"/>
-      <c r="M137" s="85" t="n"/>
-      <c r="N137" s="85" t="n"/>
-      <c r="O137" s="85" t="n"/>
-      <c r="P137" s="84">
-        <f>IF(C137="","",IF(OR(E137="",E137="未検証"),"① STEP1待ち",IF(E137="不通過","✕ STEP1不通過",IF(OR(G137="",H137=""),"② STEP2-3 未記入",IF(COUNTIF(J137:O137,"×")&gt;0,"✕ ボツ候補",IF(COUNTA(J137:O137)&lt;6,"③ STEP4 審査待ち",IF(COUNTIF(J137:O137,"△")&gt;0,"△ 修正して再審査","◎ 候補リスト")))))))</f>
-        <v/>
-      </c>
-      <c r="Q137" s="85" t="n"/>
-      <c r="R137" s="85" t="n"/>
-      <c r="S137" s="85" t="n"/>
-      <c r="T137" s="84">
-        <f>IF(COUNT(Q137:S137)&lt;3,"",Q137+(11-R137)+S137)</f>
-        <v/>
-      </c>
-      <c r="U137" s="85" t="n"/>
-      <c r="V137" s="86" t="n"/>
-      <c r="W137" s="87">
-        <f>IF(AND(P137="◎ 候補リスト",U137&lt;&gt;"ボツ",U137&lt;&gt;"制作済み",T137&lt;&gt;"",OR('②候補ランキング'!$C$5="すべて",B137='②候補ランキング'!$C$5)),IF('②候補ランキング'!$C$4="ワクワク",Q137,IF('②候補ランキング'!$C$4="手軽さ",11-R137,IF('②候補ランキング'!$C$4="確信度",S137,T137)))*1000+T137+(1000-A137)/10000,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="138" ht="18" customHeight="1" s="35">
-      <c r="A138" s="84">
-        <f>IF(C138="","",ROW()-5)</f>
-        <v/>
-      </c>
-      <c r="B138" s="85" t="n"/>
-      <c r="C138" s="86" t="n"/>
-      <c r="D138" s="86" t="n"/>
-      <c r="E138" s="85" t="n"/>
-      <c r="F138" s="86" t="n"/>
-      <c r="G138" s="86" t="n"/>
-      <c r="H138" s="86" t="n"/>
-      <c r="I138" s="86" t="n"/>
-      <c r="J138" s="85" t="n"/>
-      <c r="K138" s="85" t="n"/>
-      <c r="L138" s="85" t="n"/>
-      <c r="M138" s="85" t="n"/>
-      <c r="N138" s="85" t="n"/>
-      <c r="O138" s="85" t="n"/>
-      <c r="P138" s="84">
-        <f>IF(C138="","",IF(OR(E138="",E138="未検証"),"① STEP1待ち",IF(E138="不通過","✕ STEP1不通過",IF(OR(G138="",H138=""),"② STEP2-3 未記入",IF(COUNTIF(J138:O138,"×")&gt;0,"✕ ボツ候補",IF(COUNTA(J138:O138)&lt;6,"③ STEP4 審査待ち",IF(COUNTIF(J138:O138,"△")&gt;0,"△ 修正して再審査","◎ 候補リスト")))))))</f>
-        <v/>
-      </c>
-      <c r="Q138" s="85" t="n"/>
-      <c r="R138" s="85" t="n"/>
-      <c r="S138" s="85" t="n"/>
-      <c r="T138" s="84">
-        <f>IF(COUNT(Q138:S138)&lt;3,"",Q138+(11-R138)+S138)</f>
-        <v/>
-      </c>
-      <c r="U138" s="85" t="n"/>
-      <c r="V138" s="86" t="n"/>
-      <c r="W138" s="87">
-        <f>IF(AND(P138="◎ 候補リスト",U138&lt;&gt;"ボツ",U138&lt;&gt;"制作済み",T138&lt;&gt;"",OR('②候補ランキング'!$C$5="すべて",B138='②候補ランキング'!$C$5)),IF('②候補ランキング'!$C$4="ワクワク",Q138,IF('②候補ランキング'!$C$4="手軽さ",11-R138,IF('②候補ランキング'!$C$4="確信度",S138,T138)))*1000+T138+(1000-A138)/10000,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="139" ht="18" customHeight="1" s="35">
-      <c r="A139" s="84">
-        <f>IF(C139="","",ROW()-5)</f>
-        <v/>
-      </c>
-      <c r="B139" s="85" t="n"/>
-      <c r="C139" s="86" t="n"/>
-      <c r="D139" s="86" t="n"/>
-      <c r="E139" s="85" t="n"/>
-      <c r="F139" s="86" t="n"/>
-      <c r="G139" s="86" t="n"/>
-      <c r="H139" s="86" t="n"/>
-      <c r="I139" s="86" t="n"/>
-      <c r="J139" s="85" t="n"/>
-      <c r="K139" s="85" t="n"/>
-      <c r="L139" s="85" t="n"/>
-      <c r="M139" s="85" t="n"/>
-      <c r="N139" s="85" t="n"/>
-      <c r="O139" s="85" t="n"/>
-      <c r="P139" s="84">
-        <f>IF(C139="","",IF(OR(E139="",E139="未検証"),"① STEP1待ち",IF(E139="不通過","✕ STEP1不通過",IF(OR(G139="",H139=""),"② STEP2-3 未記入",IF(COUNTIF(J139:O139,"×")&gt;0,"✕ ボツ候補",IF(COUNTA(J139:O139)&lt;6,"③ STEP4 審査待ち",IF(COUNTIF(J139:O139,"△")&gt;0,"△ 修正して再審査","◎ 候補リスト")))))))</f>
-        <v/>
-      </c>
-      <c r="Q139" s="85" t="n"/>
-      <c r="R139" s="85" t="n"/>
-      <c r="S139" s="85" t="n"/>
-      <c r="T139" s="84">
-        <f>IF(COUNT(Q139:S139)&lt;3,"",Q139+(11-R139)+S139)</f>
-        <v/>
-      </c>
-      <c r="U139" s="85" t="n"/>
-      <c r="V139" s="86" t="n"/>
-      <c r="W139" s="87">
-        <f>IF(AND(P139="◎ 候補リスト",U139&lt;&gt;"ボツ",U139&lt;&gt;"制作済み",T139&lt;&gt;"",OR('②候補ランキング'!$C$5="すべて",B139='②候補ランキング'!$C$5)),IF('②候補ランキング'!$C$4="ワクワク",Q139,IF('②候補ランキング'!$C$4="手軽さ",11-R139,IF('②候補ランキング'!$C$4="確信度",S139,T139)))*1000+T139+(1000-A139)/10000,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="140" ht="18" customHeight="1" s="35">
-      <c r="A140" s="84">
-        <f>IF(C140="","",ROW()-5)</f>
-        <v/>
-      </c>
-      <c r="B140" s="85" t="n"/>
-      <c r="C140" s="86" t="n"/>
-      <c r="D140" s="86" t="n"/>
-      <c r="E140" s="85" t="n"/>
-      <c r="F140" s="86" t="n"/>
-      <c r="G140" s="86" t="n"/>
-      <c r="H140" s="86" t="n"/>
-      <c r="I140" s="86" t="n"/>
-      <c r="J140" s="85" t="n"/>
-      <c r="K140" s="85" t="n"/>
-      <c r="L140" s="85" t="n"/>
-      <c r="M140" s="85" t="n"/>
-      <c r="N140" s="85" t="n"/>
-      <c r="O140" s="85" t="n"/>
-      <c r="P140" s="84">
-        <f>IF(C140="","",IF(OR(E140="",E140="未検証"),"① STEP1待ち",IF(E140="不通過","✕ STEP1不通過",IF(OR(G140="",H140=""),"② STEP2-3 未記入",IF(COUNTIF(J140:O140,"×")&gt;0,"✕ ボツ候補",IF(COUNTA(J140:O140)&lt;6,"③ STEP4 審査待ち",IF(COUNTIF(J140:O140,"△")&gt;0,"△ 修正して再審査","◎ 候補リスト")))))))</f>
-        <v/>
-      </c>
-      <c r="Q140" s="85" t="n"/>
-      <c r="R140" s="85" t="n"/>
-      <c r="S140" s="85" t="n"/>
-      <c r="T140" s="84">
-        <f>IF(COUNT(Q140:S140)&lt;3,"",Q140+(11-R140)+S140)</f>
-        <v/>
-      </c>
-      <c r="U140" s="85" t="n"/>
-      <c r="V140" s="86" t="n"/>
-      <c r="W140" s="87">
-        <f>IF(AND(P140="◎ 候補リスト",U140&lt;&gt;"ボツ",U140&lt;&gt;"制作済み",T140&lt;&gt;"",OR('②候補ランキング'!$C$5="すべて",B140='②候補ランキング'!$C$5)),IF('②候補ランキング'!$C$4="ワクワク",Q140,IF('②候補ランキング'!$C$4="手軽さ",11-R140,IF('②候補ランキング'!$C$4="確信度",S140,T140)))*1000+T140+(1000-A140)/10000,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="141" ht="18" customHeight="1" s="35">
-      <c r="A141" s="84">
-        <f>IF(C141="","",ROW()-5)</f>
-        <v/>
-      </c>
-      <c r="B141" s="85" t="n"/>
-      <c r="C141" s="86" t="n"/>
-      <c r="D141" s="86" t="n"/>
-      <c r="E141" s="85" t="n"/>
-      <c r="F141" s="86" t="n"/>
-      <c r="G141" s="86" t="n"/>
-      <c r="H141" s="86" t="n"/>
-      <c r="I141" s="86" t="n"/>
-      <c r="J141" s="85" t="n"/>
-      <c r="K141" s="85" t="n"/>
-      <c r="L141" s="85" t="n"/>
-      <c r="M141" s="85" t="n"/>
-      <c r="N141" s="85" t="n"/>
-      <c r="O141" s="85" t="n"/>
-      <c r="P141" s="84">
-        <f>IF(C141="","",IF(OR(E141="",E141="未検証"),"① STEP1待ち",IF(E141="不通過","✕ STEP1不通過",IF(OR(G141="",H141=""),"② STEP2-3 未記入",IF(COUNTIF(J141:O141,"×")&gt;0,"✕ ボツ候補",IF(COUNTA(J141:O141)&lt;6,"③ STEP4 審査待ち",IF(COUNTIF(J141:O141,"△")&gt;0,"△ 修正して再審査","◎ 候補リスト")))))))</f>
-        <v/>
-      </c>
-      <c r="Q141" s="85" t="n"/>
-      <c r="R141" s="85" t="n"/>
-      <c r="S141" s="85" t="n"/>
-      <c r="T141" s="84">
-        <f>IF(COUNT(Q141:S141)&lt;3,"",Q141+(11-R141)+S141)</f>
-        <v/>
-      </c>
-      <c r="U141" s="85" t="n"/>
-      <c r="V141" s="86" t="n"/>
-      <c r="W141" s="87">
-        <f>IF(AND(P141="◎ 候補リスト",U141&lt;&gt;"ボツ",U141&lt;&gt;"制作済み",T141&lt;&gt;"",OR('②候補ランキング'!$C$5="すべて",B141='②候補ランキング'!$C$5)),IF('②候補ランキング'!$C$4="ワクワク",Q141,IF('②候補ランキング'!$C$4="手軽さ",11-R141,IF('②候補ランキング'!$C$4="確信度",S141,T141)))*1000+T141+(1000-A141)/10000,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="142" ht="18" customHeight="1" s="35">
-      <c r="A142" s="84">
-        <f>IF(C142="","",ROW()-5)</f>
-        <v/>
-      </c>
-      <c r="B142" s="85" t="n"/>
-      <c r="C142" s="86" t="n"/>
-      <c r="D142" s="86" t="n"/>
-      <c r="E142" s="85" t="n"/>
-      <c r="F142" s="86" t="n"/>
-      <c r="G142" s="86" t="n"/>
-      <c r="H142" s="86" t="n"/>
-      <c r="I142" s="86" t="n"/>
-      <c r="J142" s="85" t="n"/>
-      <c r="K142" s="85" t="n"/>
-      <c r="L142" s="85" t="n"/>
-      <c r="M142" s="85" t="n"/>
-      <c r="N142" s="85" t="n"/>
-      <c r="O142" s="85" t="n"/>
-      <c r="P142" s="84">
-        <f>IF(C142="","",IF(OR(E142="",E142="未検証"),"① STEP1待ち",IF(E142="不通過","✕ STEP1不通過",IF(OR(G142="",H142=""),"② STEP2-3 未記入",IF(COUNTIF(J142:O142,"×")&gt;0,"✕ ボツ候補",IF(COUNTA(J142:O142)&lt;6,"③ STEP4 審査待ち",IF(COUNTIF(J142:O142,"△")&gt;0,"△ 修正して再審査","◎ 候補リスト")))))))</f>
-        <v/>
-      </c>
-      <c r="Q142" s="85" t="n"/>
-      <c r="R142" s="85" t="n"/>
-      <c r="S142" s="85" t="n"/>
-      <c r="T142" s="84">
-        <f>IF(COUNT(Q142:S142)&lt;3,"",Q142+(11-R142)+S142)</f>
-        <v/>
-      </c>
-      <c r="U142" s="85" t="n"/>
-      <c r="V142" s="86" t="n"/>
-      <c r="W142" s="87">
-        <f>IF(AND(P142="◎ 候補リスト",U142&lt;&gt;"ボツ",U142&lt;&gt;"制作済み",T142&lt;&gt;"",OR('②候補ランキング'!$C$5="すべて",B142='②候補ランキング'!$C$5)),IF('②候補ランキング'!$C$4="ワクワク",Q142,IF('②候補ランキング'!$C$4="手軽さ",11-R142,IF('②候補ランキング'!$C$4="確信度",S142,T142)))*1000+T142+(1000-A142)/10000,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="143" ht="18" customHeight="1" s="35">
-      <c r="A143" s="84">
-        <f>IF(C143="","",ROW()-5)</f>
-        <v/>
-      </c>
-      <c r="B143" s="85" t="n"/>
-      <c r="C143" s="86" t="n"/>
-      <c r="D143" s="86" t="n"/>
-      <c r="E143" s="85" t="n"/>
-      <c r="F143" s="86" t="n"/>
-      <c r="G143" s="86" t="n"/>
-      <c r="H143" s="86" t="n"/>
-      <c r="I143" s="86" t="n"/>
-      <c r="J143" s="85" t="n"/>
-      <c r="K143" s="85" t="n"/>
-      <c r="L143" s="85" t="n"/>
-      <c r="M143" s="85" t="n"/>
-      <c r="N143" s="85" t="n"/>
-      <c r="O143" s="85" t="n"/>
-      <c r="P143" s="84">
-        <f>IF(C143="","",IF(OR(E143="",E143="未検証"),"① STEP1待ち",IF(E143="不通過","✕ STEP1不通過",IF(OR(G143="",H143=""),"② STEP2-3 未記入",IF(COUNTIF(J143:O143,"×")&gt;0,"✕ ボツ候補",IF(COUNTA(J143:O143)&lt;6,"③ STEP4 審査待ち",IF(COUNTIF(J143:O143,"△")&gt;0,"△ 修正して再審査","◎ 候補リスト")))))))</f>
-        <v/>
-      </c>
-      <c r="Q143" s="85" t="n"/>
-      <c r="R143" s="85" t="n"/>
-      <c r="S143" s="85" t="n"/>
-      <c r="T143" s="84">
-        <f>IF(COUNT(Q143:S143)&lt;3,"",Q143+(11-R143)+S143)</f>
-        <v/>
-      </c>
-      <c r="U143" s="85" t="n"/>
-      <c r="V143" s="86" t="n"/>
-      <c r="W143" s="87">
-        <f>IF(AND(P143="◎ 候補リスト",U143&lt;&gt;"ボツ",U143&lt;&gt;"制作済み",T143&lt;&gt;"",OR('②候補ランキング'!$C$5="すべて",B143='②候補ランキング'!$C$5)),IF('②候補ランキング'!$C$4="ワクワク",Q143,IF('②候補ランキング'!$C$4="手軽さ",11-R143,IF('②候補ランキング'!$C$4="確信度",S143,T143)))*1000+T143+(1000-A143)/10000,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="144" ht="18" customHeight="1" s="35">
-      <c r="A144" s="84">
-        <f>IF(C144="","",ROW()-5)</f>
-        <v/>
-      </c>
-      <c r="B144" s="85" t="n"/>
-      <c r="C144" s="86" t="n"/>
-      <c r="D144" s="86" t="n"/>
-      <c r="E144" s="85" t="n"/>
-      <c r="F144" s="86" t="n"/>
-      <c r="G144" s="86" t="n"/>
-      <c r="H144" s="86" t="n"/>
-      <c r="I144" s="86" t="n"/>
-      <c r="J144" s="85" t="n"/>
-      <c r="K144" s="85" t="n"/>
-      <c r="L144" s="85" t="n"/>
-      <c r="M144" s="85" t="n"/>
-      <c r="N144" s="85" t="n"/>
-      <c r="O144" s="85" t="n"/>
-      <c r="P144" s="84">
-        <f>IF(C144="","",IF(OR(E144="",E144="未検証"),"① STEP1待ち",IF(E144="不通過","✕ STEP1不通過",IF(OR(G144="",H144=""),"② STEP2-3 未記入",IF(COUNTIF(J144:O144,"×")&gt;0,"✕ ボツ候補",IF(COUNTA(J144:O144)&lt;6,"③ STEP4 審査待ち",IF(COUNTIF(J144:O144,"△")&gt;0,"△ 修正して再審査","◎ 候補リスト")))))))</f>
-        <v/>
-      </c>
-      <c r="Q144" s="85" t="n"/>
-      <c r="R144" s="85" t="n"/>
-      <c r="S144" s="85" t="n"/>
-      <c r="T144" s="84">
-        <f>IF(COUNT(Q144:S144)&lt;3,"",Q144+(11-R144)+S144)</f>
-        <v/>
-      </c>
-      <c r="U144" s="85" t="n"/>
-      <c r="V144" s="86" t="n"/>
-      <c r="W144" s="87">
-        <f>IF(AND(P144="◎ 候補リスト",U144&lt;&gt;"ボツ",U144&lt;&gt;"制作済み",T144&lt;&gt;"",OR('②候補ランキング'!$C$5="すべて",B144='②候補ランキング'!$C$5)),IF('②候補ランキング'!$C$4="ワクワク",Q144,IF('②候補ランキング'!$C$4="手軽さ",11-R144,IF('②候補ランキング'!$C$4="確信度",S144,T144)))*1000+T144+(1000-A144)/10000,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="145" ht="18" customHeight="1" s="35">
-      <c r="A145" s="84">
-        <f>IF(C145="","",ROW()-5)</f>
-        <v/>
-      </c>
-      <c r="B145" s="85" t="n"/>
-      <c r="C145" s="86" t="n"/>
-      <c r="D145" s="86" t="n"/>
-      <c r="E145" s="85" t="n"/>
-      <c r="F145" s="86" t="n"/>
-      <c r="G145" s="86" t="n"/>
-      <c r="H145" s="86" t="n"/>
-      <c r="I145" s="86" t="n"/>
-      <c r="J145" s="85" t="n"/>
-      <c r="K145" s="85" t="n"/>
-      <c r="L145" s="85" t="n"/>
-      <c r="M145" s="85" t="n"/>
-      <c r="N145" s="85" t="n"/>
-      <c r="O145" s="85" t="n"/>
-      <c r="P145" s="84">
-        <f>IF(C145="","",IF(OR(E145="",E145="未検証"),"① STEP1待ち",IF(E145="不通過","✕ STEP1不通過",IF(OR(G145="",H145=""),"② STEP2-3 未記入",IF(COUNTIF(J145:O145,"×")&gt;0,"✕ ボツ候補",IF(COUNTA(J145:O145)&lt;6,"③ STEP4 審査待ち",IF(COUNTIF(J145:O145,"△")&gt;0,"△ 修正して再審査","◎ 候補リスト")))))))</f>
-        <v/>
-      </c>
-      <c r="Q145" s="85" t="n"/>
-      <c r="R145" s="85" t="n"/>
-      <c r="S145" s="85" t="n"/>
-      <c r="T145" s="84">
-        <f>IF(COUNT(Q145:S145)&lt;3,"",Q145+(11-R145)+S145)</f>
-        <v/>
-      </c>
-      <c r="U145" s="85" t="n"/>
-      <c r="V145" s="86" t="n"/>
-      <c r="W145" s="87">
-        <f>IF(AND(P145="◎ 候補リスト",U145&lt;&gt;"ボツ",U145&lt;&gt;"制作済み",T145&lt;&gt;"",OR('②候補ランキング'!$C$5="すべて",B145='②候補ランキング'!$C$5)),IF('②候補ランキング'!$C$4="ワクワク",Q145,IF('②候補ランキング'!$C$4="手軽さ",11-R145,IF('②候補ランキング'!$C$4="確信度",S145,T145)))*1000+T145+(1000-A145)/10000,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="146" ht="18" customHeight="1" s="35">
-      <c r="A146" s="84">
-        <f>IF(C146="","",ROW()-5)</f>
-        <v/>
-      </c>
-      <c r="B146" s="85" t="n"/>
-      <c r="C146" s="86" t="n"/>
-      <c r="D146" s="86" t="n"/>
-      <c r="E146" s="85" t="n"/>
-      <c r="F146" s="86" t="n"/>
-      <c r="G146" s="86" t="n"/>
-      <c r="H146" s="86" t="n"/>
-      <c r="I146" s="86" t="n"/>
-      <c r="J146" s="85" t="n"/>
-      <c r="K146" s="85" t="n"/>
-      <c r="L146" s="85" t="n"/>
-      <c r="M146" s="85" t="n"/>
-      <c r="N146" s="85" t="n"/>
-      <c r="O146" s="85" t="n"/>
-      <c r="P146" s="84">
-        <f>IF(C146="","",IF(OR(E146="",E146="未検証"),"① STEP1待ち",IF(E146="不通過","✕ STEP1不通過",IF(OR(G146="",H146=""),"② STEP2-3 未記入",IF(COUNTIF(J146:O146,"×")&gt;0,"✕ ボツ候補",IF(COUNTA(J146:O146)&lt;6,"③ STEP4 審査待ち",IF(COUNTIF(J146:O146,"△")&gt;0,"△ 修正して再審査","◎ 候補リスト")))))))</f>
-        <v/>
-      </c>
-      <c r="Q146" s="85" t="n"/>
-      <c r="R146" s="85" t="n"/>
-      <c r="S146" s="85" t="n"/>
-      <c r="T146" s="84">
-        <f>IF(COUNT(Q146:S146)&lt;3,"",Q146+(11-R146)+S146)</f>
-        <v/>
-      </c>
-      <c r="U146" s="85" t="n"/>
-      <c r="V146" s="86" t="n"/>
-      <c r="W146" s="87">
-        <f>IF(AND(P146="◎ 候補リスト",U146&lt;&gt;"ボツ",U146&lt;&gt;"制作済み",T146&lt;&gt;"",OR('②候補ランキング'!$C$5="すべて",B146='②候補ランキング'!$C$5)),IF('②候補ランキング'!$C$4="ワクワク",Q146,IF('②候補ランキング'!$C$4="手軽さ",11-R146,IF('②候補ランキング'!$C$4="確信度",S146,T146)))*1000+T146+(1000-A146)/10000,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="147" ht="18" customHeight="1" s="35">
-      <c r="A147" s="84">
-        <f>IF(C147="","",ROW()-5)</f>
-        <v/>
-      </c>
-      <c r="B147" s="85" t="n"/>
-      <c r="C147" s="86" t="n"/>
-      <c r="D147" s="86" t="n"/>
-      <c r="E147" s="85" t="n"/>
-      <c r="F147" s="86" t="n"/>
-      <c r="G147" s="86" t="n"/>
-      <c r="H147" s="86" t="n"/>
-      <c r="I147" s="86" t="n"/>
-      <c r="J147" s="85" t="n"/>
-      <c r="K147" s="85" t="n"/>
-      <c r="L147" s="85" t="n"/>
-      <c r="M147" s="85" t="n"/>
-      <c r="N147" s="85" t="n"/>
-      <c r="O147" s="85" t="n"/>
-      <c r="P147" s="84">
-        <f>IF(C147="","",IF(OR(E147="",E147="未検証"),"① STEP1待ち",IF(E147="不通過","✕ STEP1不通過",IF(OR(G147="",H147=""),"② STEP2-3 未記入",IF(COUNTIF(J147:O147,"×")&gt;0,"✕ ボツ候補",IF(COUNTA(J147:O147)&lt;6,"③ STEP4 審査待ち",IF(COUNTIF(J147:O147,"△")&gt;0,"△ 修正して再審査","◎ 候補リスト")))))))</f>
-        <v/>
-      </c>
-      <c r="Q147" s="85" t="n"/>
-      <c r="R147" s="85" t="n"/>
-      <c r="S147" s="85" t="n"/>
-      <c r="T147" s="84">
-        <f>IF(COUNT(Q147:S147)&lt;3,"",Q147+(11-R147)+S147)</f>
-        <v/>
-      </c>
-      <c r="U147" s="85" t="n"/>
-      <c r="V147" s="86" t="n"/>
-      <c r="W147" s="87">
-        <f>IF(AND(P147="◎ 候補リスト",U147&lt;&gt;"ボツ",U147&lt;&gt;"制作済み",T147&lt;&gt;"",OR('②候補ランキング'!$C$5="すべて",B147='②候補ランキング'!$C$5)),IF('②候補ランキング'!$C$4="ワクワク",Q147,IF('②候補ランキング'!$C$4="手軽さ",11-R147,IF('②候補ランキング'!$C$4="確信度",S147,T147)))*1000+T147+(1000-A147)/10000,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="148" ht="18" customHeight="1" s="35">
-      <c r="A148" s="84">
-        <f>IF(C148="","",ROW()-5)</f>
-        <v/>
-      </c>
-      <c r="B148" s="85" t="n"/>
-      <c r="C148" s="86" t="n"/>
-      <c r="D148" s="86" t="n"/>
-      <c r="E148" s="85" t="n"/>
-      <c r="F148" s="86" t="n"/>
-      <c r="G148" s="86" t="n"/>
-      <c r="H148" s="86" t="n"/>
-      <c r="I148" s="86" t="n"/>
-      <c r="J148" s="85" t="n"/>
-      <c r="K148" s="85" t="n"/>
-      <c r="L148" s="85" t="n"/>
-      <c r="M148" s="85" t="n"/>
-      <c r="N148" s="85" t="n"/>
-      <c r="O148" s="85" t="n"/>
-      <c r="P148" s="84">
-        <f>IF(C148="","",IF(OR(E148="",E148="未検証"),"① STEP1待ち",IF(E148="不通過","✕ STEP1不通過",IF(OR(G148="",H148=""),"② STEP2-3 未記入",IF(COUNTIF(J148:O148,"×")&gt;0,"✕ ボツ候補",IF(COUNTA(J148:O148)&lt;6,"③ STEP4 審査待ち",IF(COUNTIF(J148:O148,"△")&gt;0,"△ 修正して再審査","◎ 候補リスト")))))))</f>
-        <v/>
-      </c>
-      <c r="Q148" s="85" t="n"/>
-      <c r="R148" s="85" t="n"/>
-      <c r="S148" s="85" t="n"/>
-      <c r="T148" s="84">
-        <f>IF(COUNT(Q148:S148)&lt;3,"",Q148+(11-R148)+S148)</f>
-        <v/>
-      </c>
-      <c r="U148" s="85" t="n"/>
-      <c r="V148" s="86" t="n"/>
-      <c r="W148" s="87">
-        <f>IF(AND(P148="◎ 候補リスト",U148&lt;&gt;"ボツ",U148&lt;&gt;"制作済み",T148&lt;&gt;"",OR('②候補ランキング'!$C$5="すべて",B148='②候補ランキング'!$C$5)),IF('②候補ランキング'!$C$4="ワクワク",Q148,IF('②候補ランキング'!$C$4="手軽さ",11-R148,IF('②候補ランキング'!$C$4="確信度",S148,T148)))*1000+T148+(1000-A148)/10000,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="149" ht="18" customHeight="1" s="35">
-      <c r="A149" s="84">
-        <f>IF(C149="","",ROW()-5)</f>
-        <v/>
-      </c>
-      <c r="B149" s="85" t="n"/>
-      <c r="C149" s="86" t="n"/>
-      <c r="D149" s="86" t="n"/>
-      <c r="E149" s="85" t="n"/>
-      <c r="F149" s="86" t="n"/>
-      <c r="G149" s="86" t="n"/>
-      <c r="H149" s="86" t="n"/>
-      <c r="I149" s="86" t="n"/>
-      <c r="J149" s="85" t="n"/>
-      <c r="K149" s="85" t="n"/>
-      <c r="L149" s="85" t="n"/>
-      <c r="M149" s="85" t="n"/>
-      <c r="N149" s="85" t="n"/>
-      <c r="O149" s="85" t="n"/>
-      <c r="P149" s="84">
-        <f>IF(C149="","",IF(OR(E149="",E149="未検証"),"① STEP1待ち",IF(E149="不通過","✕ STEP1不通過",IF(OR(G149="",H149=""),"② STEP2-3 未記入",IF(COUNTIF(J149:O149,"×")&gt;0,"✕ ボツ候補",IF(COUNTA(J149:O149)&lt;6,"③ STEP4 審査待ち",IF(COUNTIF(J149:O149,"△")&gt;0,"△ 修正して再審査","◎ 候補リスト")))))))</f>
-        <v/>
-      </c>
-      <c r="Q149" s="85" t="n"/>
-      <c r="R149" s="85" t="n"/>
-      <c r="S149" s="85" t="n"/>
-      <c r="T149" s="84">
-        <f>IF(COUNT(Q149:S149)&lt;3,"",Q149+(11-R149)+S149)</f>
-        <v/>
-      </c>
-      <c r="U149" s="85" t="n"/>
-      <c r="V149" s="86" t="n"/>
-      <c r="W149" s="87">
-        <f>IF(AND(P149="◎ 候補リスト",U149&lt;&gt;"ボツ",U149&lt;&gt;"制作済み",T149&lt;&gt;"",OR('②候補ランキング'!$C$5="すべて",B149='②候補ランキング'!$C$5)),IF('②候補ランキング'!$C$4="ワクワク",Q149,IF('②候補ランキング'!$C$4="手軽さ",11-R149,IF('②候補ランキング'!$C$4="確信度",S149,T149)))*1000+T149+(1000-A149)/10000,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="150" ht="18" customHeight="1" s="35">
-      <c r="A150" s="84">
-        <f>IF(C150="","",ROW()-5)</f>
-        <v/>
-      </c>
-      <c r="B150" s="85" t="n"/>
-      <c r="C150" s="86" t="n"/>
-      <c r="D150" s="86" t="n"/>
-      <c r="E150" s="85" t="n"/>
-      <c r="F150" s="86" t="n"/>
-      <c r="G150" s="86" t="n"/>
-      <c r="H150" s="86" t="n"/>
-      <c r="I150" s="86" t="n"/>
-      <c r="J150" s="85" t="n"/>
-      <c r="K150" s="85" t="n"/>
-      <c r="L150" s="85" t="n"/>
-      <c r="M150" s="85" t="n"/>
-      <c r="N150" s="85" t="n"/>
-      <c r="O150" s="85" t="n"/>
-      <c r="P150" s="84">
-        <f>IF(C150="","",IF(OR(E150="",E150="未検証"),"① STEP1待ち",IF(E150="不通過","✕ STEP1不通過",IF(OR(G150="",H150=""),"② STEP2-3 未記入",IF(COUNTIF(J150:O150,"×")&gt;0,"✕ ボツ候補",IF(COUNTA(J150:O150)&lt;6,"③ STEP4 審査待ち",IF(COUNTIF(J150:O150,"△")&gt;0,"△ 修正して再審査","◎ 候補リスト")))))))</f>
-        <v/>
-      </c>
-      <c r="Q150" s="85" t="n"/>
-      <c r="R150" s="85" t="n"/>
-      <c r="S150" s="85" t="n"/>
-      <c r="T150" s="84">
-        <f>IF(COUNT(Q150:S150)&lt;3,"",Q150+(11-R150)+S150)</f>
-        <v/>
-      </c>
-      <c r="U150" s="85" t="n"/>
-      <c r="V150" s="86" t="n"/>
-      <c r="W150" s="87">
-        <f>IF(AND(P150="◎ 候補リスト",U150&lt;&gt;"ボツ",U150&lt;&gt;"制作済み",T150&lt;&gt;"",OR('②候補ランキング'!$C$5="すべて",B150='②候補ランキング'!$C$5)),IF('②候補ランキング'!$C$4="ワクワク",Q150,IF('②候補ランキング'!$C$4="手軽さ",11-R150,IF('②候補ランキング'!$C$4="確信度",S150,T150)))*1000+T150+(1000-A150)/10000,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="151" ht="18" customHeight="1" s="35">
-      <c r="A151" s="84">
-        <f>IF(C151="","",ROW()-5)</f>
-        <v/>
-      </c>
-      <c r="B151" s="85" t="n"/>
-      <c r="C151" s="86" t="n"/>
-      <c r="D151" s="86" t="n"/>
-      <c r="E151" s="85" t="n"/>
-      <c r="F151" s="86" t="n"/>
-      <c r="G151" s="86" t="n"/>
-      <c r="H151" s="86" t="n"/>
-      <c r="I151" s="86" t="n"/>
-      <c r="J151" s="85" t="n"/>
-      <c r="K151" s="85" t="n"/>
-      <c r="L151" s="85" t="n"/>
-      <c r="M151" s="85" t="n"/>
-      <c r="N151" s="85" t="n"/>
-      <c r="O151" s="85" t="n"/>
-      <c r="P151" s="84">
-        <f>IF(C151="","",IF(OR(E151="",E151="未検証"),"① STEP1待ち",IF(E151="不通過","✕ STEP1不通過",IF(OR(G151="",H151=""),"② STEP2-3 未記入",IF(COUNTIF(J151:O151,"×")&gt;0,"✕ ボツ候補",IF(COUNTA(J151:O151)&lt;6,"③ STEP4 審査待ち",IF(COUNTIF(J151:O151,"△")&gt;0,"△ 修正して再審査","◎ 候補リスト")))))))</f>
-        <v/>
-      </c>
-      <c r="Q151" s="85" t="n"/>
-      <c r="R151" s="85" t="n"/>
-      <c r="S151" s="85" t="n"/>
-      <c r="T151" s="84">
-        <f>IF(COUNT(Q151:S151)&lt;3,"",Q151+(11-R151)+S151)</f>
-        <v/>
-      </c>
-      <c r="U151" s="85" t="n"/>
-      <c r="V151" s="86" t="n"/>
-      <c r="W151" s="87">
-        <f>IF(AND(P151="◎ 候補リスト",U151&lt;&gt;"ボツ",U151&lt;&gt;"制作済み",T151&lt;&gt;"",OR('②候補ランキング'!$C$5="すべて",B151='②候補ランキング'!$C$5)),IF('②候補ランキング'!$C$4="ワクワク",Q151,IF('②候補ランキング'!$C$4="手軽さ",11-R151,IF('②候補ランキング'!$C$4="確信度",S151,T151)))*1000+T151+(1000-A151)/10000,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="152" ht="18" customHeight="1" s="35">
-      <c r="A152" s="84">
-        <f>IF(C152="","",ROW()-5)</f>
-        <v/>
-      </c>
-      <c r="B152" s="85" t="n"/>
-      <c r="C152" s="86" t="n"/>
-      <c r="D152" s="86" t="n"/>
-      <c r="E152" s="85" t="n"/>
-      <c r="F152" s="86" t="n"/>
-      <c r="G152" s="86" t="n"/>
-      <c r="H152" s="86" t="n"/>
-      <c r="I152" s="86" t="n"/>
-      <c r="J152" s="85" t="n"/>
-      <c r="K152" s="85" t="n"/>
-      <c r="L152" s="85" t="n"/>
-      <c r="M152" s="85" t="n"/>
-      <c r="N152" s="85" t="n"/>
-      <c r="O152" s="85" t="n"/>
-      <c r="P152" s="84">
-        <f>IF(C152="","",IF(OR(E152="",E152="未検証"),"① STEP1待ち",IF(E152="不通過","✕ STEP1不通過",IF(OR(G152="",H152=""),"② STEP2-3 未記入",IF(COUNTIF(J152:O152,"×")&gt;0,"✕ ボツ候補",IF(COUNTA(J152:O152)&lt;6,"③ STEP4 審査待ち",IF(COUNTIF(J152:O152,"△")&gt;0,"△ 修正して再審査","◎ 候補リスト")))))))</f>
-        <v/>
-      </c>
-      <c r="Q152" s="85" t="n"/>
-      <c r="R152" s="85" t="n"/>
-      <c r="S152" s="85" t="n"/>
-      <c r="T152" s="84">
-        <f>IF(COUNT(Q152:S152)&lt;3,"",Q152+(11-R152)+S152)</f>
-        <v/>
-      </c>
-      <c r="U152" s="85" t="n"/>
-      <c r="V152" s="86" t="n"/>
-      <c r="W152" s="87">
-        <f>IF(AND(P152="◎ 候補リスト",U152&lt;&gt;"ボツ",U152&lt;&gt;"制作済み",T152&lt;&gt;"",OR('②候補ランキング'!$C$5="すべて",B152='②候補ランキング'!$C$5)),IF('②候補ランキング'!$C$4="ワクワク",Q152,IF('②候補ランキング'!$C$4="手軽さ",11-R152,IF('②候補ランキング'!$C$4="確信度",S152,T152)))*1000+T152+(1000-A152)/10000,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="153" ht="18" customHeight="1" s="35">
-      <c r="A153" s="84">
-        <f>IF(C153="","",ROW()-5)</f>
-        <v/>
-      </c>
-      <c r="B153" s="85" t="n"/>
-      <c r="C153" s="86" t="n"/>
-      <c r="D153" s="86" t="n"/>
-      <c r="E153" s="85" t="n"/>
-      <c r="F153" s="86" t="n"/>
-      <c r="G153" s="86" t="n"/>
-      <c r="H153" s="86" t="n"/>
-      <c r="I153" s="86" t="n"/>
-      <c r="J153" s="85" t="n"/>
-      <c r="K153" s="85" t="n"/>
-      <c r="L153" s="85" t="n"/>
-      <c r="M153" s="85" t="n"/>
-      <c r="N153" s="85" t="n"/>
-      <c r="O153" s="85" t="n"/>
-      <c r="P153" s="84">
-        <f>IF(C153="","",IF(OR(E153="",E153="未検証"),"① STEP1待ち",IF(E153="不通過","✕ STEP1不通過",IF(OR(G153="",H153=""),"② STEP2-3 未記入",IF(COUNTIF(J153:O153,"×")&gt;0,"✕ ボツ候補",IF(COUNTA(J153:O153)&lt;6,"③ STEP4 審査待ち",IF(COUNTIF(J153:O153,"△")&gt;0,"△ 修正して再審査","◎ 候補リスト")))))))</f>
-        <v/>
-      </c>
-      <c r="Q153" s="85" t="n"/>
-      <c r="R153" s="85" t="n"/>
-      <c r="S153" s="85" t="n"/>
-      <c r="T153" s="84">
-        <f>IF(COUNT(Q153:S153)&lt;3,"",Q153+(11-R153)+S153)</f>
-        <v/>
-      </c>
-      <c r="U153" s="85" t="n"/>
-      <c r="V153" s="86" t="n"/>
-      <c r="W153" s="87">
-        <f>IF(AND(P153="◎ 候補リスト",U153&lt;&gt;"ボツ",U153&lt;&gt;"制作済み",T153&lt;&gt;"",OR('②候補ランキング'!$C$5="すべて",B153='②候補ランキング'!$C$5)),IF('②候補ランキング'!$C$4="ワクワク",Q153,IF('②候補ランキング'!$C$4="手軽さ",11-R153,IF('②候補ランキング'!$C$4="確信度",S153,T153)))*1000+T153+(1000-A153)/10000,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="154" ht="18" customHeight="1" s="35">
-      <c r="A154" s="84">
-        <f>IF(C154="","",ROW()-5)</f>
-        <v/>
-      </c>
-      <c r="B154" s="85" t="n"/>
-      <c r="C154" s="86" t="n"/>
-      <c r="D154" s="86" t="n"/>
-      <c r="E154" s="85" t="n"/>
-      <c r="F154" s="86" t="n"/>
-      <c r="G154" s="86" t="n"/>
-      <c r="H154" s="86" t="n"/>
-      <c r="I154" s="86" t="n"/>
-      <c r="J154" s="85" t="n"/>
-      <c r="K154" s="85" t="n"/>
-      <c r="L154" s="85" t="n"/>
-      <c r="M154" s="85" t="n"/>
-      <c r="N154" s="85" t="n"/>
-      <c r="O154" s="85" t="n"/>
-      <c r="P154" s="84">
-        <f>IF(C154="","",IF(OR(E154="",E154="未検証"),"① STEP1待ち",IF(E154="不通過","✕ STEP1不通過",IF(OR(G154="",H154=""),"② STEP2-3 未記入",IF(COUNTIF(J154:O154,"×")&gt;0,"✕ ボツ候補",IF(COUNTA(J154:O154)&lt;6,"③ STEP4 審査待ち",IF(COUNTIF(J154:O154,"△")&gt;0,"△ 修正して再審査","◎ 候補リスト")))))))</f>
-        <v/>
-      </c>
-      <c r="Q154" s="85" t="n"/>
-      <c r="R154" s="85" t="n"/>
-      <c r="S154" s="85" t="n"/>
-      <c r="T154" s="84">
-        <f>IF(COUNT(Q154:S154)&lt;3,"",Q154+(11-R154)+S154)</f>
-        <v/>
-      </c>
-      <c r="U154" s="85" t="n"/>
-      <c r="V154" s="86" t="n"/>
-      <c r="W154" s="87">
-        <f>IF(AND(P154="◎ 候補リスト",U154&lt;&gt;"ボツ",U154&lt;&gt;"制作済み",T154&lt;&gt;"",OR('②候補ランキング'!$C$5="すべて",B154='②候補ランキング'!$C$5)),IF('②候補ランキング'!$C$4="ワクワク",Q154,IF('②候補ランキング'!$C$4="手軽さ",11-R154,IF('②候補ランキング'!$C$4="確信度",S154,T154)))*1000+T154+(1000-A154)/10000,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="155" ht="18" customHeight="1" s="35">
-      <c r="A155" s="84">
-        <f>IF(C155="","",ROW()-5)</f>
-        <v/>
-      </c>
-      <c r="B155" s="85" t="n"/>
-      <c r="C155" s="86" t="n"/>
-      <c r="D155" s="86" t="n"/>
-      <c r="E155" s="85" t="n"/>
-      <c r="F155" s="86" t="n"/>
-      <c r="G155" s="86" t="n"/>
-      <c r="H155" s="86" t="n"/>
-      <c r="I155" s="86" t="n"/>
-      <c r="J155" s="85" t="n"/>
-      <c r="K155" s="85" t="n"/>
-      <c r="L155" s="85" t="n"/>
-      <c r="M155" s="85" t="n"/>
-      <c r="N155" s="85" t="n"/>
-      <c r="O155" s="85" t="n"/>
-      <c r="P155" s="84">
-        <f>IF(C155="","",IF(OR(E155="",E155="未検証"),"① STEP1待ち",IF(E155="不通過","✕ STEP1不通過",IF(OR(G155="",H155=""),"② STEP2-3 未記入",IF(COUNTIF(J155:O155,"×")&gt;0,"✕ ボツ候補",IF(COUNTA(J155:O155)&lt;6,"③ STEP4 審査待ち",IF(COUNTIF(J155:O155,"△")&gt;0,"△ 修正して再審査","◎ 候補リスト")))))))</f>
-        <v/>
-      </c>
-      <c r="Q155" s="85" t="n"/>
-      <c r="R155" s="85" t="n"/>
-      <c r="S155" s="85" t="n"/>
-      <c r="T155" s="84">
-        <f>IF(COUNT(Q155:S155)&lt;3,"",Q155+(11-R155)+S155)</f>
-        <v/>
-      </c>
-      <c r="U155" s="85" t="n"/>
-      <c r="V155" s="86" t="n"/>
-      <c r="W155" s="87">
-        <f>IF(AND(P155="◎ 候補リスト",U155&lt;&gt;"ボツ",U155&lt;&gt;"制作済み",T155&lt;&gt;"",OR('②候補ランキング'!$C$5="すべて",B155='②候補ランキング'!$C$5)),IF('②候補ランキング'!$C$4="ワクワク",Q155,IF('②候補ランキング'!$C$4="手軽さ",11-R155,IF('②候補ランキング'!$C$4="確信度",S155,T155)))*1000+T155+(1000-A155)/10000,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="156" ht="18" customHeight="1" s="35">
-      <c r="A156" s="84">
-        <f>IF(C156="","",ROW()-5)</f>
-        <v/>
-      </c>
-      <c r="B156" s="85" t="n"/>
-      <c r="C156" s="86" t="n"/>
-      <c r="D156" s="86" t="n"/>
-      <c r="E156" s="85" t="n"/>
-      <c r="F156" s="86" t="n"/>
-      <c r="G156" s="86" t="n"/>
-      <c r="H156" s="86" t="n"/>
-      <c r="I156" s="86" t="n"/>
-      <c r="J156" s="85" t="n"/>
-      <c r="K156" s="85" t="n"/>
-      <c r="L156" s="85" t="n"/>
-      <c r="M156" s="85" t="n"/>
-      <c r="N156" s="85" t="n"/>
-      <c r="O156" s="85" t="n"/>
-      <c r="P156" s="84">
-        <f>IF(C156="","",IF(OR(E156="",E156="未検証"),"① STEP1待ち",IF(E156="不通過","✕ STEP1不通過",IF(OR(G156="",H156=""),"② STEP2-3 未記入",IF(COUNTIF(J156:O156,"×")&gt;0,"✕ ボツ候補",IF(COUNTA(J156:O156)&lt;6,"③ STEP4 審査待ち",IF(COUNTIF(J156:O156,"△")&gt;0,"△ 修正して再審査","◎ 候補リスト")))))))</f>
-        <v/>
-      </c>
-      <c r="Q156" s="85" t="n"/>
-      <c r="R156" s="85" t="n"/>
-      <c r="S156" s="85" t="n"/>
-      <c r="T156" s="84">
-        <f>IF(COUNT(Q156:S156)&lt;3,"",Q156+(11-R156)+S156)</f>
-        <v/>
-      </c>
-      <c r="U156" s="85" t="n"/>
-      <c r="V156" s="86" t="n"/>
-      <c r="W156" s="87">
-        <f>IF(AND(P156="◎ 候補リスト",U156&lt;&gt;"ボツ",U156&lt;&gt;"制作済み",T156&lt;&gt;"",OR('②候補ランキング'!$C$5="すべて",B156='②候補ランキング'!$C$5)),IF('②候補ランキング'!$C$4="ワクワク",Q156,IF('②候補ランキング'!$C$4="手軽さ",11-R156,IF('②候補ランキング'!$C$4="確信度",S156,T156)))*1000+T156+(1000-A156)/10000,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="157" ht="18" customHeight="1" s="35">
-      <c r="A157" s="84">
-        <f>IF(C157="","",ROW()-5)</f>
-        <v/>
-      </c>
-      <c r="B157" s="85" t="n"/>
-      <c r="C157" s="86" t="n"/>
-      <c r="D157" s="86" t="n"/>
-      <c r="E157" s="85" t="n"/>
-      <c r="F157" s="86" t="n"/>
-      <c r="G157" s="86" t="n"/>
-      <c r="H157" s="86" t="n"/>
-      <c r="I157" s="86" t="n"/>
-      <c r="J157" s="85" t="n"/>
-      <c r="K157" s="85" t="n"/>
-      <c r="L157" s="85" t="n"/>
-      <c r="M157" s="85" t="n"/>
-      <c r="N157" s="85" t="n"/>
-      <c r="O157" s="85" t="n"/>
-      <c r="P157" s="84">
-        <f>IF(C157="","",IF(OR(E157="",E157="未検証"),"① STEP1待ち",IF(E157="不通過","✕ STEP1不通過",IF(OR(G157="",H157=""),"② STEP2-3 未記入",IF(COUNTIF(J157:O157,"×")&gt;0,"✕ ボツ候補",IF(COUNTA(J157:O157)&lt;6,"③ STEP4 審査待ち",IF(COUNTIF(J157:O157,"△")&gt;0,"△ 修正して再審査","◎ 候補リスト")))))))</f>
-        <v/>
-      </c>
-      <c r="Q157" s="85" t="n"/>
-      <c r="R157" s="85" t="n"/>
-      <c r="S157" s="85" t="n"/>
-      <c r="T157" s="84">
-        <f>IF(COUNT(Q157:S157)&lt;3,"",Q157+(11-R157)+S157)</f>
-        <v/>
-      </c>
-      <c r="U157" s="85" t="n"/>
-      <c r="V157" s="86" t="n"/>
-      <c r="W157" s="87">
-        <f>IF(AND(P157="◎ 候補リスト",U157&lt;&gt;"ボツ",U157&lt;&gt;"制作済み",T157&lt;&gt;"",OR('②候補ランキング'!$C$5="すべて",B157='②候補ランキング'!$C$5)),IF('②候補ランキング'!$C$4="ワクワク",Q157,IF('②候補ランキング'!$C$4="手軽さ",11-R157,IF('②候補ランキング'!$C$4="確信度",S157,T157)))*1000+T157+(1000-A157)/10000,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="158" ht="18" customHeight="1" s="35">
-      <c r="A158" s="84">
-        <f>IF(C158="","",ROW()-5)</f>
-        <v/>
-      </c>
-      <c r="B158" s="85" t="n"/>
-      <c r="C158" s="86" t="n"/>
-      <c r="D158" s="86" t="n"/>
-      <c r="E158" s="85" t="n"/>
-      <c r="F158" s="86" t="n"/>
-      <c r="G158" s="86" t="n"/>
-      <c r="H158" s="86" t="n"/>
-      <c r="I158" s="86" t="n"/>
-      <c r="J158" s="85" t="n"/>
-      <c r="K158" s="85" t="n"/>
-      <c r="L158" s="85" t="n"/>
-      <c r="M158" s="85" t="n"/>
-      <c r="N158" s="85" t="n"/>
-      <c r="O158" s="85" t="n"/>
-      <c r="P158" s="84">
-        <f>IF(C158="","",IF(OR(E158="",E158="未検証"),"① STEP1待ち",IF(E158="不通過","✕ STEP1不通過",IF(OR(G158="",H158=""),"② STEP2-3 未記入",IF(COUNTIF(J158:O158,"×")&gt;0,"✕ ボツ候補",IF(COUNTA(J158:O158)&lt;6,"③ STEP4 審査待ち",IF(COUNTIF(J158:O158,"△")&gt;0,"△ 修正して再審査","◎ 候補リスト")))))))</f>
-        <v/>
-      </c>
-      <c r="Q158" s="85" t="n"/>
-      <c r="R158" s="85" t="n"/>
-      <c r="S158" s="85" t="n"/>
-      <c r="T158" s="84">
-        <f>IF(COUNT(Q158:S158)&lt;3,"",Q158+(11-R158)+S158)</f>
-        <v/>
-      </c>
-      <c r="U158" s="85" t="n"/>
-      <c r="V158" s="86" t="n"/>
-      <c r="W158" s="87">
-        <f>IF(AND(P158="◎ 候補リスト",U158&lt;&gt;"ボツ",U158&lt;&gt;"制作済み",T158&lt;&gt;"",OR('②候補ランキング'!$C$5="すべて",B158='②候補ランキング'!$C$5)),IF('②候補ランキング'!$C$4="ワクワク",Q158,IF('②候補ランキング'!$C$4="手軽さ",11-R158,IF('②候補ランキング'!$C$4="確信度",S158,T158)))*1000+T158+(1000-A158)/10000,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="159" ht="18" customHeight="1" s="35">
-      <c r="A159" s="84">
-        <f>IF(C159="","",ROW()-5)</f>
-        <v/>
-      </c>
-      <c r="B159" s="85" t="n"/>
-      <c r="C159" s="86" t="n"/>
-      <c r="D159" s="86" t="n"/>
-      <c r="E159" s="85" t="n"/>
-      <c r="F159" s="86" t="n"/>
-      <c r="G159" s="86" t="n"/>
-      <c r="H159" s="86" t="n"/>
-      <c r="I159" s="86" t="n"/>
-      <c r="J159" s="85" t="n"/>
-      <c r="K159" s="85" t="n"/>
-      <c r="L159" s="85" t="n"/>
-      <c r="M159" s="85" t="n"/>
-      <c r="N159" s="85" t="n"/>
-      <c r="O159" s="85" t="n"/>
-      <c r="P159" s="84">
-        <f>IF(C159="","",IF(OR(E159="",E159="未検証"),"① STEP1待ち",IF(E159="不通過","✕ STEP1不通過",IF(OR(G159="",H159=""),"② STEP2-3 未記入",IF(COUNTIF(J159:O159,"×")&gt;0,"✕ ボツ候補",IF(COUNTA(J159:O159)&lt;6,"③ STEP4 審査待ち",IF(COUNTIF(J159:O159,"△")&gt;0,"△ 修正して再審査","◎ 候補リスト")))))))</f>
-        <v/>
-      </c>
-      <c r="Q159" s="85" t="n"/>
-      <c r="R159" s="85" t="n"/>
-      <c r="S159" s="85" t="n"/>
-      <c r="T159" s="84">
-        <f>IF(COUNT(Q159:S159)&lt;3,"",Q159+(11-R159)+S159)</f>
-        <v/>
-      </c>
-      <c r="U159" s="85" t="n"/>
-      <c r="V159" s="86" t="n"/>
-      <c r="W159" s="87">
-        <f>IF(AND(P159="◎ 候補リスト",U159&lt;&gt;"ボツ",U159&lt;&gt;"制作済み",T159&lt;&gt;"",OR('②候補ランキング'!$C$5="すべて",B159='②候補ランキング'!$C$5)),IF('②候補ランキング'!$C$4="ワクワク",Q159,IF('②候補ランキング'!$C$4="手軽さ",11-R159,IF('②候補ランキング'!$C$4="確信度",S159,T159)))*1000+T159+(1000-A159)/10000,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="160" ht="18" customHeight="1" s="35">
-      <c r="A160" s="84">
-        <f>IF(C160="","",ROW()-5)</f>
-        <v/>
-      </c>
-      <c r="B160" s="85" t="n"/>
-      <c r="C160" s="86" t="n"/>
-      <c r="D160" s="86" t="n"/>
-      <c r="E160" s="85" t="n"/>
-      <c r="F160" s="86" t="n"/>
-      <c r="G160" s="86" t="n"/>
-      <c r="H160" s="86" t="n"/>
-      <c r="I160" s="86" t="n"/>
-      <c r="J160" s="85" t="n"/>
-      <c r="K160" s="85" t="n"/>
-      <c r="L160" s="85" t="n"/>
-      <c r="M160" s="85" t="n"/>
-      <c r="N160" s="85" t="n"/>
-      <c r="O160" s="85" t="n"/>
-      <c r="P160" s="84">
-        <f>IF(C160="","",IF(OR(E160="",E160="未検証"),"① STEP1待ち",IF(E160="不通過","✕ STEP1不通過",IF(OR(G160="",H160=""),"② STEP2-3 未記入",IF(COUNTIF(J160:O160,"×")&gt;0,"✕ ボツ候補",IF(COUNTA(J160:O160)&lt;6,"③ STEP4 審査待ち",IF(COUNTIF(J160:O160,"△")&gt;0,"△ 修正して再審査","◎ 候補リスト")))))))</f>
-        <v/>
-      </c>
-      <c r="Q160" s="85" t="n"/>
-      <c r="R160" s="85" t="n"/>
-      <c r="S160" s="85" t="n"/>
-      <c r="T160" s="84">
-        <f>IF(COUNT(Q160:S160)&lt;3,"",Q160+(11-R160)+S160)</f>
-        <v/>
-      </c>
-      <c r="U160" s="85" t="n"/>
-      <c r="V160" s="86" t="n"/>
-      <c r="W160" s="87">
-        <f>IF(AND(P160="◎ 候補リスト",U160&lt;&gt;"ボツ",U160&lt;&gt;"制作済み",T160&lt;&gt;"",OR('②候補ランキング'!$C$5="すべて",B160='②候補ランキング'!$C$5)),IF('②候補ランキング'!$C$4="ワクワク",Q160,IF('②候補ランキング'!$C$4="手軽さ",11-R160,IF('②候補ランキング'!$C$4="確信度",S160,T160)))*1000+T160+(1000-A160)/10000,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="161" ht="18" customHeight="1" s="35">
-      <c r="A161" s="84">
-        <f>IF(C161="","",ROW()-5)</f>
-        <v/>
-      </c>
-      <c r="B161" s="85" t="n"/>
-      <c r="C161" s="86" t="n"/>
-      <c r="D161" s="86" t="n"/>
-      <c r="E161" s="85" t="n"/>
-      <c r="F161" s="86" t="n"/>
-      <c r="G161" s="86" t="n"/>
-      <c r="H161" s="86" t="n"/>
-      <c r="I161" s="86" t="n"/>
-      <c r="J161" s="85" t="n"/>
-      <c r="K161" s="85" t="n"/>
-      <c r="L161" s="85" t="n"/>
-      <c r="M161" s="85" t="n"/>
-      <c r="N161" s="85" t="n"/>
-      <c r="O161" s="85" t="n"/>
-      <c r="P161" s="84">
-        <f>IF(C161="","",IF(OR(E161="",E161="未検証"),"① STEP1待ち",IF(E161="不通過","✕ STEP1不通過",IF(OR(G161="",H161=""),"② STEP2-3 未記入",IF(COUNTIF(J161:O161,"×")&gt;0,"✕ ボツ候補",IF(COUNTA(J161:O161)&lt;6,"③ STEP4 審査待ち",IF(COUNTIF(J161:O161,"△")&gt;0,"△ 修正して再審査","◎ 候補リスト")))))))</f>
-        <v/>
-      </c>
-      <c r="Q161" s="85" t="n"/>
-      <c r="R161" s="85" t="n"/>
-      <c r="S161" s="85" t="n"/>
-      <c r="T161" s="84">
-        <f>IF(COUNT(Q161:S161)&lt;3,"",Q161+(11-R161)+S161)</f>
-        <v/>
-      </c>
-      <c r="U161" s="85" t="n"/>
-      <c r="V161" s="86" t="n"/>
-      <c r="W161" s="87">
-        <f>IF(AND(P161="◎ 候補リスト",U161&lt;&gt;"ボツ",U161&lt;&gt;"制作済み",T161&lt;&gt;"",OR('②候補ランキング'!$C$5="すべて",B161='②候補ランキング'!$C$5)),IF('②候補ランキング'!$C$4="ワクワク",Q161,IF('②候補ランキング'!$C$4="手軽さ",11-R161,IF('②候補ランキング'!$C$4="確信度",S161,T161)))*1000+T161+(1000-A161)/10000,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="162" ht="18" customHeight="1" s="35">
-      <c r="A162" s="84">
-        <f>IF(C162="","",ROW()-5)</f>
-        <v/>
-      </c>
-      <c r="B162" s="85" t="n"/>
-      <c r="C162" s="86" t="n"/>
-      <c r="D162" s="86" t="n"/>
-      <c r="E162" s="85" t="n"/>
-      <c r="F162" s="86" t="n"/>
-      <c r="G162" s="86" t="n"/>
-      <c r="H162" s="86" t="n"/>
-      <c r="I162" s="86" t="n"/>
-      <c r="J162" s="85" t="n"/>
-      <c r="K162" s="85" t="n"/>
-      <c r="L162" s="85" t="n"/>
-      <c r="M162" s="85" t="n"/>
-      <c r="N162" s="85" t="n"/>
-      <c r="O162" s="85" t="n"/>
-      <c r="P162" s="84">
-        <f>IF(C162="","",IF(OR(E162="",E162="未検証"),"① STEP1待ち",IF(E162="不通過","✕ STEP1不通過",IF(OR(G162="",H162=""),"② STEP2-3 未記入",IF(COUNTIF(J162:O162,"×")&gt;0,"✕ ボツ候補",IF(COUNTA(J162:O162)&lt;6,"③ STEP4 審査待ち",IF(COUNTIF(J162:O162,"△")&gt;0,"△ 修正して再審査","◎ 候補リスト")))))))</f>
-        <v/>
-      </c>
-      <c r="Q162" s="85" t="n"/>
-      <c r="R162" s="85" t="n"/>
-      <c r="S162" s="85" t="n"/>
-      <c r="T162" s="84">
-        <f>IF(COUNT(Q162:S162)&lt;3,"",Q162+(11-R162)+S162)</f>
-        <v/>
-      </c>
-      <c r="U162" s="85" t="n"/>
-      <c r="V162" s="86" t="n"/>
-      <c r="W162" s="87">
-        <f>IF(AND(P162="◎ 候補リスト",U162&lt;&gt;"ボツ",U162&lt;&gt;"制作済み",T162&lt;&gt;"",OR('②候補ランキング'!$C$5="すべて",B162='②候補ランキング'!$C$5)),IF('②候補ランキング'!$C$4="ワクワク",Q162,IF('②候補ランキング'!$C$4="手軽さ",11-R162,IF('②候補ランキング'!$C$4="確信度",S162,T162)))*1000+T162+(1000-A162)/10000,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="163" ht="18" customHeight="1" s="35">
-      <c r="A163" s="84">
-        <f>IF(C163="","",ROW()-5)</f>
-        <v/>
-      </c>
-      <c r="B163" s="85" t="n"/>
-      <c r="C163" s="86" t="n"/>
-      <c r="D163" s="86" t="n"/>
-      <c r="E163" s="85" t="n"/>
-      <c r="F163" s="86" t="n"/>
-      <c r="G163" s="86" t="n"/>
-      <c r="H163" s="86" t="n"/>
-      <c r="I163" s="86" t="n"/>
-      <c r="J163" s="85" t="n"/>
-      <c r="K163" s="85" t="n"/>
-      <c r="L163" s="85" t="n"/>
-      <c r="M163" s="85" t="n"/>
-      <c r="N163" s="85" t="n"/>
-      <c r="O163" s="85" t="n"/>
-      <c r="P163" s="84">
-        <f>IF(C163="","",IF(OR(E163="",E163="未検証"),"① STEP1待ち",IF(E163="不通過","✕ STEP1不通過",IF(OR(G163="",H163=""),"② STEP2-3 未記入",IF(COUNTIF(J163:O163,"×")&gt;0,"✕ ボツ候補",IF(COUNTA(J163:O163)&lt;6,"③ STEP4 審査待ち",IF(COUNTIF(J163:O163,"△")&gt;0,"△ 修正して再審査","◎ 候補リスト")))))))</f>
-        <v/>
-      </c>
-      <c r="Q163" s="85" t="n"/>
-      <c r="R163" s="85" t="n"/>
-      <c r="S163" s="85" t="n"/>
-      <c r="T163" s="84">
-        <f>IF(COUNT(Q163:S163)&lt;3,"",Q163+(11-R163)+S163)</f>
-        <v/>
-      </c>
-      <c r="U163" s="85" t="n"/>
-      <c r="V163" s="86" t="n"/>
-      <c r="W163" s="87">
-        <f>IF(AND(P163="◎ 候補リスト",U163&lt;&gt;"ボツ",U163&lt;&gt;"制作済み",T163&lt;&gt;"",OR('②候補ランキング'!$C$5="すべて",B163='②候補ランキング'!$C$5)),IF('②候補ランキング'!$C$4="ワクワク",Q163,IF('②候補ランキング'!$C$4="手軽さ",11-R163,IF('②候補ランキング'!$C$4="確信度",S163,T163)))*1000+T163+(1000-A163)/10000,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="164" ht="18" customHeight="1" s="35">
-      <c r="A164" s="84">
-        <f>IF(C164="","",ROW()-5)</f>
-        <v/>
-      </c>
-      <c r="B164" s="85" t="n"/>
-      <c r="C164" s="86" t="n"/>
-      <c r="D164" s="86" t="n"/>
-      <c r="E164" s="85" t="n"/>
-      <c r="F164" s="86" t="n"/>
-      <c r="G164" s="86" t="n"/>
-      <c r="H164" s="86" t="n"/>
-      <c r="I164" s="86" t="n"/>
-      <c r="J164" s="85" t="n"/>
-      <c r="K164" s="85" t="n"/>
-      <c r="L164" s="85" t="n"/>
-      <c r="M164" s="85" t="n"/>
-      <c r="N164" s="85" t="n"/>
-      <c r="O164" s="85" t="n"/>
-      <c r="P164" s="84">
-        <f>IF(C164="","",IF(OR(E164="",E164="未検証"),"① STEP1待ち",IF(E164="不通過","✕ STEP1不通過",IF(OR(G164="",H164=""),"② STEP2-3 未記入",IF(COUNTIF(J164:O164,"×")&gt;0,"✕ ボツ候補",IF(COUNTA(J164:O164)&lt;6,"③ STEP4 審査待ち",IF(COUNTIF(J164:O164,"△")&gt;0,"△ 修正して再審査","◎ 候補リスト")))))))</f>
-        <v/>
-      </c>
-      <c r="Q164" s="85" t="n"/>
-      <c r="R164" s="85" t="n"/>
-      <c r="S164" s="85" t="n"/>
-      <c r="T164" s="84">
-        <f>IF(COUNT(Q164:S164)&lt;3,"",Q164+(11-R164)+S164)</f>
-        <v/>
-      </c>
-      <c r="U164" s="85" t="n"/>
-      <c r="V164" s="86" t="n"/>
-      <c r="W164" s="87">
-        <f>IF(AND(P164="◎ 候補リスト",U164&lt;&gt;"ボツ",U164&lt;&gt;"制作済み",T164&lt;&gt;"",OR('②候補ランキング'!$C$5="すべて",B164='②候補ランキング'!$C$5)),IF('②候補ランキング'!$C$4="ワクワク",Q164,IF('②候補ランキング'!$C$4="手軽さ",11-R164,IF('②候補ランキング'!$C$4="確信度",S164,T164)))*1000+T164+(1000-A164)/10000,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="165" ht="18" customHeight="1" s="35">
-      <c r="A165" s="84">
-        <f>IF(C165="","",ROW()-5)</f>
-        <v/>
-      </c>
-      <c r="B165" s="85" t="n"/>
-      <c r="C165" s="86" t="n"/>
-      <c r="D165" s="86" t="n"/>
-      <c r="E165" s="85" t="n"/>
-      <c r="F165" s="86" t="n"/>
-      <c r="G165" s="86" t="n"/>
-      <c r="H165" s="86" t="n"/>
-      <c r="I165" s="86" t="n"/>
-      <c r="J165" s="85" t="n"/>
-      <c r="K165" s="85" t="n"/>
-      <c r="L165" s="85" t="n"/>
-      <c r="M165" s="85" t="n"/>
-      <c r="N165" s="85" t="n"/>
-      <c r="O165" s="85" t="n"/>
-      <c r="P165" s="84">
-        <f>IF(C165="","",IF(OR(E165="",E165="未検証"),"① STEP1待ち",IF(E165="不通過","✕ STEP1不通過",IF(OR(G165="",H165=""),"② STEP2-3 未記入",IF(COUNTIF(J165:O165,"×")&gt;0,"✕ ボツ候補",IF(COUNTA(J165:O165)&lt;6,"③ STEP4 審査待ち",IF(COUNTIF(J165:O165,"△")&gt;0,"△ 修正して再審査","◎ 候補リスト")))))))</f>
-        <v/>
-      </c>
-      <c r="Q165" s="85" t="n"/>
-      <c r="R165" s="85" t="n"/>
-      <c r="S165" s="85" t="n"/>
-      <c r="T165" s="84">
-        <f>IF(COUNT(Q165:S165)&lt;3,"",Q165+(11-R165)+S165)</f>
-        <v/>
-      </c>
-      <c r="U165" s="85" t="n"/>
-      <c r="V165" s="86" t="n"/>
-      <c r="W165" s="87">
-        <f>IF(AND(P165="◎ 候補リスト",U165&lt;&gt;"ボツ",U165&lt;&gt;"制作済み",T165&lt;&gt;"",OR('②候補ランキング'!$C$5="すべて",B165='②候補ランキング'!$C$5)),IF('②候補ランキング'!$C$4="ワクワク",Q165,IF('②候補ランキング'!$C$4="手軽さ",11-R165,IF('②候補ランキング'!$C$4="確信度",S165,T165)))*1000+T165+(1000-A165)/10000,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="166" ht="18" customHeight="1" s="35">
-      <c r="A166" s="84">
-        <f>IF(C166="","",ROW()-5)</f>
-        <v/>
-      </c>
-      <c r="B166" s="85" t="n"/>
-      <c r="C166" s="86" t="n"/>
-      <c r="D166" s="86" t="n"/>
-      <c r="E166" s="85" t="n"/>
-      <c r="F166" s="86" t="n"/>
-      <c r="G166" s="86" t="n"/>
-      <c r="H166" s="86" t="n"/>
-      <c r="I166" s="86" t="n"/>
-      <c r="J166" s="85" t="n"/>
-      <c r="K166" s="85" t="n"/>
-      <c r="L166" s="85" t="n"/>
-      <c r="M166" s="85" t="n"/>
-      <c r="N166" s="85" t="n"/>
-      <c r="O166" s="85" t="n"/>
-      <c r="P166" s="84">
-        <f>IF(C166="","",IF(OR(E166="",E166="未検証"),"① STEP1待ち",IF(E166="不通過","✕ STEP1不通過",IF(OR(G166="",H166=""),"② STEP2-3 未記入",IF(COUNTIF(J166:O166,"×")&gt;0,"✕ ボツ候補",IF(COUNTA(J166:O166)&lt;6,"③ STEP4 審査待ち",IF(COUNTIF(J166:O166,"△")&gt;0,"△ 修正して再審査","◎ 候補リスト")))))))</f>
-        <v/>
-      </c>
-      <c r="Q166" s="85" t="n"/>
-      <c r="R166" s="85" t="n"/>
-      <c r="S166" s="85" t="n"/>
-      <c r="T166" s="84">
-        <f>IF(COUNT(Q166:S166)&lt;3,"",Q166+(11-R166)+S166)</f>
-        <v/>
-      </c>
-      <c r="U166" s="85" t="n"/>
-      <c r="V166" s="86" t="n"/>
-      <c r="W166" s="87">
-        <f>IF(AND(P166="◎ 候補リスト",U166&lt;&gt;"ボツ",U166&lt;&gt;"制作済み",T166&lt;&gt;"",OR('②候補ランキング'!$C$5="すべて",B166='②候補ランキング'!$C$5)),IF('②候補ランキング'!$C$4="ワクワク",Q166,IF('②候補ランキング'!$C$4="手軽さ",11-R166,IF('②候補ランキング'!$C$4="確信度",S166,T166)))*1000+T166+(1000-A166)/10000,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="167" ht="18" customHeight="1" s="35">
-      <c r="A167" s="84">
-        <f>IF(C167="","",ROW()-5)</f>
-        <v/>
-      </c>
-      <c r="B167" s="85" t="n"/>
-      <c r="C167" s="86" t="n"/>
-      <c r="D167" s="86" t="n"/>
-      <c r="E167" s="85" t="n"/>
-      <c r="F167" s="86" t="n"/>
-      <c r="G167" s="86" t="n"/>
-      <c r="H167" s="86" t="n"/>
-      <c r="I167" s="86" t="n"/>
-      <c r="J167" s="85" t="n"/>
-      <c r="K167" s="85" t="n"/>
-      <c r="L167" s="85" t="n"/>
-      <c r="M167" s="85" t="n"/>
-      <c r="N167" s="85" t="n"/>
-      <c r="O167" s="85" t="n"/>
-      <c r="P167" s="84">
-        <f>IF(C167="","",IF(OR(E167="",E167="未検証"),"① STEP1待ち",IF(E167="不通過","✕ STEP1不通過",IF(OR(G167="",H167=""),"② STEP2-3 未記入",IF(COUNTIF(J167:O167,"×")&gt;0,"✕ ボツ候補",IF(COUNTA(J167:O167)&lt;6,"③ STEP4 審査待ち",IF(COUNTIF(J167:O167,"△")&gt;0,"△ 修正して再審査","◎ 候補リスト")))))))</f>
-        <v/>
-      </c>
-      <c r="Q167" s="85" t="n"/>
-      <c r="R167" s="85" t="n"/>
-      <c r="S167" s="85" t="n"/>
-      <c r="T167" s="84">
-        <f>IF(COUNT(Q167:S167)&lt;3,"",Q167+(11-R167)+S167)</f>
-        <v/>
-      </c>
-      <c r="U167" s="85" t="n"/>
-      <c r="V167" s="86" t="n"/>
-      <c r="W167" s="87">
-        <f>IF(AND(P167="◎ 候補リスト",U167&lt;&gt;"ボツ",U167&lt;&gt;"制作済み",T167&lt;&gt;"",OR('②候補ランキング'!$C$5="すべて",B167='②候補ランキング'!$C$5)),IF('②候補ランキング'!$C$4="ワクワク",Q167,IF('②候補ランキング'!$C$4="手軽さ",11-R167,IF('②候補ランキング'!$C$4="確信度",S167,T167)))*1000+T167+(1000-A167)/10000,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="168" ht="18" customHeight="1" s="35">
-      <c r="A168" s="84">
-        <f>IF(C168="","",ROW()-5)</f>
-        <v/>
-      </c>
-      <c r="B168" s="85" t="n"/>
-      <c r="C168" s="86" t="n"/>
-      <c r="D168" s="86" t="n"/>
-      <c r="E168" s="85" t="n"/>
-      <c r="F168" s="86" t="n"/>
-      <c r="G168" s="86" t="n"/>
-      <c r="H168" s="86" t="n"/>
-      <c r="I168" s="86" t="n"/>
-      <c r="J168" s="85" t="n"/>
-      <c r="K168" s="85" t="n"/>
-      <c r="L168" s="85" t="n"/>
-      <c r="M168" s="85" t="n"/>
-      <c r="N168" s="85" t="n"/>
-      <c r="O168" s="85" t="n"/>
-      <c r="P168" s="84">
-        <f>IF(C168="","",IF(OR(E168="",E168="未検証"),"① STEP1待ち",IF(E168="不通過","✕ STEP1不通過",IF(OR(G168="",H168=""),"② STEP2-3 未記入",IF(COUNTIF(J168:O168,"×")&gt;0,"✕ ボツ候補",IF(COUNTA(J168:O168)&lt;6,"③ STEP4 審査待ち",IF(COUNTIF(J168:O168,"△")&gt;0,"△ 修正して再審査","◎ 候補リスト")))))))</f>
-        <v/>
-      </c>
-      <c r="Q168" s="85" t="n"/>
-      <c r="R168" s="85" t="n"/>
-      <c r="S168" s="85" t="n"/>
-      <c r="T168" s="84">
-        <f>IF(COUNT(Q168:S168)&lt;3,"",Q168+(11-R168)+S168)</f>
-        <v/>
-      </c>
-      <c r="U168" s="85" t="n"/>
-      <c r="V168" s="86" t="n"/>
-      <c r="W168" s="87">
-        <f>IF(AND(P168="◎ 候補リスト",U168&lt;&gt;"ボツ",U168&lt;&gt;"制作済み",T168&lt;&gt;"",OR('②候補ランキング'!$C$5="すべて",B168='②候補ランキング'!$C$5)),IF('②候補ランキング'!$C$4="ワクワク",Q168,IF('②候補ランキング'!$C$4="手軽さ",11-R168,IF('②候補ランキング'!$C$4="確信度",S168,T168)))*1000+T168+(1000-A168)/10000,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="169" ht="18" customHeight="1" s="35">
-      <c r="A169" s="84">
-        <f>IF(C169="","",ROW()-5)</f>
-        <v/>
-      </c>
-      <c r="B169" s="85" t="n"/>
-      <c r="C169" s="86" t="n"/>
-      <c r="D169" s="86" t="n"/>
-      <c r="E169" s="85" t="n"/>
-      <c r="F169" s="86" t="n"/>
-      <c r="G169" s="86" t="n"/>
-      <c r="H169" s="86" t="n"/>
-      <c r="I169" s="86" t="n"/>
-      <c r="J169" s="85" t="n"/>
-      <c r="K169" s="85" t="n"/>
-      <c r="L169" s="85" t="n"/>
-      <c r="M169" s="85" t="n"/>
-      <c r="N169" s="85" t="n"/>
-      <c r="O169" s="85" t="n"/>
-      <c r="P169" s="84">
-        <f>IF(C169="","",IF(OR(E169="",E169="未検証"),"① STEP1待ち",IF(E169="不通過","✕ STEP1不通過",IF(OR(G169="",H169=""),"② STEP2-3 未記入",IF(COUNTIF(J169:O169,"×")&gt;0,"✕ ボツ候補",IF(COUNTA(J169:O169)&lt;6,"③ STEP4 審査待ち",IF(COUNTIF(J169:O169,"△")&gt;0,"△ 修正して再審査","◎ 候補リスト")))))))</f>
-        <v/>
-      </c>
-      <c r="Q169" s="85" t="n"/>
-      <c r="R169" s="85" t="n"/>
-      <c r="S169" s="85" t="n"/>
-      <c r="T169" s="84">
-        <f>IF(COUNT(Q169:S169)&lt;3,"",Q169+(11-R169)+S169)</f>
-        <v/>
-      </c>
-      <c r="U169" s="85" t="n"/>
-      <c r="V169" s="86" t="n"/>
-      <c r="W169" s="87">
-        <f>IF(AND(P169="◎ 候補リスト",U169&lt;&gt;"ボツ",U169&lt;&gt;"制作済み",T169&lt;&gt;"",OR('②候補ランキング'!$C$5="すべて",B169='②候補ランキング'!$C$5)),IF('②候補ランキング'!$C$4="ワクワク",Q169,IF('②候補ランキング'!$C$4="手軽さ",11-R169,IF('②候補ランキング'!$C$4="確信度",S169,T169)))*1000+T169+(1000-A169)/10000,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="170" ht="18" customHeight="1" s="35">
-      <c r="A170" s="84">
-        <f>IF(C170="","",ROW()-5)</f>
-        <v/>
-      </c>
-      <c r="B170" s="85" t="n"/>
-      <c r="C170" s="86" t="n"/>
-      <c r="D170" s="86" t="n"/>
-      <c r="E170" s="85" t="n"/>
-      <c r="F170" s="86" t="n"/>
-      <c r="G170" s="86" t="n"/>
-      <c r="H170" s="86" t="n"/>
-      <c r="I170" s="86" t="n"/>
-      <c r="J170" s="85" t="n"/>
-      <c r="K170" s="85" t="n"/>
-      <c r="L170" s="85" t="n"/>
-      <c r="M170" s="85" t="n"/>
-      <c r="N170" s="85" t="n"/>
-      <c r="O170" s="85" t="n"/>
-      <c r="P170" s="84">
-        <f>IF(C170="","",IF(OR(E170="",E170="未検証"),"① STEP1待ち",IF(E170="不通過","✕ STEP1不通過",IF(OR(G170="",H170=""),"② STEP2-3 未記入",IF(COUNTIF(J170:O170,"×")&gt;0,"✕ ボツ候補",IF(COUNTA(J170:O170)&lt;6,"③ STEP4 審査待ち",IF(COUNTIF(J170:O170,"△")&gt;0,"△ 修正して再審査","◎ 候補リスト")))))))</f>
-        <v/>
-      </c>
-      <c r="Q170" s="85" t="n"/>
-      <c r="R170" s="85" t="n"/>
-      <c r="S170" s="85" t="n"/>
-      <c r="T170" s="84">
-        <f>IF(COUNT(Q170:S170)&lt;3,"",Q170+(11-R170)+S170)</f>
-        <v/>
-      </c>
-      <c r="U170" s="85" t="n"/>
-      <c r="V170" s="86" t="n"/>
-      <c r="W170" s="87">
-        <f>IF(AND(P170="◎ 候補リスト",U170&lt;&gt;"ボツ",U170&lt;&gt;"制作済み",T170&lt;&gt;"",OR('②候補ランキング'!$C$5="すべて",B170='②候補ランキング'!$C$5)),IF('②候補ランキング'!$C$4="ワクワク",Q170,IF('②候補ランキング'!$C$4="手軽さ",11-R170,IF('②候補ランキング'!$C$4="確信度",S170,T170)))*1000+T170+(1000-A170)/10000,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="171" ht="18" customHeight="1" s="35">
-      <c r="A171" s="84">
-        <f>IF(C171="","",ROW()-5)</f>
-        <v/>
-      </c>
-      <c r="B171" s="85" t="n"/>
-      <c r="C171" s="86" t="n"/>
-      <c r="D171" s="86" t="n"/>
-      <c r="E171" s="85" t="n"/>
-      <c r="F171" s="86" t="n"/>
-      <c r="G171" s="86" t="n"/>
-      <c r="H171" s="86" t="n"/>
-      <c r="I171" s="86" t="n"/>
-      <c r="J171" s="85" t="n"/>
-      <c r="K171" s="85" t="n"/>
-      <c r="L171" s="85" t="n"/>
-      <c r="M171" s="85" t="n"/>
-      <c r="N171" s="85" t="n"/>
-      <c r="O171" s="85" t="n"/>
-      <c r="P171" s="84">
-        <f>IF(C171="","",IF(OR(E171="",E171="未検証"),"① STEP1待ち",IF(E171="不通過","✕ STEP1不通過",IF(OR(G171="",H171=""),"② STEP2-3 未記入",IF(COUNTIF(J171:O171,"×")&gt;0,"✕ ボツ候補",IF(COUNTA(J171:O171)&lt;6,"③ STEP4 審査待ち",IF(COUNTIF(J171:O171,"△")&gt;0,"△ 修正して再審査","◎ 候補リスト")))))))</f>
-        <v/>
-      </c>
-      <c r="Q171" s="85" t="n"/>
-      <c r="R171" s="85" t="n"/>
-      <c r="S171" s="85" t="n"/>
-      <c r="T171" s="84">
-        <f>IF(COUNT(Q171:S171)&lt;3,"",Q171+(11-R171)+S171)</f>
-        <v/>
-      </c>
-      <c r="U171" s="85" t="n"/>
-      <c r="V171" s="86" t="n"/>
-      <c r="W171" s="87">
-        <f>IF(AND(P171="◎ 候補リスト",U171&lt;&gt;"ボツ",U171&lt;&gt;"制作済み",T171&lt;&gt;"",OR('②候補ランキング'!$C$5="すべて",B171='②候補ランキング'!$C$5)),IF('②候補ランキング'!$C$4="ワクワク",Q171,IF('②候補ランキング'!$C$4="手軽さ",11-R171,IF('②候補ランキング'!$C$4="確信度",S171,T171)))*1000+T171+(1000-A171)/10000,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="172" ht="18" customHeight="1" s="35">
-      <c r="A172" s="84">
-        <f>IF(C172="","",ROW()-5)</f>
-        <v/>
-      </c>
-      <c r="B172" s="85" t="n"/>
-      <c r="C172" s="86" t="n"/>
-      <c r="D172" s="86" t="n"/>
-      <c r="E172" s="85" t="n"/>
-      <c r="F172" s="86" t="n"/>
-      <c r="G172" s="86" t="n"/>
-      <c r="H172" s="86" t="n"/>
-      <c r="I172" s="86" t="n"/>
-      <c r="J172" s="85" t="n"/>
-      <c r="K172" s="85" t="n"/>
-      <c r="L172" s="85" t="n"/>
-      <c r="M172" s="85" t="n"/>
-      <c r="N172" s="85" t="n"/>
-      <c r="O172" s="85" t="n"/>
-      <c r="P172" s="84">
-        <f>IF(C172="","",IF(OR(E172="",E172="未検証"),"① STEP1待ち",IF(E172="不通過","✕ STEP1不通過",IF(OR(G172="",H172=""),"② STEP2-3 未記入",IF(COUNTIF(J172:O172,"×")&gt;0,"✕ ボツ候補",IF(COUNTA(J172:O172)&lt;6,"③ STEP4 審査待ち",IF(COUNTIF(J172:O172,"△")&gt;0,"△ 修正して再審査","◎ 候補リスト")))))))</f>
-        <v/>
-      </c>
-      <c r="Q172" s="85" t="n"/>
-      <c r="R172" s="85" t="n"/>
-      <c r="S172" s="85" t="n"/>
-      <c r="T172" s="84">
-        <f>IF(COUNT(Q172:S172)&lt;3,"",Q172+(11-R172)+S172)</f>
-        <v/>
-      </c>
-      <c r="U172" s="85" t="n"/>
-      <c r="V172" s="86" t="n"/>
-      <c r="W172" s="87">
-        <f>IF(AND(P172="◎ 候補リスト",U172&lt;&gt;"ボツ",U172&lt;&gt;"制作済み",T172&lt;&gt;"",OR('②候補ランキング'!$C$5="すべて",B172='②候補ランキング'!$C$5)),IF('②候補ランキング'!$C$4="ワクワク",Q172,IF('②候補ランキング'!$C$4="手軽さ",11-R172,IF('②候補ランキング'!$C$4="確信度",S172,T172)))*1000+T172+(1000-A172)/10000,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="173" ht="18" customHeight="1" s="35">
-      <c r="A173" s="84">
-        <f>IF(C173="","",ROW()-5)</f>
-        <v/>
-      </c>
-      <c r="B173" s="85" t="n"/>
-      <c r="C173" s="86" t="n"/>
-      <c r="D173" s="86" t="n"/>
-      <c r="E173" s="85" t="n"/>
-      <c r="F173" s="86" t="n"/>
-      <c r="G173" s="86" t="n"/>
-      <c r="H173" s="86" t="n"/>
-      <c r="I173" s="86" t="n"/>
-      <c r="J173" s="85" t="n"/>
-      <c r="K173" s="85" t="n"/>
-      <c r="L173" s="85" t="n"/>
-      <c r="M173" s="85" t="n"/>
-      <c r="N173" s="85" t="n"/>
-      <c r="O173" s="85" t="n"/>
-      <c r="P173" s="84">
-        <f>IF(C173="","",IF(OR(E173="",E173="未検証"),"① STEP1待ち",IF(E173="不通過","✕ STEP1不通過",IF(OR(G173="",H173=""),"② STEP2-3 未記入",IF(COUNTIF(J173:O173,"×")&gt;0,"✕ ボツ候補",IF(COUNTA(J173:O173)&lt;6,"③ STEP4 審査待ち",IF(COUNTIF(J173:O173,"△")&gt;0,"△ 修正して再審査","◎ 候補リスト")))))))</f>
-        <v/>
-      </c>
-      <c r="Q173" s="85" t="n"/>
-      <c r="R173" s="85" t="n"/>
-      <c r="S173" s="85" t="n"/>
-      <c r="T173" s="84">
-        <f>IF(COUNT(Q173:S173)&lt;3,"",Q173+(11-R173)+S173)</f>
-        <v/>
-      </c>
-      <c r="U173" s="85" t="n"/>
-      <c r="V173" s="86" t="n"/>
-      <c r="W173" s="87">
-        <f>IF(AND(P173="◎ 候補リスト",U173&lt;&gt;"ボツ",U173&lt;&gt;"制作済み",T173&lt;&gt;"",OR('②候補ランキング'!$C$5="すべて",B173='②候補ランキング'!$C$5)),IF('②候補ランキング'!$C$4="ワクワク",Q173,IF('②候補ランキング'!$C$4="手軽さ",11-R173,IF('②候補ランキング'!$C$4="確信度",S173,T173)))*1000+T173+(1000-A173)/10000,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="174" ht="18" customHeight="1" s="35">
-      <c r="A174" s="84">
-        <f>IF(C174="","",ROW()-5)</f>
-        <v/>
-      </c>
-      <c r="B174" s="85" t="n"/>
-      <c r="C174" s="86" t="n"/>
-      <c r="D174" s="86" t="n"/>
-      <c r="E174" s="85" t="n"/>
-      <c r="F174" s="86" t="n"/>
-      <c r="G174" s="86" t="n"/>
-      <c r="H174" s="86" t="n"/>
-      <c r="I174" s="86" t="n"/>
-      <c r="J174" s="85" t="n"/>
-      <c r="K174" s="85" t="n"/>
-      <c r="L174" s="85" t="n"/>
-      <c r="M174" s="85" t="n"/>
-      <c r="N174" s="85" t="n"/>
-      <c r="O174" s="85" t="n"/>
-      <c r="P174" s="84">
-        <f>IF(C174="","",IF(OR(E174="",E174="未検証"),"① STEP1待ち",IF(E174="不通過","✕ STEP1不通過",IF(OR(G174="",H174=""),"② STEP2-3 未記入",IF(COUNTIF(J174:O174,"×")&gt;0,"✕ ボツ候補",IF(COUNTA(J174:O174)&lt;6,"③ STEP4 審査待ち",IF(COUNTIF(J174:O174,"△")&gt;0,"△ 修正して再審査","◎ 候補リスト")))))))</f>
-        <v/>
-      </c>
-      <c r="Q174" s="85" t="n"/>
-      <c r="R174" s="85" t="n"/>
-      <c r="S174" s="85" t="n"/>
-      <c r="T174" s="84">
-        <f>IF(COUNT(Q174:S174)&lt;3,"",Q174+(11-R174)+S174)</f>
-        <v/>
-      </c>
-      <c r="U174" s="85" t="n"/>
-      <c r="V174" s="86" t="n"/>
-      <c r="W174" s="87">
-        <f>IF(AND(P174="◎ 候補リスト",U174&lt;&gt;"ボツ",U174&lt;&gt;"制作済み",T174&lt;&gt;"",OR('②候補ランキング'!$C$5="すべて",B174='②候補ランキング'!$C$5)),IF('②候補ランキング'!$C$4="ワクワク",Q174,IF('②候補ランキング'!$C$4="手軽さ",11-R174,IF('②候補ランキング'!$C$4="確信度",S174,T174)))*1000+T174+(1000-A174)/10000,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="175" ht="18" customHeight="1" s="35">
-      <c r="A175" s="84">
-        <f>IF(C175="","",ROW()-5)</f>
-        <v/>
-      </c>
-      <c r="B175" s="85" t="n"/>
-      <c r="C175" s="86" t="n"/>
-      <c r="D175" s="86" t="n"/>
-      <c r="E175" s="85" t="n"/>
-      <c r="F175" s="86" t="n"/>
-      <c r="G175" s="86" t="n"/>
-      <c r="H175" s="86" t="n"/>
-      <c r="I175" s="86" t="n"/>
-      <c r="J175" s="85" t="n"/>
-      <c r="K175" s="85" t="n"/>
-      <c r="L175" s="85" t="n"/>
-      <c r="M175" s="85" t="n"/>
-      <c r="N175" s="85" t="n"/>
-      <c r="O175" s="85" t="n"/>
-      <c r="P175" s="84">
-        <f>IF(C175="","",IF(OR(E175="",E175="未検証"),"① STEP1待ち",IF(E175="不通過","✕ STEP1不通過",IF(OR(G175="",H175=""),"② STEP2-3 未記入",IF(COUNTIF(J175:O175,"×")&gt;0,"✕ ボツ候補",IF(COUNTA(J175:O175)&lt;6,"③ STEP4 審査待ち",IF(COUNTIF(J175:O175,"△")&gt;0,"△ 修正して再審査","◎ 候補リスト")))))))</f>
-        <v/>
-      </c>
-      <c r="Q175" s="85" t="n"/>
-      <c r="R175" s="85" t="n"/>
-      <c r="S175" s="85" t="n"/>
-      <c r="T175" s="84">
-        <f>IF(COUNT(Q175:S175)&lt;3,"",Q175+(11-R175)+S175)</f>
-        <v/>
-      </c>
-      <c r="U175" s="85" t="n"/>
-      <c r="V175" s="86" t="n"/>
-      <c r="W175" s="87">
-        <f>IF(AND(P175="◎ 候補リスト",U175&lt;&gt;"ボツ",U175&lt;&gt;"制作済み",T175&lt;&gt;"",OR('②候補ランキング'!$C$5="すべて",B175='②候補ランキング'!$C$5)),IF('②候補ランキング'!$C$4="ワクワク",Q175,IF('②候補ランキング'!$C$4="手軽さ",11-R175,IF('②候補ランキング'!$C$4="確信度",S175,T175)))*1000+T175+(1000-A175)/10000,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="176" ht="18" customHeight="1" s="35">
-      <c r="A176" s="84">
-        <f>IF(C176="","",ROW()-5)</f>
-        <v/>
-      </c>
-      <c r="B176" s="85" t="n"/>
-      <c r="C176" s="86" t="n"/>
-      <c r="D176" s="86" t="n"/>
-      <c r="E176" s="85" t="n"/>
-      <c r="F176" s="86" t="n"/>
-      <c r="G176" s="86" t="n"/>
-      <c r="H176" s="86" t="n"/>
-      <c r="I176" s="86" t="n"/>
-      <c r="J176" s="85" t="n"/>
-      <c r="K176" s="85" t="n"/>
-      <c r="L176" s="85" t="n"/>
-      <c r="M176" s="85" t="n"/>
-      <c r="N176" s="85" t="n"/>
-      <c r="O176" s="85" t="n"/>
-      <c r="P176" s="84">
-        <f>IF(C176="","",IF(OR(E176="",E176="未検証"),"① STEP1待ち",IF(E176="不通過","✕ STEP1不通過",IF(OR(G176="",H176=""),"② STEP2-3 未記入",IF(COUNTIF(J176:O176,"×")&gt;0,"✕ ボツ候補",IF(COUNTA(J176:O176)&lt;6,"③ STEP4 審査待ち",IF(COUNTIF(J176:O176,"△")&gt;0,"△ 修正して再審査","◎ 候補リスト")))))))</f>
-        <v/>
-      </c>
-      <c r="Q176" s="85" t="n"/>
-      <c r="R176" s="85" t="n"/>
-      <c r="S176" s="85" t="n"/>
-      <c r="T176" s="84">
-        <f>IF(COUNT(Q176:S176)&lt;3,"",Q176+(11-R176)+S176)</f>
-        <v/>
-      </c>
-      <c r="U176" s="85" t="n"/>
-      <c r="V176" s="86" t="n"/>
-      <c r="W176" s="87">
-        <f>IF(AND(P176="◎ 候補リスト",U176&lt;&gt;"ボツ",U176&lt;&gt;"制作済み",T176&lt;&gt;"",OR('②候補ランキング'!$C$5="すべて",B176='②候補ランキング'!$C$5)),IF('②候補ランキング'!$C$4="ワクワク",Q176,IF('②候補ランキング'!$C$4="手軽さ",11-R176,IF('②候補ランキング'!$C$4="確信度",S176,T176)))*1000+T176+(1000-A176)/10000,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="177" ht="18" customHeight="1" s="35">
-      <c r="A177" s="84">
-        <f>IF(C177="","",ROW()-5)</f>
-        <v/>
-      </c>
-      <c r="B177" s="85" t="n"/>
-      <c r="C177" s="86" t="n"/>
-      <c r="D177" s="86" t="n"/>
-      <c r="E177" s="85" t="n"/>
-      <c r="F177" s="86" t="n"/>
-      <c r="G177" s="86" t="n"/>
-      <c r="H177" s="86" t="n"/>
-      <c r="I177" s="86" t="n"/>
-      <c r="J177" s="85" t="n"/>
-      <c r="K177" s="85" t="n"/>
-      <c r="L177" s="85" t="n"/>
-      <c r="M177" s="85" t="n"/>
-      <c r="N177" s="85" t="n"/>
-      <c r="O177" s="85" t="n"/>
-      <c r="P177" s="84">
-        <f>IF(C177="","",IF(OR(E177="",E177="未検証"),"① STEP1待ち",IF(E177="不通過","✕ STEP1不通過",IF(OR(G177="",H177=""),"② STEP2-3 未記入",IF(COUNTIF(J177:O177,"×")&gt;0,"✕ ボツ候補",IF(COUNTA(J177:O177)&lt;6,"③ STEP4 審査待ち",IF(COUNTIF(J177:O177,"△")&gt;0,"△ 修正して再審査","◎ 候補リスト")))))))</f>
-        <v/>
-      </c>
-      <c r="Q177" s="85" t="n"/>
-      <c r="R177" s="85" t="n"/>
-      <c r="S177" s="85" t="n"/>
-      <c r="T177" s="84">
-        <f>IF(COUNT(Q177:S177)&lt;3,"",Q177+(11-R177)+S177)</f>
-        <v/>
-      </c>
-      <c r="U177" s="85" t="n"/>
-      <c r="V177" s="86" t="n"/>
-      <c r="W177" s="87">
-        <f>IF(AND(P177="◎ 候補リスト",U177&lt;&gt;"ボツ",U177&lt;&gt;"制作済み",T177&lt;&gt;"",OR('②候補ランキング'!$C$5="すべて",B177='②候補ランキング'!$C$5)),IF('②候補ランキング'!$C$4="ワクワク",Q177,IF('②候補ランキング'!$C$4="手軽さ",11-R177,IF('②候補ランキング'!$C$4="確信度",S177,T177)))*1000+T177+(1000-A177)/10000,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="178" ht="18" customHeight="1" s="35">
-      <c r="A178" s="84">
-        <f>IF(C178="","",ROW()-5)</f>
-        <v/>
-      </c>
-      <c r="B178" s="85" t="n"/>
-      <c r="C178" s="86" t="n"/>
-      <c r="D178" s="86" t="n"/>
-      <c r="E178" s="85" t="n"/>
-      <c r="F178" s="86" t="n"/>
-      <c r="G178" s="86" t="n"/>
-      <c r="H178" s="86" t="n"/>
-      <c r="I178" s="86" t="n"/>
-      <c r="J178" s="85" t="n"/>
-      <c r="K178" s="85" t="n"/>
-      <c r="L178" s="85" t="n"/>
-      <c r="M178" s="85" t="n"/>
-      <c r="N178" s="85" t="n"/>
-      <c r="O178" s="85" t="n"/>
-      <c r="P178" s="84">
-        <f>IF(C178="","",IF(OR(E178="",E178="未検証"),"① STEP1待ち",IF(E178="不通過","✕ STEP1不通過",IF(OR(G178="",H178=""),"② STEP2-3 未記入",IF(COUNTIF(J178:O178,"×")&gt;0,"✕ ボツ候補",IF(COUNTA(J178:O178)&lt;6,"③ STEP4 審査待ち",IF(COUNTIF(J178:O178,"△")&gt;0,"△ 修正して再審査","◎ 候補リスト")))))))</f>
-        <v/>
-      </c>
-      <c r="Q178" s="85" t="n"/>
-      <c r="R178" s="85" t="n"/>
-      <c r="S178" s="85" t="n"/>
-      <c r="T178" s="84">
-        <f>IF(COUNT(Q178:S178)&lt;3,"",Q178+(11-R178)+S178)</f>
-        <v/>
-      </c>
-      <c r="U178" s="85" t="n"/>
-      <c r="V178" s="86" t="n"/>
-      <c r="W178" s="87">
-        <f>IF(AND(P178="◎ 候補リスト",U178&lt;&gt;"ボツ",U178&lt;&gt;"制作済み",T178&lt;&gt;"",OR('②候補ランキング'!$C$5="すべて",B178='②候補ランキング'!$C$5)),IF('②候補ランキング'!$C$4="ワクワク",Q178,IF('②候補ランキング'!$C$4="手軽さ",11-R178,IF('②候補ランキング'!$C$4="確信度",S178,T178)))*1000+T178+(1000-A178)/10000,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="179" ht="18" customHeight="1" s="35">
-      <c r="A179" s="84">
-        <f>IF(C179="","",ROW()-5)</f>
-        <v/>
-      </c>
-      <c r="B179" s="85" t="n"/>
-      <c r="C179" s="86" t="n"/>
-      <c r="D179" s="86" t="n"/>
-      <c r="E179" s="85" t="n"/>
-      <c r="F179" s="86" t="n"/>
-      <c r="G179" s="86" t="n"/>
-      <c r="H179" s="86" t="n"/>
-      <c r="I179" s="86" t="n"/>
-      <c r="J179" s="85" t="n"/>
-      <c r="K179" s="85" t="n"/>
-      <c r="L179" s="85" t="n"/>
-      <c r="M179" s="85" t="n"/>
-      <c r="N179" s="85" t="n"/>
-      <c r="O179" s="85" t="n"/>
-      <c r="P179" s="84">
-        <f>IF(C179="","",IF(OR(E179="",E179="未検証"),"① STEP1待ち",IF(E179="不通過","✕ STEP1不通過",IF(OR(G179="",H179=""),"② STEP2-3 未記入",IF(COUNTIF(J179:O179,"×")&gt;0,"✕ ボツ候補",IF(COUNTA(J179:O179)&lt;6,"③ STEP4 審査待ち",IF(COUNTIF(J179:O179,"△")&gt;0,"△ 修正して再審査","◎ 候補リスト")))))))</f>
-        <v/>
-      </c>
-      <c r="Q179" s="85" t="n"/>
-      <c r="R179" s="85" t="n"/>
-      <c r="S179" s="85" t="n"/>
-      <c r="T179" s="84">
-        <f>IF(COUNT(Q179:S179)&lt;3,"",Q179+(11-R179)+S179)</f>
-        <v/>
-      </c>
-      <c r="U179" s="85" t="n"/>
-      <c r="V179" s="86" t="n"/>
-      <c r="W179" s="87">
-        <f>IF(AND(P179="◎ 候補リスト",U179&lt;&gt;"ボツ",U179&lt;&gt;"制作済み",T179&lt;&gt;"",OR('②候補ランキング'!$C$5="すべて",B179='②候補ランキング'!$C$5)),IF('②候補ランキング'!$C$4="ワクワク",Q179,IF('②候補ランキング'!$C$4="手軽さ",11-R179,IF('②候補ランキング'!$C$4="確信度",S179,T179)))*1000+T179+(1000-A179)/10000,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="180" ht="18" customHeight="1" s="35">
-      <c r="A180" s="84">
-        <f>IF(C180="","",ROW()-5)</f>
-        <v/>
-      </c>
-      <c r="B180" s="85" t="n"/>
-      <c r="C180" s="86" t="n"/>
-      <c r="D180" s="86" t="n"/>
-      <c r="E180" s="85" t="n"/>
-      <c r="F180" s="86" t="n"/>
-      <c r="G180" s="86" t="n"/>
-      <c r="H180" s="86" t="n"/>
-      <c r="I180" s="86" t="n"/>
-      <c r="J180" s="85" t="n"/>
-      <c r="K180" s="85" t="n"/>
-      <c r="L180" s="85" t="n"/>
-      <c r="M180" s="85" t="n"/>
-      <c r="N180" s="85" t="n"/>
-      <c r="O180" s="85" t="n"/>
-      <c r="P180" s="84">
-        <f>IF(C180="","",IF(OR(E180="",E180="未検証"),"① STEP1待ち",IF(E180="不通過","✕ STEP1不通過",IF(OR(G180="",H180=""),"② STEP2-3 未記入",IF(COUNTIF(J180:O180,"×")&gt;0,"✕ ボツ候補",IF(COUNTA(J180:O180)&lt;6,"③ STEP4 審査待ち",IF(COUNTIF(J180:O180,"△")&gt;0,"△ 修正して再審査","◎ 候補リスト")))))))</f>
-        <v/>
-      </c>
-      <c r="Q180" s="85" t="n"/>
-      <c r="R180" s="85" t="n"/>
-      <c r="S180" s="85" t="n"/>
-      <c r="T180" s="84">
-        <f>IF(COUNT(Q180:S180)&lt;3,"",Q180+(11-R180)+S180)</f>
-        <v/>
-      </c>
-      <c r="U180" s="85" t="n"/>
-      <c r="V180" s="86" t="n"/>
-      <c r="W180" s="87">
-        <f>IF(AND(P180="◎ 候補リスト",U180&lt;&gt;"ボツ",U180&lt;&gt;"制作済み",T180&lt;&gt;"",OR('②候補ランキング'!$C$5="すべて",B180='②候補ランキング'!$C$5)),IF('②候補ランキング'!$C$4="ワクワク",Q180,IF('②候補ランキング'!$C$4="手軽さ",11-R180,IF('②候補ランキング'!$C$4="確信度",S180,T180)))*1000+T180+(1000-A180)/10000,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="181" ht="18" customHeight="1" s="35">
-      <c r="A181" s="84">
-        <f>IF(C181="","",ROW()-5)</f>
-        <v/>
-      </c>
-      <c r="B181" s="85" t="n"/>
-      <c r="C181" s="86" t="n"/>
-      <c r="D181" s="86" t="n"/>
-      <c r="E181" s="85" t="n"/>
-      <c r="F181" s="86" t="n"/>
-      <c r="G181" s="86" t="n"/>
-      <c r="H181" s="86" t="n"/>
-      <c r="I181" s="86" t="n"/>
-      <c r="J181" s="85" t="n"/>
-      <c r="K181" s="85" t="n"/>
-      <c r="L181" s="85" t="n"/>
-      <c r="M181" s="85" t="n"/>
-      <c r="N181" s="85" t="n"/>
-      <c r="O181" s="85" t="n"/>
-      <c r="P181" s="84">
-        <f>IF(C181="","",IF(OR(E181="",E181="未検証"),"① STEP1待ち",IF(E181="不通過","✕ STEP1不通過",IF(OR(G181="",H181=""),"② STEP2-3 未記入",IF(COUNTIF(J181:O181,"×")&gt;0,"✕ ボツ候補",IF(COUNTA(J181:O181)&lt;6,"③ STEP4 審査待ち",IF(COUNTIF(J181:O181,"△")&gt;0,"△ 修正して再審査","◎ 候補リスト")))))))</f>
-        <v/>
-      </c>
-      <c r="Q181" s="85" t="n"/>
-      <c r="R181" s="85" t="n"/>
-      <c r="S181" s="85" t="n"/>
-      <c r="T181" s="84">
-        <f>IF(COUNT(Q181:S181)&lt;3,"",Q181+(11-R181)+S181)</f>
-        <v/>
-      </c>
-      <c r="U181" s="85" t="n"/>
-      <c r="V181" s="86" t="n"/>
-      <c r="W181" s="87">
-        <f>IF(AND(P181="◎ 候補リスト",U181&lt;&gt;"ボツ",U181&lt;&gt;"制作済み",T181&lt;&gt;"",OR('②候補ランキング'!$C$5="すべて",B181='②候補ランキング'!$C$5)),IF('②候補ランキング'!$C$4="ワクワク",Q181,IF('②候補ランキング'!$C$4="手軽さ",11-R181,IF('②候補ランキング'!$C$4="確信度",S181,T181)))*1000+T181+(1000-A181)/10000,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="182" ht="18" customHeight="1" s="35">
-      <c r="A182" s="84">
-        <f>IF(C182="","",ROW()-5)</f>
-        <v/>
-      </c>
-      <c r="B182" s="85" t="n"/>
-      <c r="C182" s="86" t="n"/>
-      <c r="D182" s="86" t="n"/>
-      <c r="E182" s="85" t="n"/>
-      <c r="F182" s="86" t="n"/>
-      <c r="G182" s="86" t="n"/>
-      <c r="H182" s="86" t="n"/>
-      <c r="I182" s="86" t="n"/>
-      <c r="J182" s="85" t="n"/>
-      <c r="K182" s="85" t="n"/>
-      <c r="L182" s="85" t="n"/>
-      <c r="M182" s="85" t="n"/>
-      <c r="N182" s="85" t="n"/>
-      <c r="O182" s="85" t="n"/>
-      <c r="P182" s="84">
-        <f>IF(C182="","",IF(OR(E182="",E182="未検証"),"① STEP1待ち",IF(E182="不通過","✕ STEP1不通過",IF(OR(G182="",H182=""),"② STEP2-3 未記入",IF(COUNTIF(J182:O182,"×")&gt;0,"✕ ボツ候補",IF(COUNTA(J182:O182)&lt;6,"③ STEP4 審査待ち",IF(COUNTIF(J182:O182,"△")&gt;0,"△ 修正して再審査","◎ 候補リスト")))))))</f>
-        <v/>
-      </c>
-      <c r="Q182" s="85" t="n"/>
-      <c r="R182" s="85" t="n"/>
-      <c r="S182" s="85" t="n"/>
-      <c r="T182" s="84">
-        <f>IF(COUNT(Q182:S182)&lt;3,"",Q182+(11-R182)+S182)</f>
-        <v/>
-      </c>
-      <c r="U182" s="85" t="n"/>
-      <c r="V182" s="86" t="n"/>
-      <c r="W182" s="87">
-        <f>IF(AND(P182="◎ 候補リスト",U182&lt;&gt;"ボツ",U182&lt;&gt;"制作済み",T182&lt;&gt;"",OR('②候補ランキング'!$C$5="すべて",B182='②候補ランキング'!$C$5)),IF('②候補ランキング'!$C$4="ワクワク",Q182,IF('②候補ランキング'!$C$4="手軽さ",11-R182,IF('②候補ランキング'!$C$4="確信度",S182,T182)))*1000+T182+(1000-A182)/10000,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="183" ht="18" customHeight="1" s="35">
-      <c r="A183" s="84">
-        <f>IF(C183="","",ROW()-5)</f>
-        <v/>
-      </c>
-      <c r="B183" s="85" t="n"/>
-      <c r="C183" s="86" t="n"/>
-      <c r="D183" s="86" t="n"/>
-      <c r="E183" s="85" t="n"/>
-      <c r="F183" s="86" t="n"/>
-      <c r="G183" s="86" t="n"/>
-      <c r="H183" s="86" t="n"/>
-      <c r="I183" s="86" t="n"/>
-      <c r="J183" s="85" t="n"/>
-      <c r="K183" s="85" t="n"/>
-      <c r="L183" s="85" t="n"/>
-      <c r="M183" s="85" t="n"/>
-      <c r="N183" s="85" t="n"/>
-      <c r="O183" s="85" t="n"/>
-      <c r="P183" s="84">
-        <f>IF(C183="","",IF(OR(E183="",E183="未検証"),"① STEP1待ち",IF(E183="不通過","✕ STEP1不通過",IF(OR(G183="",H183=""),"② STEP2-3 未記入",IF(COUNTIF(J183:O183,"×")&gt;0,"✕ ボツ候補",IF(COUNTA(J183:O183)&lt;6,"③ STEP4 審査待ち",IF(COUNTIF(J183:O183,"△")&gt;0,"△ 修正して再審査","◎ 候補リスト")))))))</f>
-        <v/>
-      </c>
-      <c r="Q183" s="85" t="n"/>
-      <c r="R183" s="85" t="n"/>
-      <c r="S183" s="85" t="n"/>
-      <c r="T183" s="84">
-        <f>IF(COUNT(Q183:S183)&lt;3,"",Q183+(11-R183)+S183)</f>
-        <v/>
-      </c>
-      <c r="U183" s="85" t="n"/>
-      <c r="V183" s="86" t="n"/>
-      <c r="W183" s="87">
-        <f>IF(AND(P183="◎ 候補リスト",U183&lt;&gt;"ボツ",U183&lt;&gt;"制作済み",T183&lt;&gt;"",OR('②候補ランキング'!$C$5="すべて",B183='②候補ランキング'!$C$5)),IF('②候補ランキング'!$C$4="ワクワク",Q183,IF('②候補ランキング'!$C$4="手軽さ",11-R183,IF('②候補ランキング'!$C$4="確信度",S183,T183)))*1000+T183+(1000-A183)/10000,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="184" ht="18" customHeight="1" s="35">
-      <c r="A184" s="84">
-        <f>IF(C184="","",ROW()-5)</f>
-        <v/>
-      </c>
-      <c r="B184" s="85" t="n"/>
-      <c r="C184" s="86" t="n"/>
-      <c r="D184" s="86" t="n"/>
-      <c r="E184" s="85" t="n"/>
-      <c r="F184" s="86" t="n"/>
-      <c r="G184" s="86" t="n"/>
-      <c r="H184" s="86" t="n"/>
-      <c r="I184" s="86" t="n"/>
-      <c r="J184" s="85" t="n"/>
-      <c r="K184" s="85" t="n"/>
-      <c r="L184" s="85" t="n"/>
-      <c r="M184" s="85" t="n"/>
-      <c r="N184" s="85" t="n"/>
-      <c r="O184" s="85" t="n"/>
-      <c r="P184" s="84">
-        <f>IF(C184="","",IF(OR(E184="",E184="未検証"),"① STEP1待ち",IF(E184="不通過","✕ STEP1不通過",IF(OR(G184="",H184=""),"② STEP2-3 未記入",IF(COUNTIF(J184:O184,"×")&gt;0,"✕ ボツ候補",IF(COUNTA(J184:O184)&lt;6,"③ STEP4 審査待ち",IF(COUNTIF(J184:O184,"△")&gt;0,"△ 修正して再審査","◎ 候補リスト")))))))</f>
-        <v/>
-      </c>
-      <c r="Q184" s="85" t="n"/>
-      <c r="R184" s="85" t="n"/>
-      <c r="S184" s="85" t="n"/>
-      <c r="T184" s="84">
-        <f>IF(COUNT(Q184:S184)&lt;3,"",Q184+(11-R184)+S184)</f>
-        <v/>
-      </c>
-      <c r="U184" s="85" t="n"/>
-      <c r="V184" s="86" t="n"/>
-      <c r="W184" s="87">
-        <f>IF(AND(P184="◎ 候補リスト",U184&lt;&gt;"ボツ",U184&lt;&gt;"制作済み",T184&lt;&gt;"",OR('②候補ランキング'!$C$5="すべて",B184='②候補ランキング'!$C$5)),IF('②候補ランキング'!$C$4="ワクワク",Q184,IF('②候補ランキング'!$C$4="手軽さ",11-R184,IF('②候補ランキング'!$C$4="確信度",S184,T184)))*1000+T184+(1000-A184)/10000,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="185" ht="18" customHeight="1" s="35">
-      <c r="A185" s="84">
-        <f>IF(C185="","",ROW()-5)</f>
-        <v/>
-      </c>
-      <c r="B185" s="85" t="n"/>
-      <c r="C185" s="86" t="n"/>
-      <c r="D185" s="86" t="n"/>
-      <c r="E185" s="85" t="n"/>
-      <c r="F185" s="86" t="n"/>
-      <c r="G185" s="86" t="n"/>
-      <c r="H185" s="86" t="n"/>
-      <c r="I185" s="86" t="n"/>
-      <c r="J185" s="85" t="n"/>
-      <c r="K185" s="85" t="n"/>
-      <c r="L185" s="85" t="n"/>
-      <c r="M185" s="85" t="n"/>
-      <c r="N185" s="85" t="n"/>
-      <c r="O185" s="85" t="n"/>
-      <c r="P185" s="84">
-        <f>IF(C185="","",IF(OR(E185="",E185="未検証"),"① STEP1待ち",IF(E185="不通過","✕ STEP1不通過",IF(OR(G185="",H185=""),"② STEP2-3 未記入",IF(COUNTIF(J185:O185,"×")&gt;0,"✕ ボツ候補",IF(COUNTA(J185:O185)&lt;6,"③ STEP4 審査待ち",IF(COUNTIF(J185:O185,"△")&gt;0,"△ 修正して再審査","◎ 候補リスト")))))))</f>
-        <v/>
-      </c>
-      <c r="Q185" s="85" t="n"/>
-      <c r="R185" s="85" t="n"/>
-      <c r="S185" s="85" t="n"/>
-      <c r="T185" s="84">
-        <f>IF(COUNT(Q185:S185)&lt;3,"",Q185+(11-R185)+S185)</f>
-        <v/>
-      </c>
-      <c r="U185" s="85" t="n"/>
-      <c r="V185" s="86" t="n"/>
-      <c r="W185" s="87">
-        <f>IF(AND(P185="◎ 候補リスト",U185&lt;&gt;"ボツ",U185&lt;&gt;"制作済み",T185&lt;&gt;"",OR('②候補ランキング'!$C$5="すべて",B185='②候補ランキング'!$C$5)),IF('②候補ランキング'!$C$4="ワクワク",Q185,IF('②候補ランキング'!$C$4="手軽さ",11-R185,IF('②候補ランキング'!$C$4="確信度",S185,T185)))*1000+T185+(1000-A185)/10000,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="186" ht="18" customHeight="1" s="35">
-      <c r="A186" s="84">
-        <f>IF(C186="","",ROW()-5)</f>
-        <v/>
-      </c>
-      <c r="B186" s="85" t="n"/>
-      <c r="C186" s="86" t="n"/>
-      <c r="D186" s="86" t="n"/>
-      <c r="E186" s="85" t="n"/>
-      <c r="F186" s="86" t="n"/>
-      <c r="G186" s="86" t="n"/>
-      <c r="H186" s="86" t="n"/>
-      <c r="I186" s="86" t="n"/>
-      <c r="J186" s="85" t="n"/>
-      <c r="K186" s="85" t="n"/>
-      <c r="L186" s="85" t="n"/>
-      <c r="M186" s="85" t="n"/>
-      <c r="N186" s="85" t="n"/>
-      <c r="O186" s="85" t="n"/>
-      <c r="P186" s="84">
-        <f>IF(C186="","",IF(OR(E186="",E186="未検証"),"① STEP1待ち",IF(E186="不通過","✕ STEP1不通過",IF(OR(G186="",H186=""),"② STEP2-3 未記入",IF(COUNTIF(J186:O186,"×")&gt;0,"✕ ボツ候補",IF(COUNTA(J186:O186)&lt;6,"③ STEP4 審査待ち",IF(COUNTIF(J186:O186,"△")&gt;0,"△ 修正して再審査","◎ 候補リスト")))))))</f>
-        <v/>
-      </c>
-      <c r="Q186" s="85" t="n"/>
-      <c r="R186" s="85" t="n"/>
-      <c r="S186" s="85" t="n"/>
-      <c r="T186" s="84">
-        <f>IF(COUNT(Q186:S186)&lt;3,"",Q186+(11-R186)+S186)</f>
-        <v/>
-      </c>
-      <c r="U186" s="85" t="n"/>
-      <c r="V186" s="86" t="n"/>
-      <c r="W186" s="87">
-        <f>IF(AND(P186="◎ 候補リスト",U186&lt;&gt;"ボツ",U186&lt;&gt;"制作済み",T186&lt;&gt;"",OR('②候補ランキング'!$C$5="すべて",B186='②候補ランキング'!$C$5)),IF('②候補ランキング'!$C$4="ワクワク",Q186,IF('②候補ランキング'!$C$4="手軽さ",11-R186,IF('②候補ランキング'!$C$4="確信度",S186,T186)))*1000+T186+(1000-A186)/10000,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="187" ht="18" customHeight="1" s="35">
-      <c r="A187" s="84">
-        <f>IF(C187="","",ROW()-5)</f>
-        <v/>
-      </c>
-      <c r="B187" s="85" t="n"/>
-      <c r="C187" s="86" t="n"/>
-      <c r="D187" s="86" t="n"/>
-      <c r="E187" s="85" t="n"/>
-      <c r="F187" s="86" t="n"/>
-      <c r="G187" s="86" t="n"/>
-      <c r="H187" s="86" t="n"/>
-      <c r="I187" s="86" t="n"/>
-      <c r="J187" s="85" t="n"/>
-      <c r="K187" s="85" t="n"/>
-      <c r="L187" s="85" t="n"/>
-      <c r="M187" s="85" t="n"/>
-      <c r="N187" s="85" t="n"/>
-      <c r="O187" s="85" t="n"/>
-      <c r="P187" s="84">
-        <f>IF(C187="","",IF(OR(E187="",E187="未検証"),"① STEP1待ち",IF(E187="不通過","✕ STEP1不通過",IF(OR(G187="",H187=""),"② STEP2-3 未記入",IF(COUNTIF(J187:O187,"×")&gt;0,"✕ ボツ候補",IF(COUNTA(J187:O187)&lt;6,"③ STEP4 審査待ち",IF(COUNTIF(J187:O187,"△")&gt;0,"△ 修正して再審査","◎ 候補リスト")))))))</f>
-        <v/>
-      </c>
-      <c r="Q187" s="85" t="n"/>
-      <c r="R187" s="85" t="n"/>
-      <c r="S187" s="85" t="n"/>
-      <c r="T187" s="84">
-        <f>IF(COUNT(Q187:S187)&lt;3,"",Q187+(11-R187)+S187)</f>
-        <v/>
-      </c>
-      <c r="U187" s="85" t="n"/>
-      <c r="V187" s="86" t="n"/>
-      <c r="W187" s="87">
-        <f>IF(AND(P187="◎ 候補リスト",U187&lt;&gt;"ボツ",U187&lt;&gt;"制作済み",T187&lt;&gt;"",OR('②候補ランキング'!$C$5="すべて",B187='②候補ランキング'!$C$5)),IF('②候補ランキング'!$C$4="ワクワク",Q187,IF('②候補ランキング'!$C$4="手軽さ",11-R187,IF('②候補ランキング'!$C$4="確信度",S187,T187)))*1000+T187+(1000-A187)/10000,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="188" ht="18" customHeight="1" s="35">
-      <c r="A188" s="84">
-        <f>IF(C188="","",ROW()-5)</f>
-        <v/>
-      </c>
-      <c r="B188" s="85" t="n"/>
-      <c r="C188" s="86" t="n"/>
-      <c r="D188" s="86" t="n"/>
-      <c r="E188" s="85" t="n"/>
-      <c r="F188" s="86" t="n"/>
-      <c r="G188" s="86" t="n"/>
-      <c r="H188" s="86" t="n"/>
-      <c r="I188" s="86" t="n"/>
-      <c r="J188" s="85" t="n"/>
-      <c r="K188" s="85" t="n"/>
-      <c r="L188" s="85" t="n"/>
-      <c r="M188" s="85" t="n"/>
-      <c r="N188" s="85" t="n"/>
-      <c r="O188" s="85" t="n"/>
-      <c r="P188" s="84">
-        <f>IF(C188="","",IF(OR(E188="",E188="未検証"),"① STEP1待ち",IF(E188="不通過","✕ STEP1不通過",IF(OR(G188="",H188=""),"② STEP2-3 未記入",IF(COUNTIF(J188:O188,"×")&gt;0,"✕ ボツ候補",IF(COUNTA(J188:O188)&lt;6,"③ STEP4 審査待ち",IF(COUNTIF(J188:O188,"△")&gt;0,"△ 修正して再審査","◎ 候補リスト")))))))</f>
-        <v/>
-      </c>
-      <c r="Q188" s="85" t="n"/>
-      <c r="R188" s="85" t="n"/>
-      <c r="S188" s="85" t="n"/>
-      <c r="T188" s="84">
-        <f>IF(COUNT(Q188:S188)&lt;3,"",Q188+(11-R188)+S188)</f>
-        <v/>
-      </c>
-      <c r="U188" s="85" t="n"/>
-      <c r="V188" s="86" t="n"/>
-      <c r="W188" s="87">
-        <f>IF(AND(P188="◎ 候補リスト",U188&lt;&gt;"ボツ",U188&lt;&gt;"制作済み",T188&lt;&gt;"",OR('②候補ランキング'!$C$5="すべて",B188='②候補ランキング'!$C$5)),IF('②候補ランキング'!$C$4="ワクワク",Q188,IF('②候補ランキング'!$C$4="手軽さ",11-R188,IF('②候補ランキング'!$C$4="確信度",S188,T188)))*1000+T188+(1000-A188)/10000,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="189" ht="18" customHeight="1" s="35">
-      <c r="A189" s="84">
-        <f>IF(C189="","",ROW()-5)</f>
-        <v/>
-      </c>
-      <c r="B189" s="85" t="n"/>
-      <c r="C189" s="86" t="n"/>
-      <c r="D189" s="86" t="n"/>
-      <c r="E189" s="85" t="n"/>
-      <c r="F189" s="86" t="n"/>
-      <c r="G189" s="86" t="n"/>
-      <c r="H189" s="86" t="n"/>
-      <c r="I189" s="86" t="n"/>
-      <c r="J189" s="85" t="n"/>
-      <c r="K189" s="85" t="n"/>
-      <c r="L189" s="85" t="n"/>
-      <c r="M189" s="85" t="n"/>
-      <c r="N189" s="85" t="n"/>
-      <c r="O189" s="85" t="n"/>
-      <c r="P189" s="84">
-        <f>IF(C189="","",IF(OR(E189="",E189="未検証"),"① STEP1待ち",IF(E189="不通過","✕ STEP1不通過",IF(OR(G189="",H189=""),"② STEP2-3 未記入",IF(COUNTIF(J189:O189,"×")&gt;0,"✕ ボツ候補",IF(COUNTA(J189:O189)&lt;6,"③ STEP4 審査待ち",IF(COUNTIF(J189:O189,"△")&gt;0,"△ 修正して再審査","◎ 候補リスト")))))))</f>
-        <v/>
-      </c>
-      <c r="Q189" s="85" t="n"/>
-      <c r="R189" s="85" t="n"/>
-      <c r="S189" s="85" t="n"/>
-      <c r="T189" s="84">
-        <f>IF(COUNT(Q189:S189)&lt;3,"",Q189+(11-R189)+S189)</f>
-        <v/>
-      </c>
-      <c r="U189" s="85" t="n"/>
-      <c r="V189" s="86" t="n"/>
-      <c r="W189" s="87">
-        <f>IF(AND(P189="◎ 候補リスト",U189&lt;&gt;"ボツ",U189&lt;&gt;"制作済み",T189&lt;&gt;"",OR('②候補ランキング'!$C$5="すべて",B189='②候補ランキング'!$C$5)),IF('②候補ランキング'!$C$4="ワクワク",Q189,IF('②候補ランキング'!$C$4="手軽さ",11-R189,IF('②候補ランキング'!$C$4="確信度",S189,T189)))*1000+T189+(1000-A189)/10000,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="190" ht="18" customHeight="1" s="35">
-      <c r="A190" s="84">
-        <f>IF(C190="","",ROW()-5)</f>
-        <v/>
-      </c>
-      <c r="B190" s="85" t="n"/>
-      <c r="C190" s="86" t="n"/>
-      <c r="D190" s="86" t="n"/>
-      <c r="E190" s="85" t="n"/>
-      <c r="F190" s="86" t="n"/>
-      <c r="G190" s="86" t="n"/>
-      <c r="H190" s="86" t="n"/>
-      <c r="I190" s="86" t="n"/>
-      <c r="J190" s="85" t="n"/>
-      <c r="K190" s="85" t="n"/>
-      <c r="L190" s="85" t="n"/>
-      <c r="M190" s="85" t="n"/>
-      <c r="N190" s="85" t="n"/>
-      <c r="O190" s="85" t="n"/>
-      <c r="P190" s="84">
-        <f>IF(C190="","",IF(OR(E190="",E190="未検証"),"① STEP1待ち",IF(E190="不通過","✕ STEP1不通過",IF(OR(G190="",H190=""),"② STEP2-3 未記入",IF(COUNTIF(J190:O190,"×")&gt;0,"✕ ボツ候補",IF(COUNTA(J190:O190)&lt;6,"③ STEP4 審査待ち",IF(COUNTIF(J190:O190,"△")&gt;0,"△ 修正して再審査","◎ 候補リスト")))))))</f>
-        <v/>
-      </c>
-      <c r="Q190" s="85" t="n"/>
-      <c r="R190" s="85" t="n"/>
-      <c r="S190" s="85" t="n"/>
-      <c r="T190" s="84">
-        <f>IF(COUNT(Q190:S190)&lt;3,"",Q190+(11-R190)+S190)</f>
-        <v/>
-      </c>
-      <c r="U190" s="85" t="n"/>
-      <c r="V190" s="86" t="n"/>
-      <c r="W190" s="87">
-        <f>IF(AND(P190="◎ 候補リスト",U190&lt;&gt;"ボツ",U190&lt;&gt;"制作済み",T190&lt;&gt;"",OR('②候補ランキング'!$C$5="すべて",B190='②候補ランキング'!$C$5)),IF('②候補ランキング'!$C$4="ワクワク",Q190,IF('②候補ランキング'!$C$4="手軽さ",11-R190,IF('②候補ランキング'!$C$4="確信度",S190,T190)))*1000+T190+(1000-A190)/10000,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="191" ht="18" customHeight="1" s="35">
-      <c r="A191" s="84">
-        <f>IF(C191="","",ROW()-5)</f>
-        <v/>
-      </c>
-      <c r="B191" s="85" t="n"/>
-      <c r="C191" s="86" t="n"/>
-      <c r="D191" s="86" t="n"/>
-      <c r="E191" s="85" t="n"/>
-      <c r="F191" s="86" t="n"/>
-      <c r="G191" s="86" t="n"/>
-      <c r="H191" s="86" t="n"/>
-      <c r="I191" s="86" t="n"/>
-      <c r="J191" s="85" t="n"/>
-      <c r="K191" s="85" t="n"/>
-      <c r="L191" s="85" t="n"/>
-      <c r="M191" s="85" t="n"/>
-      <c r="N191" s="85" t="n"/>
-      <c r="O191" s="85" t="n"/>
-      <c r="P191" s="84">
-        <f>IF(C191="","",IF(OR(E191="",E191="未検証"),"① STEP1待ち",IF(E191="不通過","✕ STEP1不通過",IF(OR(G191="",H191=""),"② STEP2-3 未記入",IF(COUNTIF(J191:O191,"×")&gt;0,"✕ ボツ候補",IF(COUNTA(J191:O191)&lt;6,"③ STEP4 審査待ち",IF(COUNTIF(J191:O191,"△")&gt;0,"△ 修正して再審査","◎ 候補リスト")))))))</f>
-        <v/>
-      </c>
-      <c r="Q191" s="85" t="n"/>
-      <c r="R191" s="85" t="n"/>
-      <c r="S191" s="85" t="n"/>
-      <c r="T191" s="84">
-        <f>IF(COUNT(Q191:S191)&lt;3,"",Q191+(11-R191)+S191)</f>
-        <v/>
-      </c>
-      <c r="U191" s="85" t="n"/>
-      <c r="V191" s="86" t="n"/>
-      <c r="W191" s="87">
-        <f>IF(AND(P191="◎ 候補リスト",U191&lt;&gt;"ボツ",U191&lt;&gt;"制作済み",T191&lt;&gt;"",OR('②候補ランキング'!$C$5="すべて",B191='②候補ランキング'!$C$5)),IF('②候補ランキング'!$C$4="ワクワク",Q191,IF('②候補ランキング'!$C$4="手軽さ",11-R191,IF('②候補ランキング'!$C$4="確信度",S191,T191)))*1000+T191+(1000-A191)/10000,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="192" ht="18" customHeight="1" s="35">
-      <c r="A192" s="84">
-        <f>IF(C192="","",ROW()-5)</f>
-        <v/>
-      </c>
-      <c r="B192" s="85" t="n"/>
-      <c r="C192" s="86" t="n"/>
-      <c r="D192" s="86" t="n"/>
-      <c r="E192" s="85" t="n"/>
-      <c r="F192" s="86" t="n"/>
-      <c r="G192" s="86" t="n"/>
-      <c r="H192" s="86" t="n"/>
-      <c r="I192" s="86" t="n"/>
-      <c r="J192" s="85" t="n"/>
-      <c r="K192" s="85" t="n"/>
-      <c r="L192" s="85" t="n"/>
-      <c r="M192" s="85" t="n"/>
-      <c r="N192" s="85" t="n"/>
-      <c r="O192" s="85" t="n"/>
-      <c r="P192" s="84">
-        <f>IF(C192="","",IF(OR(E192="",E192="未検証"),"① STEP1待ち",IF(E192="不通過","✕ STEP1不通過",IF(OR(G192="",H192=""),"② STEP2-3 未記入",IF(COUNTIF(J192:O192,"×")&gt;0,"✕ ボツ候補",IF(COUNTA(J192:O192)&lt;6,"③ STEP4 審査待ち",IF(COUNTIF(J192:O192,"△")&gt;0,"△ 修正して再審査","◎ 候補リスト")))))))</f>
-        <v/>
-      </c>
-      <c r="Q192" s="85" t="n"/>
-      <c r="R192" s="85" t="n"/>
-      <c r="S192" s="85" t="n"/>
-      <c r="T192" s="84">
-        <f>IF(COUNT(Q192:S192)&lt;3,"",Q192+(11-R192)+S192)</f>
-        <v/>
-      </c>
-      <c r="U192" s="85" t="n"/>
-      <c r="V192" s="86" t="n"/>
-      <c r="W192" s="87">
-        <f>IF(AND(P192="◎ 候補リスト",U192&lt;&gt;"ボツ",U192&lt;&gt;"制作済み",T192&lt;&gt;"",OR('②候補ランキング'!$C$5="すべて",B192='②候補ランキング'!$C$5)),IF('②候補ランキング'!$C$4="ワクワク",Q192,IF('②候補ランキング'!$C$4="手軽さ",11-R192,IF('②候補ランキング'!$C$4="確信度",S192,T192)))*1000+T192+(1000-A192)/10000,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="193" ht="18" customHeight="1" s="35">
-      <c r="A193" s="84">
-        <f>IF(C193="","",ROW()-5)</f>
-        <v/>
-      </c>
-      <c r="B193" s="85" t="n"/>
-      <c r="C193" s="86" t="n"/>
-      <c r="D193" s="86" t="n"/>
-      <c r="E193" s="85" t="n"/>
-      <c r="F193" s="86" t="n"/>
-      <c r="G193" s="86" t="n"/>
-      <c r="H193" s="86" t="n"/>
-      <c r="I193" s="86" t="n"/>
-      <c r="J193" s="85" t="n"/>
-      <c r="K193" s="85" t="n"/>
-      <c r="L193" s="85" t="n"/>
-      <c r="M193" s="85" t="n"/>
-      <c r="N193" s="85" t="n"/>
-      <c r="O193" s="85" t="n"/>
-      <c r="P193" s="84">
-        <f>IF(C193="","",IF(OR(E193="",E193="未検証"),"① STEP1待ち",IF(E193="不通過","✕ STEP1不通過",IF(OR(G193="",H193=""),"② STEP2-3 未記入",IF(COUNTIF(J193:O193,"×")&gt;0,"✕ ボツ候補",IF(COUNTA(J193:O193)&lt;6,"③ STEP4 審査待ち",IF(COUNTIF(J193:O193,"△")&gt;0,"△ 修正して再審査","◎ 候補リスト")))))))</f>
-        <v/>
-      </c>
-      <c r="Q193" s="85" t="n"/>
-      <c r="R193" s="85" t="n"/>
-      <c r="S193" s="85" t="n"/>
-      <c r="T193" s="84">
-        <f>IF(COUNT(Q193:S193)&lt;3,"",Q193+(11-R193)+S193)</f>
-        <v/>
-      </c>
-      <c r="U193" s="85" t="n"/>
-      <c r="V193" s="86" t="n"/>
-      <c r="W193" s="87">
-        <f>IF(AND(P193="◎ 候補リスト",U193&lt;&gt;"ボツ",U193&lt;&gt;"制作済み",T193&lt;&gt;"",OR('②候補ランキング'!$C$5="すべて",B193='②候補ランキング'!$C$5)),IF('②候補ランキング'!$C$4="ワクワク",Q193,IF('②候補ランキング'!$C$4="手軽さ",11-R193,IF('②候補ランキング'!$C$4="確信度",S193,T193)))*1000+T193+(1000-A193)/10000,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="194" ht="18" customHeight="1" s="35">
-      <c r="A194" s="84">
-        <f>IF(C194="","",ROW()-5)</f>
-        <v/>
-      </c>
-      <c r="B194" s="85" t="n"/>
-      <c r="C194" s="86" t="n"/>
-      <c r="D194" s="86" t="n"/>
-      <c r="E194" s="85" t="n"/>
-      <c r="F194" s="86" t="n"/>
-      <c r="G194" s="86" t="n"/>
-      <c r="H194" s="86" t="n"/>
-      <c r="I194" s="86" t="n"/>
-      <c r="J194" s="85" t="n"/>
-      <c r="K194" s="85" t="n"/>
-      <c r="L194" s="85" t="n"/>
-      <c r="M194" s="85" t="n"/>
-      <c r="N194" s="85" t="n"/>
-      <c r="O194" s="85" t="n"/>
-      <c r="P194" s="84">
-        <f>IF(C194="","",IF(OR(E194="",E194="未検証"),"① STEP1待ち",IF(E194="不通過","✕ STEP1不通過",IF(OR(G194="",H194=""),"② STEP2-3 未記入",IF(COUNTIF(J194:O194,"×")&gt;0,"✕ ボツ候補",IF(COUNTA(J194:O194)&lt;6,"③ STEP4 審査待ち",IF(COUNTIF(J194:O194,"△")&gt;0,"△ 修正して再審査","◎ 候補リスト")))))))</f>
-        <v/>
-      </c>
-      <c r="Q194" s="85" t="n"/>
-      <c r="R194" s="85" t="n"/>
-      <c r="S194" s="85" t="n"/>
-      <c r="T194" s="84">
-        <f>IF(COUNT(Q194:S194)&lt;3,"",Q194+(11-R194)+S194)</f>
-        <v/>
-      </c>
-      <c r="U194" s="85" t="n"/>
-      <c r="V194" s="86" t="n"/>
-      <c r="W194" s="87">
-        <f>IF(AND(P194="◎ 候補リスト",U194&lt;&gt;"ボツ",U194&lt;&gt;"制作済み",T194&lt;&gt;"",OR('②候補ランキング'!$C$5="すべて",B194='②候補ランキング'!$C$5)),IF('②候補ランキング'!$C$4="ワクワク",Q194,IF('②候補ランキング'!$C$4="手軽さ",11-R194,IF('②候補ランキング'!$C$4="確信度",S194,T194)))*1000+T194+(1000-A194)/10000,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="195" ht="18" customHeight="1" s="35">
-      <c r="A195" s="84">
-        <f>IF(C195="","",ROW()-5)</f>
-        <v/>
-      </c>
-      <c r="B195" s="85" t="n"/>
-      <c r="C195" s="86" t="n"/>
-      <c r="D195" s="86" t="n"/>
-      <c r="E195" s="85" t="n"/>
-      <c r="F195" s="86" t="n"/>
-      <c r="G195" s="86" t="n"/>
-      <c r="H195" s="86" t="n"/>
-      <c r="I195" s="86" t="n"/>
-      <c r="J195" s="85" t="n"/>
-      <c r="K195" s="85" t="n"/>
-      <c r="L195" s="85" t="n"/>
-      <c r="M195" s="85" t="n"/>
-      <c r="N195" s="85" t="n"/>
-      <c r="O195" s="85" t="n"/>
-      <c r="P195" s="84">
-        <f>IF(C195="","",IF(OR(E195="",E195="未検証"),"① STEP1待ち",IF(E195="不通過","✕ STEP1不通過",IF(OR(G195="",H195=""),"② STEP2-3 未記入",IF(COUNTIF(J195:O195,"×")&gt;0,"✕ ボツ候補",IF(COUNTA(J195:O195)&lt;6,"③ STEP4 審査待ち",IF(COUNTIF(J195:O195,"△")&gt;0,"△ 修正して再審査","◎ 候補リスト")))))))</f>
-        <v/>
-      </c>
-      <c r="Q195" s="85" t="n"/>
-      <c r="R195" s="85" t="n"/>
-      <c r="S195" s="85" t="n"/>
-      <c r="T195" s="84">
-        <f>IF(COUNT(Q195:S195)&lt;3,"",Q195+(11-R195)+S195)</f>
-        <v/>
-      </c>
-      <c r="U195" s="85" t="n"/>
-      <c r="V195" s="86" t="n"/>
-      <c r="W195" s="87">
-        <f>IF(AND(P195="◎ 候補リスト",U195&lt;&gt;"ボツ",U195&lt;&gt;"制作済み",T195&lt;&gt;"",OR('②候補ランキング'!$C$5="すべて",B195='②候補ランキング'!$C$5)),IF('②候補ランキング'!$C$4="ワクワク",Q195,IF('②候補ランキング'!$C$4="手軽さ",11-R195,IF('②候補ランキング'!$C$4="確信度",S195,T195)))*1000+T195+(1000-A195)/10000,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="196" ht="18" customHeight="1" s="35">
-      <c r="A196" s="84">
-        <f>IF(C196="","",ROW()-5)</f>
-        <v/>
-      </c>
-      <c r="B196" s="85" t="n"/>
-      <c r="C196" s="86" t="n"/>
-      <c r="D196" s="86" t="n"/>
-      <c r="E196" s="85" t="n"/>
-      <c r="F196" s="86" t="n"/>
-      <c r="G196" s="86" t="n"/>
-      <c r="H196" s="86" t="n"/>
-      <c r="I196" s="86" t="n"/>
-      <c r="J196" s="85" t="n"/>
-      <c r="K196" s="85" t="n"/>
-      <c r="L196" s="85" t="n"/>
-      <c r="M196" s="85" t="n"/>
-      <c r="N196" s="85" t="n"/>
-      <c r="O196" s="85" t="n"/>
-      <c r="P196" s="84">
-        <f>IF(C196="","",IF(OR(E196="",E196="未検証"),"① STEP1待ち",IF(E196="不通過","✕ STEP1不通過",IF(OR(G196="",H196=""),"② STEP2-3 未記入",IF(COUNTIF(J196:O196,"×")&gt;0,"✕ ボツ候補",IF(COUNTA(J196:O196)&lt;6,"③ STEP4 審査待ち",IF(COUNTIF(J196:O196,"△")&gt;0,"△ 修正して再審査","◎ 候補リスト")))))))</f>
-        <v/>
-      </c>
-      <c r="Q196" s="85" t="n"/>
-      <c r="R196" s="85" t="n"/>
-      <c r="S196" s="85" t="n"/>
-      <c r="T196" s="84">
-        <f>IF(COUNT(Q196:S196)&lt;3,"",Q196+(11-R196)+S196)</f>
-        <v/>
-      </c>
-      <c r="U196" s="85" t="n"/>
-      <c r="V196" s="86" t="n"/>
-      <c r="W196" s="87">
-        <f>IF(AND(P196="◎ 候補リスト",U196&lt;&gt;"ボツ",U196&lt;&gt;"制作済み",T196&lt;&gt;"",OR('②候補ランキング'!$C$5="すべて",B196='②候補ランキング'!$C$5)),IF('②候補ランキング'!$C$4="ワクワク",Q196,IF('②候補ランキング'!$C$4="手軽さ",11-R196,IF('②候補ランキング'!$C$4="確信度",S196,T196)))*1000+T196+(1000-A196)/10000,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="197" ht="18" customHeight="1" s="35">
-      <c r="A197" s="84">
-        <f>IF(C197="","",ROW()-5)</f>
-        <v/>
-      </c>
-      <c r="B197" s="85" t="n"/>
-      <c r="C197" s="86" t="n"/>
-      <c r="D197" s="86" t="n"/>
-      <c r="E197" s="85" t="n"/>
-      <c r="F197" s="86" t="n"/>
-      <c r="G197" s="86" t="n"/>
-      <c r="H197" s="86" t="n"/>
-      <c r="I197" s="86" t="n"/>
-      <c r="J197" s="85" t="n"/>
-      <c r="K197" s="85" t="n"/>
-      <c r="L197" s="85" t="n"/>
-      <c r="M197" s="85" t="n"/>
-      <c r="N197" s="85" t="n"/>
-      <c r="O197" s="85" t="n"/>
-      <c r="P197" s="84">
-        <f>IF(C197="","",IF(OR(E197="",E197="未検証"),"① STEP1待ち",IF(E197="不通過","✕ STEP1不通過",IF(OR(G197="",H197=""),"② STEP2-3 未記入",IF(COUNTIF(J197:O197,"×")&gt;0,"✕ ボツ候補",IF(COUNTA(J197:O197)&lt;6,"③ STEP4 審査待ち",IF(COUNTIF(J197:O197,"△")&gt;0,"△ 修正して再審査","◎ 候補リスト")))))))</f>
-        <v/>
-      </c>
-      <c r="Q197" s="85" t="n"/>
-      <c r="R197" s="85" t="n"/>
-      <c r="S197" s="85" t="n"/>
-      <c r="T197" s="84">
-        <f>IF(COUNT(Q197:S197)&lt;3,"",Q197+(11-R197)+S197)</f>
-        <v/>
-      </c>
-      <c r="U197" s="85" t="n"/>
-      <c r="V197" s="86" t="n"/>
-      <c r="W197" s="87">
-        <f>IF(AND(P197="◎ 候補リスト",U197&lt;&gt;"ボツ",U197&lt;&gt;"制作済み",T197&lt;&gt;"",OR('②候補ランキング'!$C$5="すべて",B197='②候補ランキング'!$C$5)),IF('②候補ランキング'!$C$4="ワクワク",Q197,IF('②候補ランキング'!$C$4="手軽さ",11-R197,IF('②候補ランキング'!$C$4="確信度",S197,T197)))*1000+T197+(1000-A197)/10000,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="198" ht="18" customHeight="1" s="35">
-      <c r="A198" s="84">
-        <f>IF(C198="","",ROW()-5)</f>
-        <v/>
-      </c>
-      <c r="B198" s="85" t="n"/>
-      <c r="C198" s="86" t="n"/>
-      <c r="D198" s="86" t="n"/>
-      <c r="E198" s="85" t="n"/>
-      <c r="F198" s="86" t="n"/>
-      <c r="G198" s="86" t="n"/>
-      <c r="H198" s="86" t="n"/>
-      <c r="I198" s="86" t="n"/>
-      <c r="J198" s="85" t="n"/>
-      <c r="K198" s="85" t="n"/>
-      <c r="L198" s="85" t="n"/>
-      <c r="M198" s="85" t="n"/>
-      <c r="N198" s="85" t="n"/>
-      <c r="O198" s="85" t="n"/>
-      <c r="P198" s="84">
-        <f>IF(C198="","",IF(OR(E198="",E198="未検証"),"① STEP1待ち",IF(E198="不通過","✕ STEP1不通過",IF(OR(G198="",H198=""),"② STEP2-3 未記入",IF(COUNTIF(J198:O198,"×")&gt;0,"✕ ボツ候補",IF(COUNTA(J198:O198)&lt;6,"③ STEP4 審査待ち",IF(COUNTIF(J198:O198,"△")&gt;0,"△ 修正して再審査","◎ 候補リスト")))))))</f>
-        <v/>
-      </c>
-      <c r="Q198" s="85" t="n"/>
-      <c r="R198" s="85" t="n"/>
-      <c r="S198" s="85" t="n"/>
-      <c r="T198" s="84">
-        <f>IF(COUNT(Q198:S198)&lt;3,"",Q198+(11-R198)+S198)</f>
-        <v/>
-      </c>
-      <c r="U198" s="85" t="n"/>
-      <c r="V198" s="86" t="n"/>
-      <c r="W198" s="87">
-        <f>IF(AND(P198="◎ 候補リスト",U198&lt;&gt;"ボツ",U198&lt;&gt;"制作済み",T198&lt;&gt;"",OR('②候補ランキング'!$C$5="すべて",B198='②候補ランキング'!$C$5)),IF('②候補ランキング'!$C$4="ワクワク",Q198,IF('②候補ランキング'!$C$4="手軽さ",11-R198,IF('②候補ランキング'!$C$4="確信度",S198,T198)))*1000+T198+(1000-A198)/10000,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="199" ht="18" customHeight="1" s="35">
-      <c r="A199" s="84">
-        <f>IF(C199="","",ROW()-5)</f>
-        <v/>
-      </c>
-      <c r="B199" s="85" t="n"/>
-      <c r="C199" s="86" t="n"/>
-      <c r="D199" s="86" t="n"/>
-      <c r="E199" s="85" t="n"/>
-      <c r="F199" s="86" t="n"/>
-      <c r="G199" s="86" t="n"/>
-      <c r="H199" s="86" t="n"/>
-      <c r="I199" s="86" t="n"/>
-      <c r="J199" s="85" t="n"/>
-      <c r="K199" s="85" t="n"/>
-      <c r="L199" s="85" t="n"/>
-      <c r="M199" s="85" t="n"/>
-      <c r="N199" s="85" t="n"/>
-      <c r="O199" s="85" t="n"/>
-      <c r="P199" s="84">
-        <f>IF(C199="","",IF(OR(E199="",E199="未検証"),"① STEP1待ち",IF(E199="不通過","✕ STEP1不通過",IF(OR(G199="",H199=""),"② STEP2-3 未記入",IF(COUNTIF(J199:O199,"×")&gt;0,"✕ ボツ候補",IF(COUNTA(J199:O199)&lt;6,"③ STEP4 審査待ち",IF(COUNTIF(J199:O199,"△")&gt;0,"△ 修正して再審査","◎ 候補リスト")))))))</f>
-        <v/>
-      </c>
-      <c r="Q199" s="85" t="n"/>
-      <c r="R199" s="85" t="n"/>
-      <c r="S199" s="85" t="n"/>
-      <c r="T199" s="84">
-        <f>IF(COUNT(Q199:S199)&lt;3,"",Q199+(11-R199)+S199)</f>
-        <v/>
-      </c>
-      <c r="U199" s="85" t="n"/>
-      <c r="V199" s="86" t="n"/>
-      <c r="W199" s="87">
-        <f>IF(AND(P199="◎ 候補リスト",U199&lt;&gt;"ボツ",U199&lt;&gt;"制作済み",T199&lt;&gt;"",OR('②候補ランキング'!$C$5="すべて",B199='②候補ランキング'!$C$5)),IF('②候補ランキング'!$C$4="ワクワク",Q199,IF('②候補ランキング'!$C$4="手軽さ",11-R199,IF('②候補ランキング'!$C$4="確信度",S199,T199)))*1000+T199+(1000-A199)/10000,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="200" ht="18" customHeight="1" s="35">
-      <c r="A200" s="84">
-        <f>IF(C200="","",ROW()-5)</f>
-        <v/>
-      </c>
-      <c r="B200" s="85" t="n"/>
-      <c r="C200" s="86" t="n"/>
-      <c r="D200" s="86" t="n"/>
-      <c r="E200" s="85" t="n"/>
-      <c r="F200" s="86" t="n"/>
-      <c r="G200" s="86" t="n"/>
-      <c r="H200" s="86" t="n"/>
-      <c r="I200" s="86" t="n"/>
-      <c r="J200" s="85" t="n"/>
-      <c r="K200" s="85" t="n"/>
-      <c r="L200" s="85" t="n"/>
-      <c r="M200" s="85" t="n"/>
-      <c r="N200" s="85" t="n"/>
-      <c r="O200" s="85" t="n"/>
-      <c r="P200" s="84">
-        <f>IF(C200="","",IF(OR(E200="",E200="未検証"),"① STEP1待ち",IF(E200="不通過","✕ STEP1不通過",IF(OR(G200="",H200=""),"② STEP2-3 未記入",IF(COUNTIF(J200:O200,"×")&gt;0,"✕ ボツ候補",IF(COUNTA(J200:O200)&lt;6,"③ STEP4 審査待ち",IF(COUNTIF(J200:O200,"△")&gt;0,"△ 修正して再審査","◎ 候補リスト")))))))</f>
-        <v/>
-      </c>
-      <c r="Q200" s="85" t="n"/>
-      <c r="R200" s="85" t="n"/>
-      <c r="S200" s="85" t="n"/>
-      <c r="T200" s="84">
-        <f>IF(COUNT(Q200:S200)&lt;3,"",Q200+(11-R200)+S200)</f>
-        <v/>
-      </c>
-      <c r="U200" s="85" t="n"/>
-      <c r="V200" s="86" t="n"/>
-      <c r="W200" s="87">
-        <f>IF(AND(P200="◎ 候補リスト",U200&lt;&gt;"ボツ",U200&lt;&gt;"制作済み",T200&lt;&gt;"",OR('②候補ランキング'!$C$5="すべて",B200='②候補ランキング'!$C$5)),IF('②候補ランキング'!$C$4="ワクワク",Q200,IF('②候補ランキング'!$C$4="手軽さ",11-R200,IF('②候補ランキング'!$C$4="確信度",S200,T200)))*1000+T200+(1000-A200)/10000,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="201" ht="18" customHeight="1" s="35">
-      <c r="A201" s="84">
-        <f>IF(C201="","",ROW()-5)</f>
-        <v/>
-      </c>
-      <c r="B201" s="85" t="n"/>
-      <c r="C201" s="86" t="n"/>
-      <c r="D201" s="86" t="n"/>
-      <c r="E201" s="85" t="n"/>
-      <c r="F201" s="86" t="n"/>
-      <c r="G201" s="86" t="n"/>
-      <c r="H201" s="86" t="n"/>
-      <c r="I201" s="86" t="n"/>
-      <c r="J201" s="85" t="n"/>
-      <c r="K201" s="85" t="n"/>
-      <c r="L201" s="85" t="n"/>
-      <c r="M201" s="85" t="n"/>
-      <c r="N201" s="85" t="n"/>
-      <c r="O201" s="85" t="n"/>
-      <c r="P201" s="84">
-        <f>IF(C201="","",IF(OR(E201="",E201="未検証"),"① STEP1待ち",IF(E201="不通過","✕ STEP1不通過",IF(OR(G201="",H201=""),"② STEP2-3 未記入",IF(COUNTIF(J201:O201,"×")&gt;0,"✕ ボツ候補",IF(COUNTA(J201:O201)&lt;6,"③ STEP4 審査待ち",IF(COUNTIF(J201:O201,"△")&gt;0,"△ 修正して再審査","◎ 候補リスト")))))))</f>
-        <v/>
-      </c>
-      <c r="Q201" s="85" t="n"/>
-      <c r="R201" s="85" t="n"/>
-      <c r="S201" s="85" t="n"/>
-      <c r="T201" s="84">
-        <f>IF(COUNT(Q201:S201)&lt;3,"",Q201+(11-R201)+S201)</f>
-        <v/>
-      </c>
-      <c r="U201" s="85" t="n"/>
-      <c r="V201" s="86" t="n"/>
-      <c r="W201" s="87">
-        <f>IF(AND(P201="◎ 候補リスト",U201&lt;&gt;"ボツ",U201&lt;&gt;"制作済み",T201&lt;&gt;"",OR('②候補ランキング'!$C$5="すべて",B201='②候補ランキング'!$C$5)),IF('②候補ランキング'!$C$4="ワクワク",Q201,IF('②候補ランキング'!$C$4="手軽さ",11-R201,IF('②候補ランキング'!$C$4="確信度",S201,T201)))*1000+T201+(1000-A201)/10000,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="202" ht="18" customHeight="1" s="35">
-      <c r="A202" s="84">
-        <f>IF(C202="","",ROW()-5)</f>
-        <v/>
-      </c>
-      <c r="B202" s="85" t="n"/>
-      <c r="C202" s="86" t="n"/>
-      <c r="D202" s="86" t="n"/>
-      <c r="E202" s="85" t="n"/>
-      <c r="F202" s="86" t="n"/>
-      <c r="G202" s="86" t="n"/>
-      <c r="H202" s="86" t="n"/>
-      <c r="I202" s="86" t="n"/>
-      <c r="J202" s="85" t="n"/>
-      <c r="K202" s="85" t="n"/>
-      <c r="L202" s="85" t="n"/>
-      <c r="M202" s="85" t="n"/>
-      <c r="N202" s="85" t="n"/>
-      <c r="O202" s="85" t="n"/>
-      <c r="P202" s="84">
-        <f>IF(C202="","",IF(OR(E202="",E202="未検証"),"① STEP1待ち",IF(E202="不通過","✕ STEP1不通過",IF(OR(G202="",H202=""),"② STEP2-3 未記入",IF(COUNTIF(J202:O202,"×")&gt;0,"✕ ボツ候補",IF(COUNTA(J202:O202)&lt;6,"③ STEP4 審査待ち",IF(COUNTIF(J202:O202,"△")&gt;0,"△ 修正して再審査","◎ 候補リスト")))))))</f>
-        <v/>
-      </c>
-      <c r="Q202" s="85" t="n"/>
-      <c r="R202" s="85" t="n"/>
-      <c r="S202" s="85" t="n"/>
-      <c r="T202" s="84">
-        <f>IF(COUNT(Q202:S202)&lt;3,"",Q202+(11-R202)+S202)</f>
-        <v/>
-      </c>
-      <c r="U202" s="85" t="n"/>
-      <c r="V202" s="86" t="n"/>
-      <c r="W202" s="87">
-        <f>IF(AND(P202="◎ 候補リスト",U202&lt;&gt;"ボツ",U202&lt;&gt;"制作済み",T202&lt;&gt;"",OR('②候補ランキング'!$C$5="すべて",B202='②候補ランキング'!$C$5)),IF('②候補ランキング'!$C$4="ワクワク",Q202,IF('②候補ランキング'!$C$4="手軽さ",11-R202,IF('②候補ランキング'!$C$4="確信度",S202,T202)))*1000+T202+(1000-A202)/10000,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="203" ht="18" customHeight="1" s="35">
-      <c r="A203" s="84">
-        <f>IF(C203="","",ROW()-5)</f>
-        <v/>
-      </c>
-      <c r="B203" s="85" t="n"/>
-      <c r="C203" s="86" t="n"/>
-      <c r="D203" s="86" t="n"/>
-      <c r="E203" s="85" t="n"/>
-      <c r="F203" s="86" t="n"/>
-      <c r="G203" s="86" t="n"/>
-      <c r="H203" s="86" t="n"/>
-      <c r="I203" s="86" t="n"/>
-      <c r="J203" s="85" t="n"/>
-      <c r="K203" s="85" t="n"/>
-      <c r="L203" s="85" t="n"/>
-      <c r="M203" s="85" t="n"/>
-      <c r="N203" s="85" t="n"/>
-      <c r="O203" s="85" t="n"/>
-      <c r="P203" s="84">
-        <f>IF(C203="","",IF(OR(E203="",E203="未検証"),"① STEP1待ち",IF(E203="不通過","✕ STEP1不通過",IF(OR(G203="",H203=""),"② STEP2-3 未記入",IF(COUNTIF(J203:O203,"×")&gt;0,"✕ ボツ候補",IF(COUNTA(J203:O203)&lt;6,"③ STEP4 審査待ち",IF(COUNTIF(J203:O203,"△")&gt;0,"△ 修正して再審査","◎ 候補リスト")))))))</f>
-        <v/>
-      </c>
-      <c r="Q203" s="85" t="n"/>
-      <c r="R203" s="85" t="n"/>
-      <c r="S203" s="85" t="n"/>
-      <c r="T203" s="84">
-        <f>IF(COUNT(Q203:S203)&lt;3,"",Q203+(11-R203)+S203)</f>
-        <v/>
-      </c>
-      <c r="U203" s="85" t="n"/>
-      <c r="V203" s="86" t="n"/>
-      <c r="W203" s="87">
-        <f>IF(AND(P203="◎ 候補リスト",U203&lt;&gt;"ボツ",U203&lt;&gt;"制作済み",T203&lt;&gt;"",OR('②候補ランキング'!$C$5="すべて",B203='②候補ランキング'!$C$5)),IF('②候補ランキング'!$C$4="ワクワク",Q203,IF('②候補ランキング'!$C$4="手軽さ",11-R203,IF('②候補ランキング'!$C$4="確信度",S203,T203)))*1000+T203+(1000-A203)/10000,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="204" ht="18" customHeight="1" s="35">
-      <c r="A204" s="84">
-        <f>IF(C204="","",ROW()-5)</f>
-        <v/>
-      </c>
-      <c r="B204" s="85" t="n"/>
-      <c r="C204" s="86" t="n"/>
-      <c r="D204" s="86" t="n"/>
-      <c r="E204" s="85" t="n"/>
-      <c r="F204" s="86" t="n"/>
-      <c r="G204" s="86" t="n"/>
-      <c r="H204" s="86" t="n"/>
-      <c r="I204" s="86" t="n"/>
-      <c r="J204" s="85" t="n"/>
-      <c r="K204" s="85" t="n"/>
-      <c r="L204" s="85" t="n"/>
-      <c r="M204" s="85" t="n"/>
-      <c r="N204" s="85" t="n"/>
-      <c r="O204" s="85" t="n"/>
-      <c r="P204" s="84">
-        <f>IF(C204="","",IF(OR(E204="",E204="未検証"),"① STEP1待ち",IF(E204="不通過","✕ STEP1不通過",IF(OR(G204="",H204=""),"② STEP2-3 未記入",IF(COUNTIF(J204:O204,"×")&gt;0,"✕ ボツ候補",IF(COUNTA(J204:O204)&lt;6,"③ STEP4 審査待ち",IF(COUNTIF(J204:O204,"△")&gt;0,"△ 修正して再審査","◎ 候補リスト")))))))</f>
-        <v/>
-      </c>
-      <c r="Q204" s="85" t="n"/>
-      <c r="R204" s="85" t="n"/>
-      <c r="S204" s="85" t="n"/>
-      <c r="T204" s="84">
-        <f>IF(COUNT(Q204:S204)&lt;3,"",Q204+(11-R204)+S204)</f>
-        <v/>
-      </c>
-      <c r="U204" s="85" t="n"/>
-      <c r="V204" s="86" t="n"/>
-      <c r="W204" s="87">
-        <f>IF(AND(P204="◎ 候補リスト",U204&lt;&gt;"ボツ",U204&lt;&gt;"制作済み",T204&lt;&gt;"",OR('②候補ランキング'!$C$5="すべて",B204='②候補ランキング'!$C$5)),IF('②候補ランキング'!$C$4="ワクワク",Q204,IF('②候補ランキング'!$C$4="手軽さ",11-R204,IF('②候補ランキング'!$C$4="確信度",S204,T204)))*1000+T204+(1000-A204)/10000,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="205" ht="18" customHeight="1" s="35">
-      <c r="A205" s="84">
-        <f>IF(C205="","",ROW()-5)</f>
-        <v/>
-      </c>
-      <c r="B205" s="85" t="n"/>
-      <c r="C205" s="86" t="n"/>
-      <c r="D205" s="86" t="n"/>
-      <c r="E205" s="85" t="n"/>
-      <c r="F205" s="86" t="n"/>
-      <c r="G205" s="86" t="n"/>
-      <c r="H205" s="86" t="n"/>
-      <c r="I205" s="86" t="n"/>
-      <c r="J205" s="85" t="n"/>
-      <c r="K205" s="85" t="n"/>
-      <c r="L205" s="85" t="n"/>
-      <c r="M205" s="85" t="n"/>
-      <c r="N205" s="85" t="n"/>
-      <c r="O205" s="85" t="n"/>
-      <c r="P205" s="84">
-        <f>IF(C205="","",IF(OR(E205="",E205="未検証"),"① STEP1待ち",IF(E205="不通過","✕ STEP1不通過",IF(OR(G205="",H205=""),"② STEP2-3 未記入",IF(COUNTIF(J205:O205,"×")&gt;0,"✕ ボツ候補",IF(COUNTA(J205:O205)&lt;6,"③ STEP4 審査待ち",IF(COUNTIF(J205:O205,"△")&gt;0,"△ 修正して再審査","◎ 候補リスト")))))))</f>
-        <v/>
-      </c>
-      <c r="Q205" s="85" t="n"/>
-      <c r="R205" s="85" t="n"/>
-      <c r="S205" s="85" t="n"/>
-      <c r="T205" s="84">
-        <f>IF(COUNT(Q205:S205)&lt;3,"",Q205+(11-R205)+S205)</f>
-        <v/>
-      </c>
-      <c r="U205" s="85" t="n"/>
-      <c r="V205" s="86" t="n"/>
-      <c r="W205" s="87">
-        <f>IF(AND(P205="◎ 候補リスト",U205&lt;&gt;"ボツ",U205&lt;&gt;"制作済み",T205&lt;&gt;"",OR('②候補ランキング'!$C$5="すべて",B205='②候補ランキング'!$C$5)),IF('②候補ランキング'!$C$4="ワクワク",Q205,IF('②候補ランキング'!$C$4="手軽さ",11-R205,IF('②候補ランキング'!$C$4="確信度",S205,T205)))*1000+T205+(1000-A205)/10000,"")</f>
-        <v/>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A5:W205"/>
+  <autoFilter ref="A5:W105"/>
   <mergeCells count="9">
     <mergeCell ref="E4:F4"/>
     <mergeCell ref="J4:O4"/>
@@ -9976,7 +6276,7 @@
     <mergeCell ref="A2:W2"/>
     <mergeCell ref="U4:V4"/>
   </mergeCells>
-  <conditionalFormatting sqref="J6:O205">
+  <conditionalFormatting sqref="J6:O105">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>J6="○"</formula>
     </cfRule>
@@ -9987,7 +6287,7 @@
       <formula>J6="×"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P6:P205">
+  <conditionalFormatting sqref="P6:P105">
     <cfRule type="expression" priority="4" dxfId="0">
       <formula>LEFT($P6,1)="◎"</formula>
     </cfRule>
@@ -10007,31 +6307,31 @@
       <formula>LEFT($P6,1)="①"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A6:V205">
+  <conditionalFormatting sqref="A6:V105">
     <cfRule type="expression" priority="10" dxfId="6">
       <formula>OR($U6="ボツ",$U6="制作済み")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="U6:U205">
+  <conditionalFormatting sqref="U6:U105">
     <cfRule type="expression" priority="11" dxfId="7">
       <formula>U6="制作決定"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="5">
-    <dataValidation sqref="B6:B205" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="B6:B105" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"本命,実験,転換"</formula1>
     </dataValidation>
-    <dataValidation sqref="E6:E205" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E6:E105" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"通過,実験枠,転換枠,未検証,不通過"</formula1>
     </dataValidation>
-    <dataValidation sqref="J6:O205" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="J6:O105" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"○,△,×"</formula1>
     </dataValidation>
-    <dataValidation sqref="Q6:S205" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="whole" operator="between">
+    <dataValidation sqref="Q6:S105" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="whole" operator="between">
       <formula1>1</formula1>
       <formula2>10</formula2>
     </dataValidation>
-    <dataValidation sqref="U6:U205" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="U6:U105" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"制作決定,保留,ボツ,制作済み"</formula1>
     </dataValidation>
   </dataValidations>
@@ -10046,7 +6346,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L57"/>
+  <dimension ref="A1:L47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" style="35" min="1" max="1"/>
@@ -10148,7 +6448,7 @@
         </is>
       </c>
       <c r="D9" s="94">
-        <f>COUNTIF('①企画一覧・審査'!$P$6:$P$205,"① STEP1待ち")&amp;" 件"</f>
+        <f>COUNTIF('①企画一覧・審査'!$P$6:$P$105,"① STEP1待ち")&amp;" 件"</f>
         <v/>
       </c>
       <c r="F9" s="93" t="inlineStr">
@@ -10159,7 +6459,7 @@
       <c r="G9" s="95" t="n"/>
       <c r="H9" s="89" t="n"/>
       <c r="I9" s="94">
-        <f>COUNTIF('①企画一覧・審査'!$U$6:$U$205,"制作決定")&amp;" 件"</f>
+        <f>COUNTIF('①企画一覧・審査'!$U$6:$U$105,"制作決定")&amp;" 件"</f>
         <v/>
       </c>
     </row>
@@ -10170,7 +6470,7 @@
         </is>
       </c>
       <c r="D10" s="94">
-        <f>COUNTIF('①企画一覧・審査'!$P$6:$P$205,"② STEP2-3 未記入")&amp;" 件"</f>
+        <f>COUNTIF('①企画一覧・審査'!$P$6:$P$105,"② STEP2-3 未記入")&amp;" 件"</f>
         <v/>
       </c>
       <c r="F10" s="93" t="inlineStr">
@@ -10181,7 +6481,7 @@
       <c r="G10" s="95" t="n"/>
       <c r="H10" s="89" t="n"/>
       <c r="I10" s="94">
-        <f>COUNTIF('①企画一覧・審査'!$U$6:$U$205,"保留")&amp;" 件"</f>
+        <f>COUNTIF('①企画一覧・審査'!$U$6:$U$105,"保留")&amp;" 件"</f>
         <v/>
       </c>
     </row>
@@ -10192,7 +6492,7 @@
         </is>
       </c>
       <c r="D11" s="94">
-        <f>COUNTIF('①企画一覧・審査'!$P$6:$P$205,"③ STEP4 審査待ち")&amp;" 件"</f>
+        <f>COUNTIF('①企画一覧・審査'!$P$6:$P$105,"③ STEP4 審査待ち")&amp;" 件"</f>
         <v/>
       </c>
       <c r="F11" s="93" t="inlineStr">
@@ -10203,7 +6503,7 @@
       <c r="G11" s="95" t="n"/>
       <c r="H11" s="89" t="n"/>
       <c r="I11" s="94">
-        <f>COUNTIF('①企画一覧・審査'!$U$6:$U$205,"ボツ")&amp;" 件"</f>
+        <f>COUNTIF('①企画一覧・審査'!$U$6:$U$105,"ボツ")&amp;" 件"</f>
         <v/>
       </c>
     </row>
@@ -10214,7 +6514,7 @@
         </is>
       </c>
       <c r="D12" s="94">
-        <f>COUNTIF('①企画一覧・審査'!$P$6:$P$205,"△ 修正して再審査")&amp;" 件"</f>
+        <f>COUNTIF('①企画一覧・審査'!$P$6:$P$105,"△ 修正して再審査")&amp;" 件"</f>
         <v/>
       </c>
       <c r="F12" s="93" t="inlineStr">
@@ -10225,7 +6525,7 @@
       <c r="G12" s="95" t="n"/>
       <c r="H12" s="89" t="n"/>
       <c r="I12" s="94">
-        <f>COUNTIF('①企画一覧・審査'!$U$6:$U$205,"制作済み")&amp;" 件"</f>
+        <f>COUNTIF('①企画一覧・審査'!$U$6:$U$105,"制作済み")&amp;" 件"</f>
         <v/>
       </c>
     </row>
@@ -10236,7 +6536,7 @@
         </is>
       </c>
       <c r="D13" s="94">
-        <f>COUNTIF('①企画一覧・審査'!$P$6:$P$205,"✕ ボツ候補")&amp;" 件"</f>
+        <f>COUNTIF('①企画一覧・審査'!$P$6:$P$105,"✕ ボツ候補")&amp;" 件"</f>
         <v/>
       </c>
     </row>
@@ -10247,7 +6547,7 @@
         </is>
       </c>
       <c r="D14" s="94">
-        <f>COUNTIF('①企画一覧・審査'!$P$6:$P$205,"✕ STEP1不通過")&amp;" 件"</f>
+        <f>COUNTIF('①企画一覧・審査'!$P$6:$P$105,"✕ STEP1不通過")&amp;" 件"</f>
         <v/>
       </c>
     </row>
@@ -10258,7 +6558,7 @@
         </is>
       </c>
       <c r="D15" s="94">
-        <f>COUNTIF('①企画一覧・審査'!$P$6:$P$205,"◎ 候補リスト")&amp;" 件"</f>
+        <f>COUNTIF('①企画一覧・審査'!$P$6:$P$105,"◎ 候補リスト")&amp;" 件"</f>
         <v/>
       </c>
     </row>
@@ -10323,1841 +6623,1381 @@
     </row>
     <row r="18" ht="30" customHeight="1" s="35">
       <c r="A18" s="84">
-        <f>IF(COUNT('①企画一覧・審査'!$W$6:$W$205)&lt;1,"",1)</f>
+        <f>IF(COUNT('①企画一覧・審査'!$W$6:$W$105)&lt;1,"",1)</f>
         <v/>
       </c>
       <c r="B18" s="84">
-        <f>IF($L18="","",INDEX('①企画一覧・審査'!$B$6:$B$205,$L18)&amp;"")</f>
+        <f>IF($L18="","",INDEX('①企画一覧・審査'!$B$6:$B$105,$L18)&amp;"")</f>
         <v/>
       </c>
       <c r="C18" s="93">
-        <f>IF($L18="","",INDEX('①企画一覧・審査'!$C$6:$C$205,$L18)&amp;"")</f>
+        <f>IF($L18="","",INDEX('①企画一覧・審査'!$C$6:$C$105,$L18)&amp;"")</f>
         <v/>
       </c>
       <c r="D18" s="93">
-        <f>IF($L18="","",INDEX('①企画一覧・審査'!$I$6:$I$205,$L18)&amp;"")</f>
+        <f>IF($L18="","",INDEX('①企画一覧・審査'!$I$6:$I$105,$L18)&amp;"")</f>
         <v/>
       </c>
       <c r="E18" s="84">
-        <f>IF($L18="","",INDEX('①企画一覧・審査'!$Q$6:$Q$205,$L18))</f>
+        <f>IF($L18="","",INDEX('①企画一覧・審査'!$Q$6:$Q$105,$L18))</f>
         <v/>
       </c>
       <c r="F18" s="84">
-        <f>IF($L18="","",INDEX('①企画一覧・審査'!$R$6:$R$205,$L18))</f>
+        <f>IF($L18="","",INDEX('①企画一覧・審査'!$R$6:$R$105,$L18))</f>
         <v/>
       </c>
       <c r="G18" s="84">
-        <f>IF($L18="","",INDEX('①企画一覧・審査'!$S$6:$S$205,$L18))</f>
+        <f>IF($L18="","",INDEX('①企画一覧・審査'!$S$6:$S$105,$L18))</f>
         <v/>
       </c>
       <c r="H18" s="84">
-        <f>IF($L18="","",INDEX('①企画一覧・審査'!$T$6:$T$205,$L18))</f>
+        <f>IF($L18="","",INDEX('①企画一覧・審査'!$T$6:$T$105,$L18))</f>
         <v/>
       </c>
       <c r="I18" s="84">
-        <f>IF($L18="","",INDEX('①企画一覧・審査'!$U$6:$U$205,$L18)&amp;"")</f>
+        <f>IF($L18="","",INDEX('①企画一覧・審査'!$U$6:$U$105,$L18)&amp;"")</f>
         <v/>
       </c>
       <c r="J18" s="93">
-        <f>IF($L18="","",INDEX('①企画一覧・審査'!$F$6:$F$205,$L18)&amp;"")</f>
+        <f>IF($L18="","",INDEX('①企画一覧・審査'!$F$6:$F$105,$L18)&amp;"")</f>
         <v/>
       </c>
       <c r="L18">
-        <f>IF(A18="","",MATCH(LARGE('①企画一覧・審査'!$W$6:$W$205,1),'①企画一覧・審査'!$W$6:$W$205,0))</f>
+        <f>IF(A18="","",MATCH(LARGE('①企画一覧・審査'!$W$6:$W$105,1),'①企画一覧・審査'!$W$6:$W$105,0))</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="30" customHeight="1" s="35">
       <c r="A19" s="84">
-        <f>IF(COUNT('①企画一覧・審査'!$W$6:$W$205)&lt;2,"",2)</f>
+        <f>IF(COUNT('①企画一覧・審査'!$W$6:$W$105)&lt;2,"",2)</f>
         <v/>
       </c>
       <c r="B19" s="84">
-        <f>IF($L19="","",INDEX('①企画一覧・審査'!$B$6:$B$205,$L19)&amp;"")</f>
+        <f>IF($L19="","",INDEX('①企画一覧・審査'!$B$6:$B$105,$L19)&amp;"")</f>
         <v/>
       </c>
       <c r="C19" s="93">
-        <f>IF($L19="","",INDEX('①企画一覧・審査'!$C$6:$C$205,$L19)&amp;"")</f>
+        <f>IF($L19="","",INDEX('①企画一覧・審査'!$C$6:$C$105,$L19)&amp;"")</f>
         <v/>
       </c>
       <c r="D19" s="93">
-        <f>IF($L19="","",INDEX('①企画一覧・審査'!$I$6:$I$205,$L19)&amp;"")</f>
+        <f>IF($L19="","",INDEX('①企画一覧・審査'!$I$6:$I$105,$L19)&amp;"")</f>
         <v/>
       </c>
       <c r="E19" s="84">
-        <f>IF($L19="","",INDEX('①企画一覧・審査'!$Q$6:$Q$205,$L19))</f>
+        <f>IF($L19="","",INDEX('①企画一覧・審査'!$Q$6:$Q$105,$L19))</f>
         <v/>
       </c>
       <c r="F19" s="84">
-        <f>IF($L19="","",INDEX('①企画一覧・審査'!$R$6:$R$205,$L19))</f>
+        <f>IF($L19="","",INDEX('①企画一覧・審査'!$R$6:$R$105,$L19))</f>
         <v/>
       </c>
       <c r="G19" s="84">
-        <f>IF($L19="","",INDEX('①企画一覧・審査'!$S$6:$S$205,$L19))</f>
+        <f>IF($L19="","",INDEX('①企画一覧・審査'!$S$6:$S$105,$L19))</f>
         <v/>
       </c>
       <c r="H19" s="84">
-        <f>IF($L19="","",INDEX('①企画一覧・審査'!$T$6:$T$205,$L19))</f>
+        <f>IF($L19="","",INDEX('①企画一覧・審査'!$T$6:$T$105,$L19))</f>
         <v/>
       </c>
       <c r="I19" s="84">
-        <f>IF($L19="","",INDEX('①企画一覧・審査'!$U$6:$U$205,$L19)&amp;"")</f>
+        <f>IF($L19="","",INDEX('①企画一覧・審査'!$U$6:$U$105,$L19)&amp;"")</f>
         <v/>
       </c>
       <c r="J19" s="93">
-        <f>IF($L19="","",INDEX('①企画一覧・審査'!$F$6:$F$205,$L19)&amp;"")</f>
+        <f>IF($L19="","",INDEX('①企画一覧・審査'!$F$6:$F$105,$L19)&amp;"")</f>
         <v/>
       </c>
       <c r="L19">
-        <f>IF(A19="","",MATCH(LARGE('①企画一覧・審査'!$W$6:$W$205,2),'①企画一覧・審査'!$W$6:$W$205,0))</f>
+        <f>IF(A19="","",MATCH(LARGE('①企画一覧・審査'!$W$6:$W$105,2),'①企画一覧・審査'!$W$6:$W$105,0))</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="30" customHeight="1" s="35">
       <c r="A20" s="84">
-        <f>IF(COUNT('①企画一覧・審査'!$W$6:$W$205)&lt;3,"",3)</f>
+        <f>IF(COUNT('①企画一覧・審査'!$W$6:$W$105)&lt;3,"",3)</f>
         <v/>
       </c>
       <c r="B20" s="84">
-        <f>IF($L20="","",INDEX('①企画一覧・審査'!$B$6:$B$205,$L20)&amp;"")</f>
+        <f>IF($L20="","",INDEX('①企画一覧・審査'!$B$6:$B$105,$L20)&amp;"")</f>
         <v/>
       </c>
       <c r="C20" s="93">
-        <f>IF($L20="","",INDEX('①企画一覧・審査'!$C$6:$C$205,$L20)&amp;"")</f>
+        <f>IF($L20="","",INDEX('①企画一覧・審査'!$C$6:$C$105,$L20)&amp;"")</f>
         <v/>
       </c>
       <c r="D20" s="93">
-        <f>IF($L20="","",INDEX('①企画一覧・審査'!$I$6:$I$205,$L20)&amp;"")</f>
+        <f>IF($L20="","",INDEX('①企画一覧・審査'!$I$6:$I$105,$L20)&amp;"")</f>
         <v/>
       </c>
       <c r="E20" s="84">
-        <f>IF($L20="","",INDEX('①企画一覧・審査'!$Q$6:$Q$205,$L20))</f>
+        <f>IF($L20="","",INDEX('①企画一覧・審査'!$Q$6:$Q$105,$L20))</f>
         <v/>
       </c>
       <c r="F20" s="84">
-        <f>IF($L20="","",INDEX('①企画一覧・審査'!$R$6:$R$205,$L20))</f>
+        <f>IF($L20="","",INDEX('①企画一覧・審査'!$R$6:$R$105,$L20))</f>
         <v/>
       </c>
       <c r="G20" s="84">
-        <f>IF($L20="","",INDEX('①企画一覧・審査'!$S$6:$S$205,$L20))</f>
+        <f>IF($L20="","",INDEX('①企画一覧・審査'!$S$6:$S$105,$L20))</f>
         <v/>
       </c>
       <c r="H20" s="84">
-        <f>IF($L20="","",INDEX('①企画一覧・審査'!$T$6:$T$205,$L20))</f>
+        <f>IF($L20="","",INDEX('①企画一覧・審査'!$T$6:$T$105,$L20))</f>
         <v/>
       </c>
       <c r="I20" s="84">
-        <f>IF($L20="","",INDEX('①企画一覧・審査'!$U$6:$U$205,$L20)&amp;"")</f>
+        <f>IF($L20="","",INDEX('①企画一覧・審査'!$U$6:$U$105,$L20)&amp;"")</f>
         <v/>
       </c>
       <c r="J20" s="93">
-        <f>IF($L20="","",INDEX('①企画一覧・審査'!$F$6:$F$205,$L20)&amp;"")</f>
+        <f>IF($L20="","",INDEX('①企画一覧・審査'!$F$6:$F$105,$L20)&amp;"")</f>
         <v/>
       </c>
       <c r="L20">
-        <f>IF(A20="","",MATCH(LARGE('①企画一覧・審査'!$W$6:$W$205,3),'①企画一覧・審査'!$W$6:$W$205,0))</f>
+        <f>IF(A20="","",MATCH(LARGE('①企画一覧・審査'!$W$6:$W$105,3),'①企画一覧・審査'!$W$6:$W$105,0))</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="30" customHeight="1" s="35">
       <c r="A21" s="84">
-        <f>IF(COUNT('①企画一覧・審査'!$W$6:$W$205)&lt;4,"",4)</f>
+        <f>IF(COUNT('①企画一覧・審査'!$W$6:$W$105)&lt;4,"",4)</f>
         <v/>
       </c>
       <c r="B21" s="84">
-        <f>IF($L21="","",INDEX('①企画一覧・審査'!$B$6:$B$205,$L21)&amp;"")</f>
+        <f>IF($L21="","",INDEX('①企画一覧・審査'!$B$6:$B$105,$L21)&amp;"")</f>
         <v/>
       </c>
       <c r="C21" s="93">
-        <f>IF($L21="","",INDEX('①企画一覧・審査'!$C$6:$C$205,$L21)&amp;"")</f>
+        <f>IF($L21="","",INDEX('①企画一覧・審査'!$C$6:$C$105,$L21)&amp;"")</f>
         <v/>
       </c>
       <c r="D21" s="93">
-        <f>IF($L21="","",INDEX('①企画一覧・審査'!$I$6:$I$205,$L21)&amp;"")</f>
+        <f>IF($L21="","",INDEX('①企画一覧・審査'!$I$6:$I$105,$L21)&amp;"")</f>
         <v/>
       </c>
       <c r="E21" s="84">
-        <f>IF($L21="","",INDEX('①企画一覧・審査'!$Q$6:$Q$205,$L21))</f>
+        <f>IF($L21="","",INDEX('①企画一覧・審査'!$Q$6:$Q$105,$L21))</f>
         <v/>
       </c>
       <c r="F21" s="84">
-        <f>IF($L21="","",INDEX('①企画一覧・審査'!$R$6:$R$205,$L21))</f>
+        <f>IF($L21="","",INDEX('①企画一覧・審査'!$R$6:$R$105,$L21))</f>
         <v/>
       </c>
       <c r="G21" s="84">
-        <f>IF($L21="","",INDEX('①企画一覧・審査'!$S$6:$S$205,$L21))</f>
+        <f>IF($L21="","",INDEX('①企画一覧・審査'!$S$6:$S$105,$L21))</f>
         <v/>
       </c>
       <c r="H21" s="84">
-        <f>IF($L21="","",INDEX('①企画一覧・審査'!$T$6:$T$205,$L21))</f>
+        <f>IF($L21="","",INDEX('①企画一覧・審査'!$T$6:$T$105,$L21))</f>
         <v/>
       </c>
       <c r="I21" s="84">
-        <f>IF($L21="","",INDEX('①企画一覧・審査'!$U$6:$U$205,$L21)&amp;"")</f>
+        <f>IF($L21="","",INDEX('①企画一覧・審査'!$U$6:$U$105,$L21)&amp;"")</f>
         <v/>
       </c>
       <c r="J21" s="93">
-        <f>IF($L21="","",INDEX('①企画一覧・審査'!$F$6:$F$205,$L21)&amp;"")</f>
+        <f>IF($L21="","",INDEX('①企画一覧・審査'!$F$6:$F$105,$L21)&amp;"")</f>
         <v/>
       </c>
       <c r="L21">
-        <f>IF(A21="","",MATCH(LARGE('①企画一覧・審査'!$W$6:$W$205,4),'①企画一覧・審査'!$W$6:$W$205,0))</f>
+        <f>IF(A21="","",MATCH(LARGE('①企画一覧・審査'!$W$6:$W$105,4),'①企画一覧・審査'!$W$6:$W$105,0))</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="30" customHeight="1" s="35">
       <c r="A22" s="84">
-        <f>IF(COUNT('①企画一覧・審査'!$W$6:$W$205)&lt;5,"",5)</f>
+        <f>IF(COUNT('①企画一覧・審査'!$W$6:$W$105)&lt;5,"",5)</f>
         <v/>
       </c>
       <c r="B22" s="84">
-        <f>IF($L22="","",INDEX('①企画一覧・審査'!$B$6:$B$205,$L22)&amp;"")</f>
+        <f>IF($L22="","",INDEX('①企画一覧・審査'!$B$6:$B$105,$L22)&amp;"")</f>
         <v/>
       </c>
       <c r="C22" s="93">
-        <f>IF($L22="","",INDEX('①企画一覧・審査'!$C$6:$C$205,$L22)&amp;"")</f>
+        <f>IF($L22="","",INDEX('①企画一覧・審査'!$C$6:$C$105,$L22)&amp;"")</f>
         <v/>
       </c>
       <c r="D22" s="93">
-        <f>IF($L22="","",INDEX('①企画一覧・審査'!$I$6:$I$205,$L22)&amp;"")</f>
+        <f>IF($L22="","",INDEX('①企画一覧・審査'!$I$6:$I$105,$L22)&amp;"")</f>
         <v/>
       </c>
       <c r="E22" s="84">
-        <f>IF($L22="","",INDEX('①企画一覧・審査'!$Q$6:$Q$205,$L22))</f>
+        <f>IF($L22="","",INDEX('①企画一覧・審査'!$Q$6:$Q$105,$L22))</f>
         <v/>
       </c>
       <c r="F22" s="84">
-        <f>IF($L22="","",INDEX('①企画一覧・審査'!$R$6:$R$205,$L22))</f>
+        <f>IF($L22="","",INDEX('①企画一覧・審査'!$R$6:$R$105,$L22))</f>
         <v/>
       </c>
       <c r="G22" s="84">
-        <f>IF($L22="","",INDEX('①企画一覧・審査'!$S$6:$S$205,$L22))</f>
+        <f>IF($L22="","",INDEX('①企画一覧・審査'!$S$6:$S$105,$L22))</f>
         <v/>
       </c>
       <c r="H22" s="84">
-        <f>IF($L22="","",INDEX('①企画一覧・審査'!$T$6:$T$205,$L22))</f>
+        <f>IF($L22="","",INDEX('①企画一覧・審査'!$T$6:$T$105,$L22))</f>
         <v/>
       </c>
       <c r="I22" s="84">
-        <f>IF($L22="","",INDEX('①企画一覧・審査'!$U$6:$U$205,$L22)&amp;"")</f>
+        <f>IF($L22="","",INDEX('①企画一覧・審査'!$U$6:$U$105,$L22)&amp;"")</f>
         <v/>
       </c>
       <c r="J22" s="93">
-        <f>IF($L22="","",INDEX('①企画一覧・審査'!$F$6:$F$205,$L22)&amp;"")</f>
+        <f>IF($L22="","",INDEX('①企画一覧・審査'!$F$6:$F$105,$L22)&amp;"")</f>
         <v/>
       </c>
       <c r="L22">
-        <f>IF(A22="","",MATCH(LARGE('①企画一覧・審査'!$W$6:$W$205,5),'①企画一覧・審査'!$W$6:$W$205,0))</f>
+        <f>IF(A22="","",MATCH(LARGE('①企画一覧・審査'!$W$6:$W$105,5),'①企画一覧・審査'!$W$6:$W$105,0))</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="30" customHeight="1" s="35">
       <c r="A23" s="84">
-        <f>IF(COUNT('①企画一覧・審査'!$W$6:$W$205)&lt;6,"",6)</f>
+        <f>IF(COUNT('①企画一覧・審査'!$W$6:$W$105)&lt;6,"",6)</f>
         <v/>
       </c>
       <c r="B23" s="84">
-        <f>IF($L23="","",INDEX('①企画一覧・審査'!$B$6:$B$205,$L23)&amp;"")</f>
+        <f>IF($L23="","",INDEX('①企画一覧・審査'!$B$6:$B$105,$L23)&amp;"")</f>
         <v/>
       </c>
       <c r="C23" s="93">
-        <f>IF($L23="","",INDEX('①企画一覧・審査'!$C$6:$C$205,$L23)&amp;"")</f>
+        <f>IF($L23="","",INDEX('①企画一覧・審査'!$C$6:$C$105,$L23)&amp;"")</f>
         <v/>
       </c>
       <c r="D23" s="93">
-        <f>IF($L23="","",INDEX('①企画一覧・審査'!$I$6:$I$205,$L23)&amp;"")</f>
+        <f>IF($L23="","",INDEX('①企画一覧・審査'!$I$6:$I$105,$L23)&amp;"")</f>
         <v/>
       </c>
       <c r="E23" s="84">
-        <f>IF($L23="","",INDEX('①企画一覧・審査'!$Q$6:$Q$205,$L23))</f>
+        <f>IF($L23="","",INDEX('①企画一覧・審査'!$Q$6:$Q$105,$L23))</f>
         <v/>
       </c>
       <c r="F23" s="84">
-        <f>IF($L23="","",INDEX('①企画一覧・審査'!$R$6:$R$205,$L23))</f>
+        <f>IF($L23="","",INDEX('①企画一覧・審査'!$R$6:$R$105,$L23))</f>
         <v/>
       </c>
       <c r="G23" s="84">
-        <f>IF($L23="","",INDEX('①企画一覧・審査'!$S$6:$S$205,$L23))</f>
+        <f>IF($L23="","",INDEX('①企画一覧・審査'!$S$6:$S$105,$L23))</f>
         <v/>
       </c>
       <c r="H23" s="84">
-        <f>IF($L23="","",INDEX('①企画一覧・審査'!$T$6:$T$205,$L23))</f>
+        <f>IF($L23="","",INDEX('①企画一覧・審査'!$T$6:$T$105,$L23))</f>
         <v/>
       </c>
       <c r="I23" s="84">
-        <f>IF($L23="","",INDEX('①企画一覧・審査'!$U$6:$U$205,$L23)&amp;"")</f>
+        <f>IF($L23="","",INDEX('①企画一覧・審査'!$U$6:$U$105,$L23)&amp;"")</f>
         <v/>
       </c>
       <c r="J23" s="93">
-        <f>IF($L23="","",INDEX('①企画一覧・審査'!$F$6:$F$205,$L23)&amp;"")</f>
+        <f>IF($L23="","",INDEX('①企画一覧・審査'!$F$6:$F$105,$L23)&amp;"")</f>
         <v/>
       </c>
       <c r="L23">
-        <f>IF(A23="","",MATCH(LARGE('①企画一覧・審査'!$W$6:$W$205,6),'①企画一覧・審査'!$W$6:$W$205,0))</f>
+        <f>IF(A23="","",MATCH(LARGE('①企画一覧・審査'!$W$6:$W$105,6),'①企画一覧・審査'!$W$6:$W$105,0))</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="30" customHeight="1" s="35">
       <c r="A24" s="84">
-        <f>IF(COUNT('①企画一覧・審査'!$W$6:$W$205)&lt;7,"",7)</f>
+        <f>IF(COUNT('①企画一覧・審査'!$W$6:$W$105)&lt;7,"",7)</f>
         <v/>
       </c>
       <c r="B24" s="84">
-        <f>IF($L24="","",INDEX('①企画一覧・審査'!$B$6:$B$205,$L24)&amp;"")</f>
+        <f>IF($L24="","",INDEX('①企画一覧・審査'!$B$6:$B$105,$L24)&amp;"")</f>
         <v/>
       </c>
       <c r="C24" s="93">
-        <f>IF($L24="","",INDEX('①企画一覧・審査'!$C$6:$C$205,$L24)&amp;"")</f>
+        <f>IF($L24="","",INDEX('①企画一覧・審査'!$C$6:$C$105,$L24)&amp;"")</f>
         <v/>
       </c>
       <c r="D24" s="93">
-        <f>IF($L24="","",INDEX('①企画一覧・審査'!$I$6:$I$205,$L24)&amp;"")</f>
+        <f>IF($L24="","",INDEX('①企画一覧・審査'!$I$6:$I$105,$L24)&amp;"")</f>
         <v/>
       </c>
       <c r="E24" s="84">
-        <f>IF($L24="","",INDEX('①企画一覧・審査'!$Q$6:$Q$205,$L24))</f>
+        <f>IF($L24="","",INDEX('①企画一覧・審査'!$Q$6:$Q$105,$L24))</f>
         <v/>
       </c>
       <c r="F24" s="84">
-        <f>IF($L24="","",INDEX('①企画一覧・審査'!$R$6:$R$205,$L24))</f>
+        <f>IF($L24="","",INDEX('①企画一覧・審査'!$R$6:$R$105,$L24))</f>
         <v/>
       </c>
       <c r="G24" s="84">
-        <f>IF($L24="","",INDEX('①企画一覧・審査'!$S$6:$S$205,$L24))</f>
+        <f>IF($L24="","",INDEX('①企画一覧・審査'!$S$6:$S$105,$L24))</f>
         <v/>
       </c>
       <c r="H24" s="84">
-        <f>IF($L24="","",INDEX('①企画一覧・審査'!$T$6:$T$205,$L24))</f>
+        <f>IF($L24="","",INDEX('①企画一覧・審査'!$T$6:$T$105,$L24))</f>
         <v/>
       </c>
       <c r="I24" s="84">
-        <f>IF($L24="","",INDEX('①企画一覧・審査'!$U$6:$U$205,$L24)&amp;"")</f>
+        <f>IF($L24="","",INDEX('①企画一覧・審査'!$U$6:$U$105,$L24)&amp;"")</f>
         <v/>
       </c>
       <c r="J24" s="93">
-        <f>IF($L24="","",INDEX('①企画一覧・審査'!$F$6:$F$205,$L24)&amp;"")</f>
+        <f>IF($L24="","",INDEX('①企画一覧・審査'!$F$6:$F$105,$L24)&amp;"")</f>
         <v/>
       </c>
       <c r="L24">
-        <f>IF(A24="","",MATCH(LARGE('①企画一覧・審査'!$W$6:$W$205,7),'①企画一覧・審査'!$W$6:$W$205,0))</f>
+        <f>IF(A24="","",MATCH(LARGE('①企画一覧・審査'!$W$6:$W$105,7),'①企画一覧・審査'!$W$6:$W$105,0))</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="30" customHeight="1" s="35">
       <c r="A25" s="84">
-        <f>IF(COUNT('①企画一覧・審査'!$W$6:$W$205)&lt;8,"",8)</f>
+        <f>IF(COUNT('①企画一覧・審査'!$W$6:$W$105)&lt;8,"",8)</f>
         <v/>
       </c>
       <c r="B25" s="84">
-        <f>IF($L25="","",INDEX('①企画一覧・審査'!$B$6:$B$205,$L25)&amp;"")</f>
+        <f>IF($L25="","",INDEX('①企画一覧・審査'!$B$6:$B$105,$L25)&amp;"")</f>
         <v/>
       </c>
       <c r="C25" s="93">
-        <f>IF($L25="","",INDEX('①企画一覧・審査'!$C$6:$C$205,$L25)&amp;"")</f>
+        <f>IF($L25="","",INDEX('①企画一覧・審査'!$C$6:$C$105,$L25)&amp;"")</f>
         <v/>
       </c>
       <c r="D25" s="93">
-        <f>IF($L25="","",INDEX('①企画一覧・審査'!$I$6:$I$205,$L25)&amp;"")</f>
+        <f>IF($L25="","",INDEX('①企画一覧・審査'!$I$6:$I$105,$L25)&amp;"")</f>
         <v/>
       </c>
       <c r="E25" s="84">
-        <f>IF($L25="","",INDEX('①企画一覧・審査'!$Q$6:$Q$205,$L25))</f>
+        <f>IF($L25="","",INDEX('①企画一覧・審査'!$Q$6:$Q$105,$L25))</f>
         <v/>
       </c>
       <c r="F25" s="84">
-        <f>IF($L25="","",INDEX('①企画一覧・審査'!$R$6:$R$205,$L25))</f>
+        <f>IF($L25="","",INDEX('①企画一覧・審査'!$R$6:$R$105,$L25))</f>
         <v/>
       </c>
       <c r="G25" s="84">
-        <f>IF($L25="","",INDEX('①企画一覧・審査'!$S$6:$S$205,$L25))</f>
+        <f>IF($L25="","",INDEX('①企画一覧・審査'!$S$6:$S$105,$L25))</f>
         <v/>
       </c>
       <c r="H25" s="84">
-        <f>IF($L25="","",INDEX('①企画一覧・審査'!$T$6:$T$205,$L25))</f>
+        <f>IF($L25="","",INDEX('①企画一覧・審査'!$T$6:$T$105,$L25))</f>
         <v/>
       </c>
       <c r="I25" s="84">
-        <f>IF($L25="","",INDEX('①企画一覧・審査'!$U$6:$U$205,$L25)&amp;"")</f>
+        <f>IF($L25="","",INDEX('①企画一覧・審査'!$U$6:$U$105,$L25)&amp;"")</f>
         <v/>
       </c>
       <c r="J25" s="93">
-        <f>IF($L25="","",INDEX('①企画一覧・審査'!$F$6:$F$205,$L25)&amp;"")</f>
+        <f>IF($L25="","",INDEX('①企画一覧・審査'!$F$6:$F$105,$L25)&amp;"")</f>
         <v/>
       </c>
       <c r="L25">
-        <f>IF(A25="","",MATCH(LARGE('①企画一覧・審査'!$W$6:$W$205,8),'①企画一覧・審査'!$W$6:$W$205,0))</f>
+        <f>IF(A25="","",MATCH(LARGE('①企画一覧・審査'!$W$6:$W$105,8),'①企画一覧・審査'!$W$6:$W$105,0))</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="30" customHeight="1" s="35">
       <c r="A26" s="84">
-        <f>IF(COUNT('①企画一覧・審査'!$W$6:$W$205)&lt;9,"",9)</f>
+        <f>IF(COUNT('①企画一覧・審査'!$W$6:$W$105)&lt;9,"",9)</f>
         <v/>
       </c>
       <c r="B26" s="84">
-        <f>IF($L26="","",INDEX('①企画一覧・審査'!$B$6:$B$205,$L26)&amp;"")</f>
+        <f>IF($L26="","",INDEX('①企画一覧・審査'!$B$6:$B$105,$L26)&amp;"")</f>
         <v/>
       </c>
       <c r="C26" s="93">
-        <f>IF($L26="","",INDEX('①企画一覧・審査'!$C$6:$C$205,$L26)&amp;"")</f>
+        <f>IF($L26="","",INDEX('①企画一覧・審査'!$C$6:$C$105,$L26)&amp;"")</f>
         <v/>
       </c>
       <c r="D26" s="93">
-        <f>IF($L26="","",INDEX('①企画一覧・審査'!$I$6:$I$205,$L26)&amp;"")</f>
+        <f>IF($L26="","",INDEX('①企画一覧・審査'!$I$6:$I$105,$L26)&amp;"")</f>
         <v/>
       </c>
       <c r="E26" s="84">
-        <f>IF($L26="","",INDEX('①企画一覧・審査'!$Q$6:$Q$205,$L26))</f>
+        <f>IF($L26="","",INDEX('①企画一覧・審査'!$Q$6:$Q$105,$L26))</f>
         <v/>
       </c>
       <c r="F26" s="84">
-        <f>IF($L26="","",INDEX('①企画一覧・審査'!$R$6:$R$205,$L26))</f>
+        <f>IF($L26="","",INDEX('①企画一覧・審査'!$R$6:$R$105,$L26))</f>
         <v/>
       </c>
       <c r="G26" s="84">
-        <f>IF($L26="","",INDEX('①企画一覧・審査'!$S$6:$S$205,$L26))</f>
+        <f>IF($L26="","",INDEX('①企画一覧・審査'!$S$6:$S$105,$L26))</f>
         <v/>
       </c>
       <c r="H26" s="84">
-        <f>IF($L26="","",INDEX('①企画一覧・審査'!$T$6:$T$205,$L26))</f>
+        <f>IF($L26="","",INDEX('①企画一覧・審査'!$T$6:$T$105,$L26))</f>
         <v/>
       </c>
       <c r="I26" s="84">
-        <f>IF($L26="","",INDEX('①企画一覧・審査'!$U$6:$U$205,$L26)&amp;"")</f>
+        <f>IF($L26="","",INDEX('①企画一覧・審査'!$U$6:$U$105,$L26)&amp;"")</f>
         <v/>
       </c>
       <c r="J26" s="93">
-        <f>IF($L26="","",INDEX('①企画一覧・審査'!$F$6:$F$205,$L26)&amp;"")</f>
+        <f>IF($L26="","",INDEX('①企画一覧・審査'!$F$6:$F$105,$L26)&amp;"")</f>
         <v/>
       </c>
       <c r="L26">
-        <f>IF(A26="","",MATCH(LARGE('①企画一覧・審査'!$W$6:$W$205,9),'①企画一覧・審査'!$W$6:$W$205,0))</f>
+        <f>IF(A26="","",MATCH(LARGE('①企画一覧・審査'!$W$6:$W$105,9),'①企画一覧・審査'!$W$6:$W$105,0))</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="30" customHeight="1" s="35">
       <c r="A27" s="84">
-        <f>IF(COUNT('①企画一覧・審査'!$W$6:$W$205)&lt;10,"",10)</f>
+        <f>IF(COUNT('①企画一覧・審査'!$W$6:$W$105)&lt;10,"",10)</f>
         <v/>
       </c>
       <c r="B27" s="84">
-        <f>IF($L27="","",INDEX('①企画一覧・審査'!$B$6:$B$205,$L27)&amp;"")</f>
+        <f>IF($L27="","",INDEX('①企画一覧・審査'!$B$6:$B$105,$L27)&amp;"")</f>
         <v/>
       </c>
       <c r="C27" s="93">
-        <f>IF($L27="","",INDEX('①企画一覧・審査'!$C$6:$C$205,$L27)&amp;"")</f>
+        <f>IF($L27="","",INDEX('①企画一覧・審査'!$C$6:$C$105,$L27)&amp;"")</f>
         <v/>
       </c>
       <c r="D27" s="93">
-        <f>IF($L27="","",INDEX('①企画一覧・審査'!$I$6:$I$205,$L27)&amp;"")</f>
+        <f>IF($L27="","",INDEX('①企画一覧・審査'!$I$6:$I$105,$L27)&amp;"")</f>
         <v/>
       </c>
       <c r="E27" s="84">
-        <f>IF($L27="","",INDEX('①企画一覧・審査'!$Q$6:$Q$205,$L27))</f>
+        <f>IF($L27="","",INDEX('①企画一覧・審査'!$Q$6:$Q$105,$L27))</f>
         <v/>
       </c>
       <c r="F27" s="84">
-        <f>IF($L27="","",INDEX('①企画一覧・審査'!$R$6:$R$205,$L27))</f>
+        <f>IF($L27="","",INDEX('①企画一覧・審査'!$R$6:$R$105,$L27))</f>
         <v/>
       </c>
       <c r="G27" s="84">
-        <f>IF($L27="","",INDEX('①企画一覧・審査'!$S$6:$S$205,$L27))</f>
+        <f>IF($L27="","",INDEX('①企画一覧・審査'!$S$6:$S$105,$L27))</f>
         <v/>
       </c>
       <c r="H27" s="84">
-        <f>IF($L27="","",INDEX('①企画一覧・審査'!$T$6:$T$205,$L27))</f>
+        <f>IF($L27="","",INDEX('①企画一覧・審査'!$T$6:$T$105,$L27))</f>
         <v/>
       </c>
       <c r="I27" s="84">
-        <f>IF($L27="","",INDEX('①企画一覧・審査'!$U$6:$U$205,$L27)&amp;"")</f>
+        <f>IF($L27="","",INDEX('①企画一覧・審査'!$U$6:$U$105,$L27)&amp;"")</f>
         <v/>
       </c>
       <c r="J27" s="93">
-        <f>IF($L27="","",INDEX('①企画一覧・審査'!$F$6:$F$205,$L27)&amp;"")</f>
+        <f>IF($L27="","",INDEX('①企画一覧・審査'!$F$6:$F$105,$L27)&amp;"")</f>
         <v/>
       </c>
       <c r="L27">
-        <f>IF(A27="","",MATCH(LARGE('①企画一覧・審査'!$W$6:$W$205,10),'①企画一覧・審査'!$W$6:$W$205,0))</f>
+        <f>IF(A27="","",MATCH(LARGE('①企画一覧・審査'!$W$6:$W$105,10),'①企画一覧・審査'!$W$6:$W$105,0))</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="30" customHeight="1" s="35">
       <c r="A28" s="84">
-        <f>IF(COUNT('①企画一覧・審査'!$W$6:$W$205)&lt;11,"",11)</f>
+        <f>IF(COUNT('①企画一覧・審査'!$W$6:$W$105)&lt;11,"",11)</f>
         <v/>
       </c>
       <c r="B28" s="84">
-        <f>IF($L28="","",INDEX('①企画一覧・審査'!$B$6:$B$205,$L28)&amp;"")</f>
+        <f>IF($L28="","",INDEX('①企画一覧・審査'!$B$6:$B$105,$L28)&amp;"")</f>
         <v/>
       </c>
       <c r="C28" s="93">
-        <f>IF($L28="","",INDEX('①企画一覧・審査'!$C$6:$C$205,$L28)&amp;"")</f>
+        <f>IF($L28="","",INDEX('①企画一覧・審査'!$C$6:$C$105,$L28)&amp;"")</f>
         <v/>
       </c>
       <c r="D28" s="93">
-        <f>IF($L28="","",INDEX('①企画一覧・審査'!$I$6:$I$205,$L28)&amp;"")</f>
+        <f>IF($L28="","",INDEX('①企画一覧・審査'!$I$6:$I$105,$L28)&amp;"")</f>
         <v/>
       </c>
       <c r="E28" s="84">
-        <f>IF($L28="","",INDEX('①企画一覧・審査'!$Q$6:$Q$205,$L28))</f>
+        <f>IF($L28="","",INDEX('①企画一覧・審査'!$Q$6:$Q$105,$L28))</f>
         <v/>
       </c>
       <c r="F28" s="84">
-        <f>IF($L28="","",INDEX('①企画一覧・審査'!$R$6:$R$205,$L28))</f>
+        <f>IF($L28="","",INDEX('①企画一覧・審査'!$R$6:$R$105,$L28))</f>
         <v/>
       </c>
       <c r="G28" s="84">
-        <f>IF($L28="","",INDEX('①企画一覧・審査'!$S$6:$S$205,$L28))</f>
+        <f>IF($L28="","",INDEX('①企画一覧・審査'!$S$6:$S$105,$L28))</f>
         <v/>
       </c>
       <c r="H28" s="84">
-        <f>IF($L28="","",INDEX('①企画一覧・審査'!$T$6:$T$205,$L28))</f>
+        <f>IF($L28="","",INDEX('①企画一覧・審査'!$T$6:$T$105,$L28))</f>
         <v/>
       </c>
       <c r="I28" s="84">
-        <f>IF($L28="","",INDEX('①企画一覧・審査'!$U$6:$U$205,$L28)&amp;"")</f>
+        <f>IF($L28="","",INDEX('①企画一覧・審査'!$U$6:$U$105,$L28)&amp;"")</f>
         <v/>
       </c>
       <c r="J28" s="93">
-        <f>IF($L28="","",INDEX('①企画一覧・審査'!$F$6:$F$205,$L28)&amp;"")</f>
+        <f>IF($L28="","",INDEX('①企画一覧・審査'!$F$6:$F$105,$L28)&amp;"")</f>
         <v/>
       </c>
       <c r="L28">
-        <f>IF(A28="","",MATCH(LARGE('①企画一覧・審査'!$W$6:$W$205,11),'①企画一覧・審査'!$W$6:$W$205,0))</f>
+        <f>IF(A28="","",MATCH(LARGE('①企画一覧・審査'!$W$6:$W$105,11),'①企画一覧・審査'!$W$6:$W$105,0))</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="30" customHeight="1" s="35">
       <c r="A29" s="84">
-        <f>IF(COUNT('①企画一覧・審査'!$W$6:$W$205)&lt;12,"",12)</f>
+        <f>IF(COUNT('①企画一覧・審査'!$W$6:$W$105)&lt;12,"",12)</f>
         <v/>
       </c>
       <c r="B29" s="84">
-        <f>IF($L29="","",INDEX('①企画一覧・審査'!$B$6:$B$205,$L29)&amp;"")</f>
+        <f>IF($L29="","",INDEX('①企画一覧・審査'!$B$6:$B$105,$L29)&amp;"")</f>
         <v/>
       </c>
       <c r="C29" s="93">
-        <f>IF($L29="","",INDEX('①企画一覧・審査'!$C$6:$C$205,$L29)&amp;"")</f>
+        <f>IF($L29="","",INDEX('①企画一覧・審査'!$C$6:$C$105,$L29)&amp;"")</f>
         <v/>
       </c>
       <c r="D29" s="93">
-        <f>IF($L29="","",INDEX('①企画一覧・審査'!$I$6:$I$205,$L29)&amp;"")</f>
+        <f>IF($L29="","",INDEX('①企画一覧・審査'!$I$6:$I$105,$L29)&amp;"")</f>
         <v/>
       </c>
       <c r="E29" s="84">
-        <f>IF($L29="","",INDEX('①企画一覧・審査'!$Q$6:$Q$205,$L29))</f>
+        <f>IF($L29="","",INDEX('①企画一覧・審査'!$Q$6:$Q$105,$L29))</f>
         <v/>
       </c>
       <c r="F29" s="84">
-        <f>IF($L29="","",INDEX('①企画一覧・審査'!$R$6:$R$205,$L29))</f>
+        <f>IF($L29="","",INDEX('①企画一覧・審査'!$R$6:$R$105,$L29))</f>
         <v/>
       </c>
       <c r="G29" s="84">
-        <f>IF($L29="","",INDEX('①企画一覧・審査'!$S$6:$S$205,$L29))</f>
+        <f>IF($L29="","",INDEX('①企画一覧・審査'!$S$6:$S$105,$L29))</f>
         <v/>
       </c>
       <c r="H29" s="84">
-        <f>IF($L29="","",INDEX('①企画一覧・審査'!$T$6:$T$205,$L29))</f>
+        <f>IF($L29="","",INDEX('①企画一覧・審査'!$T$6:$T$105,$L29))</f>
         <v/>
       </c>
       <c r="I29" s="84">
-        <f>IF($L29="","",INDEX('①企画一覧・審査'!$U$6:$U$205,$L29)&amp;"")</f>
+        <f>IF($L29="","",INDEX('①企画一覧・審査'!$U$6:$U$105,$L29)&amp;"")</f>
         <v/>
       </c>
       <c r="J29" s="93">
-        <f>IF($L29="","",INDEX('①企画一覧・審査'!$F$6:$F$205,$L29)&amp;"")</f>
+        <f>IF($L29="","",INDEX('①企画一覧・審査'!$F$6:$F$105,$L29)&amp;"")</f>
         <v/>
       </c>
       <c r="L29">
-        <f>IF(A29="","",MATCH(LARGE('①企画一覧・審査'!$W$6:$W$205,12),'①企画一覧・審査'!$W$6:$W$205,0))</f>
+        <f>IF(A29="","",MATCH(LARGE('①企画一覧・審査'!$W$6:$W$105,12),'①企画一覧・審査'!$W$6:$W$105,0))</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="30" customHeight="1" s="35">
       <c r="A30" s="84">
-        <f>IF(COUNT('①企画一覧・審査'!$W$6:$W$205)&lt;13,"",13)</f>
+        <f>IF(COUNT('①企画一覧・審査'!$W$6:$W$105)&lt;13,"",13)</f>
         <v/>
       </c>
       <c r="B30" s="84">
-        <f>IF($L30="","",INDEX('①企画一覧・審査'!$B$6:$B$205,$L30)&amp;"")</f>
+        <f>IF($L30="","",INDEX('①企画一覧・審査'!$B$6:$B$105,$L30)&amp;"")</f>
         <v/>
       </c>
       <c r="C30" s="93">
-        <f>IF($L30="","",INDEX('①企画一覧・審査'!$C$6:$C$205,$L30)&amp;"")</f>
+        <f>IF($L30="","",INDEX('①企画一覧・審査'!$C$6:$C$105,$L30)&amp;"")</f>
         <v/>
       </c>
       <c r="D30" s="93">
-        <f>IF($L30="","",INDEX('①企画一覧・審査'!$I$6:$I$205,$L30)&amp;"")</f>
+        <f>IF($L30="","",INDEX('①企画一覧・審査'!$I$6:$I$105,$L30)&amp;"")</f>
         <v/>
       </c>
       <c r="E30" s="84">
-        <f>IF($L30="","",INDEX('①企画一覧・審査'!$Q$6:$Q$205,$L30))</f>
+        <f>IF($L30="","",INDEX('①企画一覧・審査'!$Q$6:$Q$105,$L30))</f>
         <v/>
       </c>
       <c r="F30" s="84">
-        <f>IF($L30="","",INDEX('①企画一覧・審査'!$R$6:$R$205,$L30))</f>
+        <f>IF($L30="","",INDEX('①企画一覧・審査'!$R$6:$R$105,$L30))</f>
         <v/>
       </c>
       <c r="G30" s="84">
-        <f>IF($L30="","",INDEX('①企画一覧・審査'!$S$6:$S$205,$L30))</f>
+        <f>IF($L30="","",INDEX('①企画一覧・審査'!$S$6:$S$105,$L30))</f>
         <v/>
       </c>
       <c r="H30" s="84">
-        <f>IF($L30="","",INDEX('①企画一覧・審査'!$T$6:$T$205,$L30))</f>
+        <f>IF($L30="","",INDEX('①企画一覧・審査'!$T$6:$T$105,$L30))</f>
         <v/>
       </c>
       <c r="I30" s="84">
-        <f>IF($L30="","",INDEX('①企画一覧・審査'!$U$6:$U$205,$L30)&amp;"")</f>
+        <f>IF($L30="","",INDEX('①企画一覧・審査'!$U$6:$U$105,$L30)&amp;"")</f>
         <v/>
       </c>
       <c r="J30" s="93">
-        <f>IF($L30="","",INDEX('①企画一覧・審査'!$F$6:$F$205,$L30)&amp;"")</f>
+        <f>IF($L30="","",INDEX('①企画一覧・審査'!$F$6:$F$105,$L30)&amp;"")</f>
         <v/>
       </c>
       <c r="L30">
-        <f>IF(A30="","",MATCH(LARGE('①企画一覧・審査'!$W$6:$W$205,13),'①企画一覧・審査'!$W$6:$W$205,0))</f>
+        <f>IF(A30="","",MATCH(LARGE('①企画一覧・審査'!$W$6:$W$105,13),'①企画一覧・審査'!$W$6:$W$105,0))</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="30" customHeight="1" s="35">
       <c r="A31" s="84">
-        <f>IF(COUNT('①企画一覧・審査'!$W$6:$W$205)&lt;14,"",14)</f>
+        <f>IF(COUNT('①企画一覧・審査'!$W$6:$W$105)&lt;14,"",14)</f>
         <v/>
       </c>
       <c r="B31" s="84">
-        <f>IF($L31="","",INDEX('①企画一覧・審査'!$B$6:$B$205,$L31)&amp;"")</f>
+        <f>IF($L31="","",INDEX('①企画一覧・審査'!$B$6:$B$105,$L31)&amp;"")</f>
         <v/>
       </c>
       <c r="C31" s="93">
-        <f>IF($L31="","",INDEX('①企画一覧・審査'!$C$6:$C$205,$L31)&amp;"")</f>
+        <f>IF($L31="","",INDEX('①企画一覧・審査'!$C$6:$C$105,$L31)&amp;"")</f>
         <v/>
       </c>
       <c r="D31" s="93">
-        <f>IF($L31="","",INDEX('①企画一覧・審査'!$I$6:$I$205,$L31)&amp;"")</f>
+        <f>IF($L31="","",INDEX('①企画一覧・審査'!$I$6:$I$105,$L31)&amp;"")</f>
         <v/>
       </c>
       <c r="E31" s="84">
-        <f>IF($L31="","",INDEX('①企画一覧・審査'!$Q$6:$Q$205,$L31))</f>
+        <f>IF($L31="","",INDEX('①企画一覧・審査'!$Q$6:$Q$105,$L31))</f>
         <v/>
       </c>
       <c r="F31" s="84">
-        <f>IF($L31="","",INDEX('①企画一覧・審査'!$R$6:$R$205,$L31))</f>
+        <f>IF($L31="","",INDEX('①企画一覧・審査'!$R$6:$R$105,$L31))</f>
         <v/>
       </c>
       <c r="G31" s="84">
-        <f>IF($L31="","",INDEX('①企画一覧・審査'!$S$6:$S$205,$L31))</f>
+        <f>IF($L31="","",INDEX('①企画一覧・審査'!$S$6:$S$105,$L31))</f>
         <v/>
       </c>
       <c r="H31" s="84">
-        <f>IF($L31="","",INDEX('①企画一覧・審査'!$T$6:$T$205,$L31))</f>
+        <f>IF($L31="","",INDEX('①企画一覧・審査'!$T$6:$T$105,$L31))</f>
         <v/>
       </c>
       <c r="I31" s="84">
-        <f>IF($L31="","",INDEX('①企画一覧・審査'!$U$6:$U$205,$L31)&amp;"")</f>
+        <f>IF($L31="","",INDEX('①企画一覧・審査'!$U$6:$U$105,$L31)&amp;"")</f>
         <v/>
       </c>
       <c r="J31" s="93">
-        <f>IF($L31="","",INDEX('①企画一覧・審査'!$F$6:$F$205,$L31)&amp;"")</f>
+        <f>IF($L31="","",INDEX('①企画一覧・審査'!$F$6:$F$105,$L31)&amp;"")</f>
         <v/>
       </c>
       <c r="L31">
-        <f>IF(A31="","",MATCH(LARGE('①企画一覧・審査'!$W$6:$W$205,14),'①企画一覧・審査'!$W$6:$W$205,0))</f>
+        <f>IF(A31="","",MATCH(LARGE('①企画一覧・審査'!$W$6:$W$105,14),'①企画一覧・審査'!$W$6:$W$105,0))</f>
         <v/>
       </c>
     </row>
     <row r="32" ht="30" customHeight="1" s="35">
       <c r="A32" s="84">
-        <f>IF(COUNT('①企画一覧・審査'!$W$6:$W$205)&lt;15,"",15)</f>
+        <f>IF(COUNT('①企画一覧・審査'!$W$6:$W$105)&lt;15,"",15)</f>
         <v/>
       </c>
       <c r="B32" s="84">
-        <f>IF($L32="","",INDEX('①企画一覧・審査'!$B$6:$B$205,$L32)&amp;"")</f>
+        <f>IF($L32="","",INDEX('①企画一覧・審査'!$B$6:$B$105,$L32)&amp;"")</f>
         <v/>
       </c>
       <c r="C32" s="93">
-        <f>IF($L32="","",INDEX('①企画一覧・審査'!$C$6:$C$205,$L32)&amp;"")</f>
+        <f>IF($L32="","",INDEX('①企画一覧・審査'!$C$6:$C$105,$L32)&amp;"")</f>
         <v/>
       </c>
       <c r="D32" s="93">
-        <f>IF($L32="","",INDEX('①企画一覧・審査'!$I$6:$I$205,$L32)&amp;"")</f>
+        <f>IF($L32="","",INDEX('①企画一覧・審査'!$I$6:$I$105,$L32)&amp;"")</f>
         <v/>
       </c>
       <c r="E32" s="84">
-        <f>IF($L32="","",INDEX('①企画一覧・審査'!$Q$6:$Q$205,$L32))</f>
+        <f>IF($L32="","",INDEX('①企画一覧・審査'!$Q$6:$Q$105,$L32))</f>
         <v/>
       </c>
       <c r="F32" s="84">
-        <f>IF($L32="","",INDEX('①企画一覧・審査'!$R$6:$R$205,$L32))</f>
+        <f>IF($L32="","",INDEX('①企画一覧・審査'!$R$6:$R$105,$L32))</f>
         <v/>
       </c>
       <c r="G32" s="84">
-        <f>IF($L32="","",INDEX('①企画一覧・審査'!$S$6:$S$205,$L32))</f>
+        <f>IF($L32="","",INDEX('①企画一覧・審査'!$S$6:$S$105,$L32))</f>
         <v/>
       </c>
       <c r="H32" s="84">
-        <f>IF($L32="","",INDEX('①企画一覧・審査'!$T$6:$T$205,$L32))</f>
+        <f>IF($L32="","",INDEX('①企画一覧・審査'!$T$6:$T$105,$L32))</f>
         <v/>
       </c>
       <c r="I32" s="84">
-        <f>IF($L32="","",INDEX('①企画一覧・審査'!$U$6:$U$205,$L32)&amp;"")</f>
+        <f>IF($L32="","",INDEX('①企画一覧・審査'!$U$6:$U$105,$L32)&amp;"")</f>
         <v/>
       </c>
       <c r="J32" s="93">
-        <f>IF($L32="","",INDEX('①企画一覧・審査'!$F$6:$F$205,$L32)&amp;"")</f>
+        <f>IF($L32="","",INDEX('①企画一覧・審査'!$F$6:$F$105,$L32)&amp;"")</f>
         <v/>
       </c>
       <c r="L32">
-        <f>IF(A32="","",MATCH(LARGE('①企画一覧・審査'!$W$6:$W$205,15),'①企画一覧・審査'!$W$6:$W$205,0))</f>
+        <f>IF(A32="","",MATCH(LARGE('①企画一覧・審査'!$W$6:$W$105,15),'①企画一覧・審査'!$W$6:$W$105,0))</f>
         <v/>
       </c>
     </row>
     <row r="33" ht="30" customHeight="1" s="35">
       <c r="A33" s="84">
-        <f>IF(COUNT('①企画一覧・審査'!$W$6:$W$205)&lt;16,"",16)</f>
+        <f>IF(COUNT('①企画一覧・審査'!$W$6:$W$105)&lt;16,"",16)</f>
         <v/>
       </c>
       <c r="B33" s="84">
-        <f>IF($L33="","",INDEX('①企画一覧・審査'!$B$6:$B$205,$L33)&amp;"")</f>
+        <f>IF($L33="","",INDEX('①企画一覧・審査'!$B$6:$B$105,$L33)&amp;"")</f>
         <v/>
       </c>
       <c r="C33" s="93">
-        <f>IF($L33="","",INDEX('①企画一覧・審査'!$C$6:$C$205,$L33)&amp;"")</f>
+        <f>IF($L33="","",INDEX('①企画一覧・審査'!$C$6:$C$105,$L33)&amp;"")</f>
         <v/>
       </c>
       <c r="D33" s="93">
-        <f>IF($L33="","",INDEX('①企画一覧・審査'!$I$6:$I$205,$L33)&amp;"")</f>
+        <f>IF($L33="","",INDEX('①企画一覧・審査'!$I$6:$I$105,$L33)&amp;"")</f>
         <v/>
       </c>
       <c r="E33" s="84">
-        <f>IF($L33="","",INDEX('①企画一覧・審査'!$Q$6:$Q$205,$L33))</f>
+        <f>IF($L33="","",INDEX('①企画一覧・審査'!$Q$6:$Q$105,$L33))</f>
         <v/>
       </c>
       <c r="F33" s="84">
-        <f>IF($L33="","",INDEX('①企画一覧・審査'!$R$6:$R$205,$L33))</f>
+        <f>IF($L33="","",INDEX('①企画一覧・審査'!$R$6:$R$105,$L33))</f>
         <v/>
       </c>
       <c r="G33" s="84">
-        <f>IF($L33="","",INDEX('①企画一覧・審査'!$S$6:$S$205,$L33))</f>
+        <f>IF($L33="","",INDEX('①企画一覧・審査'!$S$6:$S$105,$L33))</f>
         <v/>
       </c>
       <c r="H33" s="84">
-        <f>IF($L33="","",INDEX('①企画一覧・審査'!$T$6:$T$205,$L33))</f>
+        <f>IF($L33="","",INDEX('①企画一覧・審査'!$T$6:$T$105,$L33))</f>
         <v/>
       </c>
       <c r="I33" s="84">
-        <f>IF($L33="","",INDEX('①企画一覧・審査'!$U$6:$U$205,$L33)&amp;"")</f>
+        <f>IF($L33="","",INDEX('①企画一覧・審査'!$U$6:$U$105,$L33)&amp;"")</f>
         <v/>
       </c>
       <c r="J33" s="93">
-        <f>IF($L33="","",INDEX('①企画一覧・審査'!$F$6:$F$205,$L33)&amp;"")</f>
+        <f>IF($L33="","",INDEX('①企画一覧・審査'!$F$6:$F$105,$L33)&amp;"")</f>
         <v/>
       </c>
       <c r="L33">
-        <f>IF(A33="","",MATCH(LARGE('①企画一覧・審査'!$W$6:$W$205,16),'①企画一覧・審査'!$W$6:$W$205,0))</f>
+        <f>IF(A33="","",MATCH(LARGE('①企画一覧・審査'!$W$6:$W$105,16),'①企画一覧・審査'!$W$6:$W$105,0))</f>
         <v/>
       </c>
     </row>
     <row r="34" ht="30" customHeight="1" s="35">
       <c r="A34" s="84">
-        <f>IF(COUNT('①企画一覧・審査'!$W$6:$W$205)&lt;17,"",17)</f>
+        <f>IF(COUNT('①企画一覧・審査'!$W$6:$W$105)&lt;17,"",17)</f>
         <v/>
       </c>
       <c r="B34" s="84">
-        <f>IF($L34="","",INDEX('①企画一覧・審査'!$B$6:$B$205,$L34)&amp;"")</f>
+        <f>IF($L34="","",INDEX('①企画一覧・審査'!$B$6:$B$105,$L34)&amp;"")</f>
         <v/>
       </c>
       <c r="C34" s="93">
-        <f>IF($L34="","",INDEX('①企画一覧・審査'!$C$6:$C$205,$L34)&amp;"")</f>
+        <f>IF($L34="","",INDEX('①企画一覧・審査'!$C$6:$C$105,$L34)&amp;"")</f>
         <v/>
       </c>
       <c r="D34" s="93">
-        <f>IF($L34="","",INDEX('①企画一覧・審査'!$I$6:$I$205,$L34)&amp;"")</f>
+        <f>IF($L34="","",INDEX('①企画一覧・審査'!$I$6:$I$105,$L34)&amp;"")</f>
         <v/>
       </c>
       <c r="E34" s="84">
-        <f>IF($L34="","",INDEX('①企画一覧・審査'!$Q$6:$Q$205,$L34))</f>
+        <f>IF($L34="","",INDEX('①企画一覧・審査'!$Q$6:$Q$105,$L34))</f>
         <v/>
       </c>
       <c r="F34" s="84">
-        <f>IF($L34="","",INDEX('①企画一覧・審査'!$R$6:$R$205,$L34))</f>
+        <f>IF($L34="","",INDEX('①企画一覧・審査'!$R$6:$R$105,$L34))</f>
         <v/>
       </c>
       <c r="G34" s="84">
-        <f>IF($L34="","",INDEX('①企画一覧・審査'!$S$6:$S$205,$L34))</f>
+        <f>IF($L34="","",INDEX('①企画一覧・審査'!$S$6:$S$105,$L34))</f>
         <v/>
       </c>
       <c r="H34" s="84">
-        <f>IF($L34="","",INDEX('①企画一覧・審査'!$T$6:$T$205,$L34))</f>
+        <f>IF($L34="","",INDEX('①企画一覧・審査'!$T$6:$T$105,$L34))</f>
         <v/>
       </c>
       <c r="I34" s="84">
-        <f>IF($L34="","",INDEX('①企画一覧・審査'!$U$6:$U$205,$L34)&amp;"")</f>
+        <f>IF($L34="","",INDEX('①企画一覧・審査'!$U$6:$U$105,$L34)&amp;"")</f>
         <v/>
       </c>
       <c r="J34" s="93">
-        <f>IF($L34="","",INDEX('①企画一覧・審査'!$F$6:$F$205,$L34)&amp;"")</f>
+        <f>IF($L34="","",INDEX('①企画一覧・審査'!$F$6:$F$105,$L34)&amp;"")</f>
         <v/>
       </c>
       <c r="L34">
-        <f>IF(A34="","",MATCH(LARGE('①企画一覧・審査'!$W$6:$W$205,17),'①企画一覧・審査'!$W$6:$W$205,0))</f>
+        <f>IF(A34="","",MATCH(LARGE('①企画一覧・審査'!$W$6:$W$105,17),'①企画一覧・審査'!$W$6:$W$105,0))</f>
         <v/>
       </c>
     </row>
     <row r="35" ht="30" customHeight="1" s="35">
       <c r="A35" s="84">
-        <f>IF(COUNT('①企画一覧・審査'!$W$6:$W$205)&lt;18,"",18)</f>
+        <f>IF(COUNT('①企画一覧・審査'!$W$6:$W$105)&lt;18,"",18)</f>
         <v/>
       </c>
       <c r="B35" s="84">
-        <f>IF($L35="","",INDEX('①企画一覧・審査'!$B$6:$B$205,$L35)&amp;"")</f>
+        <f>IF($L35="","",INDEX('①企画一覧・審査'!$B$6:$B$105,$L35)&amp;"")</f>
         <v/>
       </c>
       <c r="C35" s="93">
-        <f>IF($L35="","",INDEX('①企画一覧・審査'!$C$6:$C$205,$L35)&amp;"")</f>
+        <f>IF($L35="","",INDEX('①企画一覧・審査'!$C$6:$C$105,$L35)&amp;"")</f>
         <v/>
       </c>
       <c r="D35" s="93">
-        <f>IF($L35="","",INDEX('①企画一覧・審査'!$I$6:$I$205,$L35)&amp;"")</f>
+        <f>IF($L35="","",INDEX('①企画一覧・審査'!$I$6:$I$105,$L35)&amp;"")</f>
         <v/>
       </c>
       <c r="E35" s="84">
-        <f>IF($L35="","",INDEX('①企画一覧・審査'!$Q$6:$Q$205,$L35))</f>
+        <f>IF($L35="","",INDEX('①企画一覧・審査'!$Q$6:$Q$105,$L35))</f>
         <v/>
       </c>
       <c r="F35" s="84">
-        <f>IF($L35="","",INDEX('①企画一覧・審査'!$R$6:$R$205,$L35))</f>
+        <f>IF($L35="","",INDEX('①企画一覧・審査'!$R$6:$R$105,$L35))</f>
         <v/>
       </c>
       <c r="G35" s="84">
-        <f>IF($L35="","",INDEX('①企画一覧・審査'!$S$6:$S$205,$L35))</f>
+        <f>IF($L35="","",INDEX('①企画一覧・審査'!$S$6:$S$105,$L35))</f>
         <v/>
       </c>
       <c r="H35" s="84">
-        <f>IF($L35="","",INDEX('①企画一覧・審査'!$T$6:$T$205,$L35))</f>
+        <f>IF($L35="","",INDEX('①企画一覧・審査'!$T$6:$T$105,$L35))</f>
         <v/>
       </c>
       <c r="I35" s="84">
-        <f>IF($L35="","",INDEX('①企画一覧・審査'!$U$6:$U$205,$L35)&amp;"")</f>
+        <f>IF($L35="","",INDEX('①企画一覧・審査'!$U$6:$U$105,$L35)&amp;"")</f>
         <v/>
       </c>
       <c r="J35" s="93">
-        <f>IF($L35="","",INDEX('①企画一覧・審査'!$F$6:$F$205,$L35)&amp;"")</f>
+        <f>IF($L35="","",INDEX('①企画一覧・審査'!$F$6:$F$105,$L35)&amp;"")</f>
         <v/>
       </c>
       <c r="L35">
-        <f>IF(A35="","",MATCH(LARGE('①企画一覧・審査'!$W$6:$W$205,18),'①企画一覧・審査'!$W$6:$W$205,0))</f>
+        <f>IF(A35="","",MATCH(LARGE('①企画一覧・審査'!$W$6:$W$105,18),'①企画一覧・審査'!$W$6:$W$105,0))</f>
         <v/>
       </c>
     </row>
     <row r="36" ht="30" customHeight="1" s="35">
       <c r="A36" s="84">
-        <f>IF(COUNT('①企画一覧・審査'!$W$6:$W$205)&lt;19,"",19)</f>
+        <f>IF(COUNT('①企画一覧・審査'!$W$6:$W$105)&lt;19,"",19)</f>
         <v/>
       </c>
       <c r="B36" s="84">
-        <f>IF($L36="","",INDEX('①企画一覧・審査'!$B$6:$B$205,$L36)&amp;"")</f>
+        <f>IF($L36="","",INDEX('①企画一覧・審査'!$B$6:$B$105,$L36)&amp;"")</f>
         <v/>
       </c>
       <c r="C36" s="93">
-        <f>IF($L36="","",INDEX('①企画一覧・審査'!$C$6:$C$205,$L36)&amp;"")</f>
+        <f>IF($L36="","",INDEX('①企画一覧・審査'!$C$6:$C$105,$L36)&amp;"")</f>
         <v/>
       </c>
       <c r="D36" s="93">
-        <f>IF($L36="","",INDEX('①企画一覧・審査'!$I$6:$I$205,$L36)&amp;"")</f>
+        <f>IF($L36="","",INDEX('①企画一覧・審査'!$I$6:$I$105,$L36)&amp;"")</f>
         <v/>
       </c>
       <c r="E36" s="84">
-        <f>IF($L36="","",INDEX('①企画一覧・審査'!$Q$6:$Q$205,$L36))</f>
+        <f>IF($L36="","",INDEX('①企画一覧・審査'!$Q$6:$Q$105,$L36))</f>
         <v/>
       </c>
       <c r="F36" s="84">
-        <f>IF($L36="","",INDEX('①企画一覧・審査'!$R$6:$R$205,$L36))</f>
+        <f>IF($L36="","",INDEX('①企画一覧・審査'!$R$6:$R$105,$L36))</f>
         <v/>
       </c>
       <c r="G36" s="84">
-        <f>IF($L36="","",INDEX('①企画一覧・審査'!$S$6:$S$205,$L36))</f>
+        <f>IF($L36="","",INDEX('①企画一覧・審査'!$S$6:$S$105,$L36))</f>
         <v/>
       </c>
       <c r="H36" s="84">
-        <f>IF($L36="","",INDEX('①企画一覧・審査'!$T$6:$T$205,$L36))</f>
+        <f>IF($L36="","",INDEX('①企画一覧・審査'!$T$6:$T$105,$L36))</f>
         <v/>
       </c>
       <c r="I36" s="84">
-        <f>IF($L36="","",INDEX('①企画一覧・審査'!$U$6:$U$205,$L36)&amp;"")</f>
+        <f>IF($L36="","",INDEX('①企画一覧・審査'!$U$6:$U$105,$L36)&amp;"")</f>
         <v/>
       </c>
       <c r="J36" s="93">
-        <f>IF($L36="","",INDEX('①企画一覧・審査'!$F$6:$F$205,$L36)&amp;"")</f>
+        <f>IF($L36="","",INDEX('①企画一覧・審査'!$F$6:$F$105,$L36)&amp;"")</f>
         <v/>
       </c>
       <c r="L36">
-        <f>IF(A36="","",MATCH(LARGE('①企画一覧・審査'!$W$6:$W$205,19),'①企画一覧・審査'!$W$6:$W$205,0))</f>
+        <f>IF(A36="","",MATCH(LARGE('①企画一覧・審査'!$W$6:$W$105,19),'①企画一覧・審査'!$W$6:$W$105,0))</f>
         <v/>
       </c>
     </row>
     <row r="37" ht="30" customHeight="1" s="35">
       <c r="A37" s="84">
-        <f>IF(COUNT('①企画一覧・審査'!$W$6:$W$205)&lt;20,"",20)</f>
+        <f>IF(COUNT('①企画一覧・審査'!$W$6:$W$105)&lt;20,"",20)</f>
         <v/>
       </c>
       <c r="B37" s="84">
-        <f>IF($L37="","",INDEX('①企画一覧・審査'!$B$6:$B$205,$L37)&amp;"")</f>
+        <f>IF($L37="","",INDEX('①企画一覧・審査'!$B$6:$B$105,$L37)&amp;"")</f>
         <v/>
       </c>
       <c r="C37" s="93">
-        <f>IF($L37="","",INDEX('①企画一覧・審査'!$C$6:$C$205,$L37)&amp;"")</f>
+        <f>IF($L37="","",INDEX('①企画一覧・審査'!$C$6:$C$105,$L37)&amp;"")</f>
         <v/>
       </c>
       <c r="D37" s="93">
-        <f>IF($L37="","",INDEX('①企画一覧・審査'!$I$6:$I$205,$L37)&amp;"")</f>
+        <f>IF($L37="","",INDEX('①企画一覧・審査'!$I$6:$I$105,$L37)&amp;"")</f>
         <v/>
       </c>
       <c r="E37" s="84">
-        <f>IF($L37="","",INDEX('①企画一覧・審査'!$Q$6:$Q$205,$L37))</f>
+        <f>IF($L37="","",INDEX('①企画一覧・審査'!$Q$6:$Q$105,$L37))</f>
         <v/>
       </c>
       <c r="F37" s="84">
-        <f>IF($L37="","",INDEX('①企画一覧・審査'!$R$6:$R$205,$L37))</f>
+        <f>IF($L37="","",INDEX('①企画一覧・審査'!$R$6:$R$105,$L37))</f>
         <v/>
       </c>
       <c r="G37" s="84">
-        <f>IF($L37="","",INDEX('①企画一覧・審査'!$S$6:$S$205,$L37))</f>
+        <f>IF($L37="","",INDEX('①企画一覧・審査'!$S$6:$S$105,$L37))</f>
         <v/>
       </c>
       <c r="H37" s="84">
-        <f>IF($L37="","",INDEX('①企画一覧・審査'!$T$6:$T$205,$L37))</f>
+        <f>IF($L37="","",INDEX('①企画一覧・審査'!$T$6:$T$105,$L37))</f>
         <v/>
       </c>
       <c r="I37" s="84">
-        <f>IF($L37="","",INDEX('①企画一覧・審査'!$U$6:$U$205,$L37)&amp;"")</f>
+        <f>IF($L37="","",INDEX('①企画一覧・審査'!$U$6:$U$105,$L37)&amp;"")</f>
         <v/>
       </c>
       <c r="J37" s="93">
-        <f>IF($L37="","",INDEX('①企画一覧・審査'!$F$6:$F$205,$L37)&amp;"")</f>
+        <f>IF($L37="","",INDEX('①企画一覧・審査'!$F$6:$F$105,$L37)&amp;"")</f>
         <v/>
       </c>
       <c r="L37">
-        <f>IF(A37="","",MATCH(LARGE('①企画一覧・審査'!$W$6:$W$205,20),'①企画一覧・審査'!$W$6:$W$205,0))</f>
+        <f>IF(A37="","",MATCH(LARGE('①企画一覧・審査'!$W$6:$W$105,20),'①企画一覧・審査'!$W$6:$W$105,0))</f>
         <v/>
       </c>
     </row>
     <row r="38" ht="30" customHeight="1" s="35">
       <c r="A38" s="84">
-        <f>IF(COUNT('①企画一覧・審査'!$W$6:$W$205)&lt;21,"",21)</f>
+        <f>IF(COUNT('①企画一覧・審査'!$W$6:$W$105)&lt;21,"",21)</f>
         <v/>
       </c>
       <c r="B38" s="84">
-        <f>IF($L38="","",INDEX('①企画一覧・審査'!$B$6:$B$205,$L38)&amp;"")</f>
+        <f>IF($L38="","",INDEX('①企画一覧・審査'!$B$6:$B$105,$L38)&amp;"")</f>
         <v/>
       </c>
       <c r="C38" s="93">
-        <f>IF($L38="","",INDEX('①企画一覧・審査'!$C$6:$C$205,$L38)&amp;"")</f>
+        <f>IF($L38="","",INDEX('①企画一覧・審査'!$C$6:$C$105,$L38)&amp;"")</f>
         <v/>
       </c>
       <c r="D38" s="93">
-        <f>IF($L38="","",INDEX('①企画一覧・審査'!$I$6:$I$205,$L38)&amp;"")</f>
+        <f>IF($L38="","",INDEX('①企画一覧・審査'!$I$6:$I$105,$L38)&amp;"")</f>
         <v/>
       </c>
       <c r="E38" s="84">
-        <f>IF($L38="","",INDEX('①企画一覧・審査'!$Q$6:$Q$205,$L38))</f>
+        <f>IF($L38="","",INDEX('①企画一覧・審査'!$Q$6:$Q$105,$L38))</f>
         <v/>
       </c>
       <c r="F38" s="84">
-        <f>IF($L38="","",INDEX('①企画一覧・審査'!$R$6:$R$205,$L38))</f>
+        <f>IF($L38="","",INDEX('①企画一覧・審査'!$R$6:$R$105,$L38))</f>
         <v/>
       </c>
       <c r="G38" s="84">
-        <f>IF($L38="","",INDEX('①企画一覧・審査'!$S$6:$S$205,$L38))</f>
+        <f>IF($L38="","",INDEX('①企画一覧・審査'!$S$6:$S$105,$L38))</f>
         <v/>
       </c>
       <c r="H38" s="84">
-        <f>IF($L38="","",INDEX('①企画一覧・審査'!$T$6:$T$205,$L38))</f>
+        <f>IF($L38="","",INDEX('①企画一覧・審査'!$T$6:$T$105,$L38))</f>
         <v/>
       </c>
       <c r="I38" s="84">
-        <f>IF($L38="","",INDEX('①企画一覧・審査'!$U$6:$U$205,$L38)&amp;"")</f>
+        <f>IF($L38="","",INDEX('①企画一覧・審査'!$U$6:$U$105,$L38)&amp;"")</f>
         <v/>
       </c>
       <c r="J38" s="93">
-        <f>IF($L38="","",INDEX('①企画一覧・審査'!$F$6:$F$205,$L38)&amp;"")</f>
+        <f>IF($L38="","",INDEX('①企画一覧・審査'!$F$6:$F$105,$L38)&amp;"")</f>
         <v/>
       </c>
       <c r="L38">
-        <f>IF(A38="","",MATCH(LARGE('①企画一覧・審査'!$W$6:$W$205,21),'①企画一覧・審査'!$W$6:$W$205,0))</f>
+        <f>IF(A38="","",MATCH(LARGE('①企画一覧・審査'!$W$6:$W$105,21),'①企画一覧・審査'!$W$6:$W$105,0))</f>
         <v/>
       </c>
     </row>
     <row r="39" ht="30" customHeight="1" s="35">
       <c r="A39" s="84">
-        <f>IF(COUNT('①企画一覧・審査'!$W$6:$W$205)&lt;22,"",22)</f>
+        <f>IF(COUNT('①企画一覧・審査'!$W$6:$W$105)&lt;22,"",22)</f>
         <v/>
       </c>
       <c r="B39" s="84">
-        <f>IF($L39="","",INDEX('①企画一覧・審査'!$B$6:$B$205,$L39)&amp;"")</f>
+        <f>IF($L39="","",INDEX('①企画一覧・審査'!$B$6:$B$105,$L39)&amp;"")</f>
         <v/>
       </c>
       <c r="C39" s="93">
-        <f>IF($L39="","",INDEX('①企画一覧・審査'!$C$6:$C$205,$L39)&amp;"")</f>
+        <f>IF($L39="","",INDEX('①企画一覧・審査'!$C$6:$C$105,$L39)&amp;"")</f>
         <v/>
       </c>
       <c r="D39" s="93">
-        <f>IF($L39="","",INDEX('①企画一覧・審査'!$I$6:$I$205,$L39)&amp;"")</f>
+        <f>IF($L39="","",INDEX('①企画一覧・審査'!$I$6:$I$105,$L39)&amp;"")</f>
         <v/>
       </c>
       <c r="E39" s="84">
-        <f>IF($L39="","",INDEX('①企画一覧・審査'!$Q$6:$Q$205,$L39))</f>
+        <f>IF($L39="","",INDEX('①企画一覧・審査'!$Q$6:$Q$105,$L39))</f>
         <v/>
       </c>
       <c r="F39" s="84">
-        <f>IF($L39="","",INDEX('①企画一覧・審査'!$R$6:$R$205,$L39))</f>
+        <f>IF($L39="","",INDEX('①企画一覧・審査'!$R$6:$R$105,$L39))</f>
         <v/>
       </c>
       <c r="G39" s="84">
-        <f>IF($L39="","",INDEX('①企画一覧・審査'!$S$6:$S$205,$L39))</f>
+        <f>IF($L39="","",INDEX('①企画一覧・審査'!$S$6:$S$105,$L39))</f>
         <v/>
       </c>
       <c r="H39" s="84">
-        <f>IF($L39="","",INDEX('①企画一覧・審査'!$T$6:$T$205,$L39))</f>
+        <f>IF($L39="","",INDEX('①企画一覧・審査'!$T$6:$T$105,$L39))</f>
         <v/>
       </c>
       <c r="I39" s="84">
-        <f>IF($L39="","",INDEX('①企画一覧・審査'!$U$6:$U$205,$L39)&amp;"")</f>
+        <f>IF($L39="","",INDEX('①企画一覧・審査'!$U$6:$U$105,$L39)&amp;"")</f>
         <v/>
       </c>
       <c r="J39" s="93">
-        <f>IF($L39="","",INDEX('①企画一覧・審査'!$F$6:$F$205,$L39)&amp;"")</f>
+        <f>IF($L39="","",INDEX('①企画一覧・審査'!$F$6:$F$105,$L39)&amp;"")</f>
         <v/>
       </c>
       <c r="L39">
-        <f>IF(A39="","",MATCH(LARGE('①企画一覧・審査'!$W$6:$W$205,22),'①企画一覧・審査'!$W$6:$W$205,0))</f>
+        <f>IF(A39="","",MATCH(LARGE('①企画一覧・審査'!$W$6:$W$105,22),'①企画一覧・審査'!$W$6:$W$105,0))</f>
         <v/>
       </c>
     </row>
     <row r="40" ht="30" customHeight="1" s="35">
       <c r="A40" s="84">
-        <f>IF(COUNT('①企画一覧・審査'!$W$6:$W$205)&lt;23,"",23)</f>
+        <f>IF(COUNT('①企画一覧・審査'!$W$6:$W$105)&lt;23,"",23)</f>
         <v/>
       </c>
       <c r="B40" s="84">
-        <f>IF($L40="","",INDEX('①企画一覧・審査'!$B$6:$B$205,$L40)&amp;"")</f>
+        <f>IF($L40="","",INDEX('①企画一覧・審査'!$B$6:$B$105,$L40)&amp;"")</f>
         <v/>
       </c>
       <c r="C40" s="93">
-        <f>IF($L40="","",INDEX('①企画一覧・審査'!$C$6:$C$205,$L40)&amp;"")</f>
+        <f>IF($L40="","",INDEX('①企画一覧・審査'!$C$6:$C$105,$L40)&amp;"")</f>
         <v/>
       </c>
       <c r="D40" s="93">
-        <f>IF($L40="","",INDEX('①企画一覧・審査'!$I$6:$I$205,$L40)&amp;"")</f>
+        <f>IF($L40="","",INDEX('①企画一覧・審査'!$I$6:$I$105,$L40)&amp;"")</f>
         <v/>
       </c>
       <c r="E40" s="84">
-        <f>IF($L40="","",INDEX('①企画一覧・審査'!$Q$6:$Q$205,$L40))</f>
+        <f>IF($L40="","",INDEX('①企画一覧・審査'!$Q$6:$Q$105,$L40))</f>
         <v/>
       </c>
       <c r="F40" s="84">
-        <f>IF($L40="","",INDEX('①企画一覧・審査'!$R$6:$R$205,$L40))</f>
+        <f>IF($L40="","",INDEX('①企画一覧・審査'!$R$6:$R$105,$L40))</f>
         <v/>
       </c>
       <c r="G40" s="84">
-        <f>IF($L40="","",INDEX('①企画一覧・審査'!$S$6:$S$205,$L40))</f>
+        <f>IF($L40="","",INDEX('①企画一覧・審査'!$S$6:$S$105,$L40))</f>
         <v/>
       </c>
       <c r="H40" s="84">
-        <f>IF($L40="","",INDEX('①企画一覧・審査'!$T$6:$T$205,$L40))</f>
+        <f>IF($L40="","",INDEX('①企画一覧・審査'!$T$6:$T$105,$L40))</f>
         <v/>
       </c>
       <c r="I40" s="84">
-        <f>IF($L40="","",INDEX('①企画一覧・審査'!$U$6:$U$205,$L40)&amp;"")</f>
+        <f>IF($L40="","",INDEX('①企画一覧・審査'!$U$6:$U$105,$L40)&amp;"")</f>
         <v/>
       </c>
       <c r="J40" s="93">
-        <f>IF($L40="","",INDEX('①企画一覧・審査'!$F$6:$F$205,$L40)&amp;"")</f>
+        <f>IF($L40="","",INDEX('①企画一覧・審査'!$F$6:$F$105,$L40)&amp;"")</f>
         <v/>
       </c>
       <c r="L40">
-        <f>IF(A40="","",MATCH(LARGE('①企画一覧・審査'!$W$6:$W$205,23),'①企画一覧・審査'!$W$6:$W$205,0))</f>
+        <f>IF(A40="","",MATCH(LARGE('①企画一覧・審査'!$W$6:$W$105,23),'①企画一覧・審査'!$W$6:$W$105,0))</f>
         <v/>
       </c>
     </row>
     <row r="41" ht="30" customHeight="1" s="35">
       <c r="A41" s="84">
-        <f>IF(COUNT('①企画一覧・審査'!$W$6:$W$205)&lt;24,"",24)</f>
+        <f>IF(COUNT('①企画一覧・審査'!$W$6:$W$105)&lt;24,"",24)</f>
         <v/>
       </c>
       <c r="B41" s="84">
-        <f>IF($L41="","",INDEX('①企画一覧・審査'!$B$6:$B$205,$L41)&amp;"")</f>
+        <f>IF($L41="","",INDEX('①企画一覧・審査'!$B$6:$B$105,$L41)&amp;"")</f>
         <v/>
       </c>
       <c r="C41" s="93">
-        <f>IF($L41="","",INDEX('①企画一覧・審査'!$C$6:$C$205,$L41)&amp;"")</f>
+        <f>IF($L41="","",INDEX('①企画一覧・審査'!$C$6:$C$105,$L41)&amp;"")</f>
         <v/>
       </c>
       <c r="D41" s="93">
-        <f>IF($L41="","",INDEX('①企画一覧・審査'!$I$6:$I$205,$L41)&amp;"")</f>
+        <f>IF($L41="","",INDEX('①企画一覧・審査'!$I$6:$I$105,$L41)&amp;"")</f>
         <v/>
       </c>
       <c r="E41" s="84">
-        <f>IF($L41="","",INDEX('①企画一覧・審査'!$Q$6:$Q$205,$L41))</f>
+        <f>IF($L41="","",INDEX('①企画一覧・審査'!$Q$6:$Q$105,$L41))</f>
         <v/>
       </c>
       <c r="F41" s="84">
-        <f>IF($L41="","",INDEX('①企画一覧・審査'!$R$6:$R$205,$L41))</f>
+        <f>IF($L41="","",INDEX('①企画一覧・審査'!$R$6:$R$105,$L41))</f>
         <v/>
       </c>
       <c r="G41" s="84">
-        <f>IF($L41="","",INDEX('①企画一覧・審査'!$S$6:$S$205,$L41))</f>
+        <f>IF($L41="","",INDEX('①企画一覧・審査'!$S$6:$S$105,$L41))</f>
         <v/>
       </c>
       <c r="H41" s="84">
-        <f>IF($L41="","",INDEX('①企画一覧・審査'!$T$6:$T$205,$L41))</f>
+        <f>IF($L41="","",INDEX('①企画一覧・審査'!$T$6:$T$105,$L41))</f>
         <v/>
       </c>
       <c r="I41" s="84">
-        <f>IF($L41="","",INDEX('①企画一覧・審査'!$U$6:$U$205,$L41)&amp;"")</f>
+        <f>IF($L41="","",INDEX('①企画一覧・審査'!$U$6:$U$105,$L41)&amp;"")</f>
         <v/>
       </c>
       <c r="J41" s="93">
-        <f>IF($L41="","",INDEX('①企画一覧・審査'!$F$6:$F$205,$L41)&amp;"")</f>
+        <f>IF($L41="","",INDEX('①企画一覧・審査'!$F$6:$F$105,$L41)&amp;"")</f>
         <v/>
       </c>
       <c r="L41">
-        <f>IF(A41="","",MATCH(LARGE('①企画一覧・審査'!$W$6:$W$205,24),'①企画一覧・審査'!$W$6:$W$205,0))</f>
+        <f>IF(A41="","",MATCH(LARGE('①企画一覧・審査'!$W$6:$W$105,24),'①企画一覧・審査'!$W$6:$W$105,0))</f>
         <v/>
       </c>
     </row>
     <row r="42" ht="30" customHeight="1" s="35">
       <c r="A42" s="84">
-        <f>IF(COUNT('①企画一覧・審査'!$W$6:$W$205)&lt;25,"",25)</f>
+        <f>IF(COUNT('①企画一覧・審査'!$W$6:$W$105)&lt;25,"",25)</f>
         <v/>
       </c>
       <c r="B42" s="84">
-        <f>IF($L42="","",INDEX('①企画一覧・審査'!$B$6:$B$205,$L42)&amp;"")</f>
+        <f>IF($L42="","",INDEX('①企画一覧・審査'!$B$6:$B$105,$L42)&amp;"")</f>
         <v/>
       </c>
       <c r="C42" s="93">
-        <f>IF($L42="","",INDEX('①企画一覧・審査'!$C$6:$C$205,$L42)&amp;"")</f>
+        <f>IF($L42="","",INDEX('①企画一覧・審査'!$C$6:$C$105,$L42)&amp;"")</f>
         <v/>
       </c>
       <c r="D42" s="93">
-        <f>IF($L42="","",INDEX('①企画一覧・審査'!$I$6:$I$205,$L42)&amp;"")</f>
+        <f>IF($L42="","",INDEX('①企画一覧・審査'!$I$6:$I$105,$L42)&amp;"")</f>
         <v/>
       </c>
       <c r="E42" s="84">
-        <f>IF($L42="","",INDEX('①企画一覧・審査'!$Q$6:$Q$205,$L42))</f>
+        <f>IF($L42="","",INDEX('①企画一覧・審査'!$Q$6:$Q$105,$L42))</f>
         <v/>
       </c>
       <c r="F42" s="84">
-        <f>IF($L42="","",INDEX('①企画一覧・審査'!$R$6:$R$205,$L42))</f>
+        <f>IF($L42="","",INDEX('①企画一覧・審査'!$R$6:$R$105,$L42))</f>
         <v/>
       </c>
       <c r="G42" s="84">
-        <f>IF($L42="","",INDEX('①企画一覧・審査'!$S$6:$S$205,$L42))</f>
+        <f>IF($L42="","",INDEX('①企画一覧・審査'!$S$6:$S$105,$L42))</f>
         <v/>
       </c>
       <c r="H42" s="84">
-        <f>IF($L42="","",INDEX('①企画一覧・審査'!$T$6:$T$205,$L42))</f>
+        <f>IF($L42="","",INDEX('①企画一覧・審査'!$T$6:$T$105,$L42))</f>
         <v/>
       </c>
       <c r="I42" s="84">
-        <f>IF($L42="","",INDEX('①企画一覧・審査'!$U$6:$U$205,$L42)&amp;"")</f>
+        <f>IF($L42="","",INDEX('①企画一覧・審査'!$U$6:$U$105,$L42)&amp;"")</f>
         <v/>
       </c>
       <c r="J42" s="93">
-        <f>IF($L42="","",INDEX('①企画一覧・審査'!$F$6:$F$205,$L42)&amp;"")</f>
+        <f>IF($L42="","",INDEX('①企画一覧・審査'!$F$6:$F$105,$L42)&amp;"")</f>
         <v/>
       </c>
       <c r="L42">
-        <f>IF(A42="","",MATCH(LARGE('①企画一覧・審査'!$W$6:$W$205,25),'①企画一覧・審査'!$W$6:$W$205,0))</f>
+        <f>IF(A42="","",MATCH(LARGE('①企画一覧・審査'!$W$6:$W$105,25),'①企画一覧・審査'!$W$6:$W$105,0))</f>
         <v/>
       </c>
     </row>
     <row r="43" ht="30" customHeight="1" s="35">
       <c r="A43" s="84">
-        <f>IF(COUNT('①企画一覧・審査'!$W$6:$W$205)&lt;26,"",26)</f>
+        <f>IF(COUNT('①企画一覧・審査'!$W$6:$W$105)&lt;26,"",26)</f>
         <v/>
       </c>
       <c r="B43" s="84">
-        <f>IF($L43="","",INDEX('①企画一覧・審査'!$B$6:$B$205,$L43)&amp;"")</f>
+        <f>IF($L43="","",INDEX('①企画一覧・審査'!$B$6:$B$105,$L43)&amp;"")</f>
         <v/>
       </c>
       <c r="C43" s="93">
-        <f>IF($L43="","",INDEX('①企画一覧・審査'!$C$6:$C$205,$L43)&amp;"")</f>
+        <f>IF($L43="","",INDEX('①企画一覧・審査'!$C$6:$C$105,$L43)&amp;"")</f>
         <v/>
       </c>
       <c r="D43" s="93">
-        <f>IF($L43="","",INDEX('①企画一覧・審査'!$I$6:$I$205,$L43)&amp;"")</f>
+        <f>IF($L43="","",INDEX('①企画一覧・審査'!$I$6:$I$105,$L43)&amp;"")</f>
         <v/>
       </c>
       <c r="E43" s="84">
-        <f>IF($L43="","",INDEX('①企画一覧・審査'!$Q$6:$Q$205,$L43))</f>
+        <f>IF($L43="","",INDEX('①企画一覧・審査'!$Q$6:$Q$105,$L43))</f>
         <v/>
       </c>
       <c r="F43" s="84">
-        <f>IF($L43="","",INDEX('①企画一覧・審査'!$R$6:$R$205,$L43))</f>
+        <f>IF($L43="","",INDEX('①企画一覧・審査'!$R$6:$R$105,$L43))</f>
         <v/>
       </c>
       <c r="G43" s="84">
-        <f>IF($L43="","",INDEX('①企画一覧・審査'!$S$6:$S$205,$L43))</f>
+        <f>IF($L43="","",INDEX('①企画一覧・審査'!$S$6:$S$105,$L43))</f>
         <v/>
       </c>
       <c r="H43" s="84">
-        <f>IF($L43="","",INDEX('①企画一覧・審査'!$T$6:$T$205,$L43))</f>
+        <f>IF($L43="","",INDEX('①企画一覧・審査'!$T$6:$T$105,$L43))</f>
         <v/>
       </c>
       <c r="I43" s="84">
-        <f>IF($L43="","",INDEX('①企画一覧・審査'!$U$6:$U$205,$L43)&amp;"")</f>
+        <f>IF($L43="","",INDEX('①企画一覧・審査'!$U$6:$U$105,$L43)&amp;"")</f>
         <v/>
       </c>
       <c r="J43" s="93">
-        <f>IF($L43="","",INDEX('①企画一覧・審査'!$F$6:$F$205,$L43)&amp;"")</f>
+        <f>IF($L43="","",INDEX('①企画一覧・審査'!$F$6:$F$105,$L43)&amp;"")</f>
         <v/>
       </c>
       <c r="L43">
-        <f>IF(A43="","",MATCH(LARGE('①企画一覧・審査'!$W$6:$W$205,26),'①企画一覧・審査'!$W$6:$W$205,0))</f>
+        <f>IF(A43="","",MATCH(LARGE('①企画一覧・審査'!$W$6:$W$105,26),'①企画一覧・審査'!$W$6:$W$105,0))</f>
         <v/>
       </c>
     </row>
     <row r="44" ht="30" customHeight="1" s="35">
       <c r="A44" s="84">
-        <f>IF(COUNT('①企画一覧・審査'!$W$6:$W$205)&lt;27,"",27)</f>
+        <f>IF(COUNT('①企画一覧・審査'!$W$6:$W$105)&lt;27,"",27)</f>
         <v/>
       </c>
       <c r="B44" s="84">
-        <f>IF($L44="","",INDEX('①企画一覧・審査'!$B$6:$B$205,$L44)&amp;"")</f>
+        <f>IF($L44="","",INDEX('①企画一覧・審査'!$B$6:$B$105,$L44)&amp;"")</f>
         <v/>
       </c>
       <c r="C44" s="93">
-        <f>IF($L44="","",INDEX('①企画一覧・審査'!$C$6:$C$205,$L44)&amp;"")</f>
+        <f>IF($L44="","",INDEX('①企画一覧・審査'!$C$6:$C$105,$L44)&amp;"")</f>
         <v/>
       </c>
       <c r="D44" s="93">
-        <f>IF($L44="","",INDEX('①企画一覧・審査'!$I$6:$I$205,$L44)&amp;"")</f>
+        <f>IF($L44="","",INDEX('①企画一覧・審査'!$I$6:$I$105,$L44)&amp;"")</f>
         <v/>
       </c>
       <c r="E44" s="84">
-        <f>IF($L44="","",INDEX('①企画一覧・審査'!$Q$6:$Q$205,$L44))</f>
+        <f>IF($L44="","",INDEX('①企画一覧・審査'!$Q$6:$Q$105,$L44))</f>
         <v/>
       </c>
       <c r="F44" s="84">
-        <f>IF($L44="","",INDEX('①企画一覧・審査'!$R$6:$R$205,$L44))</f>
+        <f>IF($L44="","",INDEX('①企画一覧・審査'!$R$6:$R$105,$L44))</f>
         <v/>
       </c>
       <c r="G44" s="84">
-        <f>IF($L44="","",INDEX('①企画一覧・審査'!$S$6:$S$205,$L44))</f>
+        <f>IF($L44="","",INDEX('①企画一覧・審査'!$S$6:$S$105,$L44))</f>
         <v/>
       </c>
       <c r="H44" s="84">
-        <f>IF($L44="","",INDEX('①企画一覧・審査'!$T$6:$T$205,$L44))</f>
+        <f>IF($L44="","",INDEX('①企画一覧・審査'!$T$6:$T$105,$L44))</f>
         <v/>
       </c>
       <c r="I44" s="84">
-        <f>IF($L44="","",INDEX('①企画一覧・審査'!$U$6:$U$205,$L44)&amp;"")</f>
+        <f>IF($L44="","",INDEX('①企画一覧・審査'!$U$6:$U$105,$L44)&amp;"")</f>
         <v/>
       </c>
       <c r="J44" s="93">
-        <f>IF($L44="","",INDEX('①企画一覧・審査'!$F$6:$F$205,$L44)&amp;"")</f>
+        <f>IF($L44="","",INDEX('①企画一覧・審査'!$F$6:$F$105,$L44)&amp;"")</f>
         <v/>
       </c>
       <c r="L44">
-        <f>IF(A44="","",MATCH(LARGE('①企画一覧・審査'!$W$6:$W$205,27),'①企画一覧・審査'!$W$6:$W$205,0))</f>
+        <f>IF(A44="","",MATCH(LARGE('①企画一覧・審査'!$W$6:$W$105,27),'①企画一覧・審査'!$W$6:$W$105,0))</f>
         <v/>
       </c>
     </row>
     <row r="45" ht="30" customHeight="1" s="35">
       <c r="A45" s="84">
-        <f>IF(COUNT('①企画一覧・審査'!$W$6:$W$205)&lt;28,"",28)</f>
+        <f>IF(COUNT('①企画一覧・審査'!$W$6:$W$105)&lt;28,"",28)</f>
         <v/>
       </c>
       <c r="B45" s="84">
-        <f>IF($L45="","",INDEX('①企画一覧・審査'!$B$6:$B$205,$L45)&amp;"")</f>
+        <f>IF($L45="","",INDEX('①企画一覧・審査'!$B$6:$B$105,$L45)&amp;"")</f>
         <v/>
       </c>
       <c r="C45" s="93">
-        <f>IF($L45="","",INDEX('①企画一覧・審査'!$C$6:$C$205,$L45)&amp;"")</f>
+        <f>IF($L45="","",INDEX('①企画一覧・審査'!$C$6:$C$105,$L45)&amp;"")</f>
         <v/>
       </c>
       <c r="D45" s="93">
-        <f>IF($L45="","",INDEX('①企画一覧・審査'!$I$6:$I$205,$L45)&amp;"")</f>
+        <f>IF($L45="","",INDEX('①企画一覧・審査'!$I$6:$I$105,$L45)&amp;"")</f>
         <v/>
       </c>
       <c r="E45" s="84">
-        <f>IF($L45="","",INDEX('①企画一覧・審査'!$Q$6:$Q$205,$L45))</f>
+        <f>IF($L45="","",INDEX('①企画一覧・審査'!$Q$6:$Q$105,$L45))</f>
         <v/>
       </c>
       <c r="F45" s="84">
-        <f>IF($L45="","",INDEX('①企画一覧・審査'!$R$6:$R$205,$L45))</f>
+        <f>IF($L45="","",INDEX('①企画一覧・審査'!$R$6:$R$105,$L45))</f>
         <v/>
       </c>
       <c r="G45" s="84">
-        <f>IF($L45="","",INDEX('①企画一覧・審査'!$S$6:$S$205,$L45))</f>
+        <f>IF($L45="","",INDEX('①企画一覧・審査'!$S$6:$S$105,$L45))</f>
         <v/>
       </c>
       <c r="H45" s="84">
-        <f>IF($L45="","",INDEX('①企画一覧・審査'!$T$6:$T$205,$L45))</f>
+        <f>IF($L45="","",INDEX('①企画一覧・審査'!$T$6:$T$105,$L45))</f>
         <v/>
       </c>
       <c r="I45" s="84">
-        <f>IF($L45="","",INDEX('①企画一覧・審査'!$U$6:$U$205,$L45)&amp;"")</f>
+        <f>IF($L45="","",INDEX('①企画一覧・審査'!$U$6:$U$105,$L45)&amp;"")</f>
         <v/>
       </c>
       <c r="J45" s="93">
-        <f>IF($L45="","",INDEX('①企画一覧・審査'!$F$6:$F$205,$L45)&amp;"")</f>
+        <f>IF($L45="","",INDEX('①企画一覧・審査'!$F$6:$F$105,$L45)&amp;"")</f>
         <v/>
       </c>
       <c r="L45">
-        <f>IF(A45="","",MATCH(LARGE('①企画一覧・審査'!$W$6:$W$205,28),'①企画一覧・審査'!$W$6:$W$205,0))</f>
+        <f>IF(A45="","",MATCH(LARGE('①企画一覧・審査'!$W$6:$W$105,28),'①企画一覧・審査'!$W$6:$W$105,0))</f>
         <v/>
       </c>
     </row>
     <row r="46" ht="30" customHeight="1" s="35">
       <c r="A46" s="84">
-        <f>IF(COUNT('①企画一覧・審査'!$W$6:$W$205)&lt;29,"",29)</f>
+        <f>IF(COUNT('①企画一覧・審査'!$W$6:$W$105)&lt;29,"",29)</f>
         <v/>
       </c>
       <c r="B46" s="84">
-        <f>IF($L46="","",INDEX('①企画一覧・審査'!$B$6:$B$205,$L46)&amp;"")</f>
+        <f>IF($L46="","",INDEX('①企画一覧・審査'!$B$6:$B$105,$L46)&amp;"")</f>
         <v/>
       </c>
       <c r="C46" s="93">
-        <f>IF($L46="","",INDEX('①企画一覧・審査'!$C$6:$C$205,$L46)&amp;"")</f>
+        <f>IF($L46="","",INDEX('①企画一覧・審査'!$C$6:$C$105,$L46)&amp;"")</f>
         <v/>
       </c>
       <c r="D46" s="93">
-        <f>IF($L46="","",INDEX('①企画一覧・審査'!$I$6:$I$205,$L46)&amp;"")</f>
+        <f>IF($L46="","",INDEX('①企画一覧・審査'!$I$6:$I$105,$L46)&amp;"")</f>
         <v/>
       </c>
       <c r="E46" s="84">
-        <f>IF($L46="","",INDEX('①企画一覧・審査'!$Q$6:$Q$205,$L46))</f>
+        <f>IF($L46="","",INDEX('①企画一覧・審査'!$Q$6:$Q$105,$L46))</f>
         <v/>
       </c>
       <c r="F46" s="84">
-        <f>IF($L46="","",INDEX('①企画一覧・審査'!$R$6:$R$205,$L46))</f>
+        <f>IF($L46="","",INDEX('①企画一覧・審査'!$R$6:$R$105,$L46))</f>
         <v/>
       </c>
       <c r="G46" s="84">
-        <f>IF($L46="","",INDEX('①企画一覧・審査'!$S$6:$S$205,$L46))</f>
+        <f>IF($L46="","",INDEX('①企画一覧・審査'!$S$6:$S$105,$L46))</f>
         <v/>
       </c>
       <c r="H46" s="84">
-        <f>IF($L46="","",INDEX('①企画一覧・審査'!$T$6:$T$205,$L46))</f>
+        <f>IF($L46="","",INDEX('①企画一覧・審査'!$T$6:$T$105,$L46))</f>
         <v/>
       </c>
       <c r="I46" s="84">
-        <f>IF($L46="","",INDEX('①企画一覧・審査'!$U$6:$U$205,$L46)&amp;"")</f>
+        <f>IF($L46="","",INDEX('①企画一覧・審査'!$U$6:$U$105,$L46)&amp;"")</f>
         <v/>
       </c>
       <c r="J46" s="93">
-        <f>IF($L46="","",INDEX('①企画一覧・審査'!$F$6:$F$205,$L46)&amp;"")</f>
+        <f>IF($L46="","",INDEX('①企画一覧・審査'!$F$6:$F$105,$L46)&amp;"")</f>
         <v/>
       </c>
       <c r="L46">
-        <f>IF(A46="","",MATCH(LARGE('①企画一覧・審査'!$W$6:$W$205,29),'①企画一覧・審査'!$W$6:$W$205,0))</f>
+        <f>IF(A46="","",MATCH(LARGE('①企画一覧・審査'!$W$6:$W$105,29),'①企画一覧・審査'!$W$6:$W$105,0))</f>
         <v/>
       </c>
     </row>
     <row r="47" ht="30" customHeight="1" s="35">
       <c r="A47" s="84">
-        <f>IF(COUNT('①企画一覧・審査'!$W$6:$W$205)&lt;30,"",30)</f>
+        <f>IF(COUNT('①企画一覧・審査'!$W$6:$W$105)&lt;30,"",30)</f>
         <v/>
       </c>
       <c r="B47" s="84">
-        <f>IF($L47="","",INDEX('①企画一覧・審査'!$B$6:$B$205,$L47)&amp;"")</f>
+        <f>IF($L47="","",INDEX('①企画一覧・審査'!$B$6:$B$105,$L47)&amp;"")</f>
         <v/>
       </c>
       <c r="C47" s="93">
-        <f>IF($L47="","",INDEX('①企画一覧・審査'!$C$6:$C$205,$L47)&amp;"")</f>
+        <f>IF($L47="","",INDEX('①企画一覧・審査'!$C$6:$C$105,$L47)&amp;"")</f>
         <v/>
       </c>
       <c r="D47" s="93">
-        <f>IF($L47="","",INDEX('①企画一覧・審査'!$I$6:$I$205,$L47)&amp;"")</f>
+        <f>IF($L47="","",INDEX('①企画一覧・審査'!$I$6:$I$105,$L47)&amp;"")</f>
         <v/>
       </c>
       <c r="E47" s="84">
-        <f>IF($L47="","",INDEX('①企画一覧・審査'!$Q$6:$Q$205,$L47))</f>
+        <f>IF($L47="","",INDEX('①企画一覧・審査'!$Q$6:$Q$105,$L47))</f>
         <v/>
       </c>
       <c r="F47" s="84">
-        <f>IF($L47="","",INDEX('①企画一覧・審査'!$R$6:$R$205,$L47))</f>
+        <f>IF($L47="","",INDEX('①企画一覧・審査'!$R$6:$R$105,$L47))</f>
         <v/>
       </c>
       <c r="G47" s="84">
-        <f>IF($L47="","",INDEX('①企画一覧・審査'!$S$6:$S$205,$L47))</f>
+        <f>IF($L47="","",INDEX('①企画一覧・審査'!$S$6:$S$105,$L47))</f>
         <v/>
       </c>
       <c r="H47" s="84">
-        <f>IF($L47="","",INDEX('①企画一覧・審査'!$T$6:$T$205,$L47))</f>
+        <f>IF($L47="","",INDEX('①企画一覧・審査'!$T$6:$T$105,$L47))</f>
         <v/>
       </c>
       <c r="I47" s="84">
-        <f>IF($L47="","",INDEX('①企画一覧・審査'!$U$6:$U$205,$L47)&amp;"")</f>
+        <f>IF($L47="","",INDEX('①企画一覧・審査'!$U$6:$U$105,$L47)&amp;"")</f>
         <v/>
       </c>
       <c r="J47" s="93">
-        <f>IF($L47="","",INDEX('①企画一覧・審査'!$F$6:$F$205,$L47)&amp;"")</f>
+        <f>IF($L47="","",INDEX('①企画一覧・審査'!$F$6:$F$105,$L47)&amp;"")</f>
         <v/>
       </c>
       <c r="L47">
-        <f>IF(A47="","",MATCH(LARGE('①企画一覧・審査'!$W$6:$W$205,30),'①企画一覧・審査'!$W$6:$W$205,0))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="48" ht="30" customHeight="1" s="35">
-      <c r="A48" s="84">
-        <f>IF(COUNT('①企画一覧・審査'!$W$6:$W$205)&lt;31,"",31)</f>
-        <v/>
-      </c>
-      <c r="B48" s="84">
-        <f>IF($L48="","",INDEX('①企画一覧・審査'!$B$6:$B$205,$L48)&amp;"")</f>
-        <v/>
-      </c>
-      <c r="C48" s="93">
-        <f>IF($L48="","",INDEX('①企画一覧・審査'!$C$6:$C$205,$L48)&amp;"")</f>
-        <v/>
-      </c>
-      <c r="D48" s="93">
-        <f>IF($L48="","",INDEX('①企画一覧・審査'!$I$6:$I$205,$L48)&amp;"")</f>
-        <v/>
-      </c>
-      <c r="E48" s="84">
-        <f>IF($L48="","",INDEX('①企画一覧・審査'!$Q$6:$Q$205,$L48))</f>
-        <v/>
-      </c>
-      <c r="F48" s="84">
-        <f>IF($L48="","",INDEX('①企画一覧・審査'!$R$6:$R$205,$L48))</f>
-        <v/>
-      </c>
-      <c r="G48" s="84">
-        <f>IF($L48="","",INDEX('①企画一覧・審査'!$S$6:$S$205,$L48))</f>
-        <v/>
-      </c>
-      <c r="H48" s="84">
-        <f>IF($L48="","",INDEX('①企画一覧・審査'!$T$6:$T$205,$L48))</f>
-        <v/>
-      </c>
-      <c r="I48" s="84">
-        <f>IF($L48="","",INDEX('①企画一覧・審査'!$U$6:$U$205,$L48)&amp;"")</f>
-        <v/>
-      </c>
-      <c r="J48" s="93">
-        <f>IF($L48="","",INDEX('①企画一覧・審査'!$F$6:$F$205,$L48)&amp;"")</f>
-        <v/>
-      </c>
-      <c r="L48">
-        <f>IF(A48="","",MATCH(LARGE('①企画一覧・審査'!$W$6:$W$205,31),'①企画一覧・審査'!$W$6:$W$205,0))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="49" ht="30" customHeight="1" s="35">
-      <c r="A49" s="84">
-        <f>IF(COUNT('①企画一覧・審査'!$W$6:$W$205)&lt;32,"",32)</f>
-        <v/>
-      </c>
-      <c r="B49" s="84">
-        <f>IF($L49="","",INDEX('①企画一覧・審査'!$B$6:$B$205,$L49)&amp;"")</f>
-        <v/>
-      </c>
-      <c r="C49" s="93">
-        <f>IF($L49="","",INDEX('①企画一覧・審査'!$C$6:$C$205,$L49)&amp;"")</f>
-        <v/>
-      </c>
-      <c r="D49" s="93">
-        <f>IF($L49="","",INDEX('①企画一覧・審査'!$I$6:$I$205,$L49)&amp;"")</f>
-        <v/>
-      </c>
-      <c r="E49" s="84">
-        <f>IF($L49="","",INDEX('①企画一覧・審査'!$Q$6:$Q$205,$L49))</f>
-        <v/>
-      </c>
-      <c r="F49" s="84">
-        <f>IF($L49="","",INDEX('①企画一覧・審査'!$R$6:$R$205,$L49))</f>
-        <v/>
-      </c>
-      <c r="G49" s="84">
-        <f>IF($L49="","",INDEX('①企画一覧・審査'!$S$6:$S$205,$L49))</f>
-        <v/>
-      </c>
-      <c r="H49" s="84">
-        <f>IF($L49="","",INDEX('①企画一覧・審査'!$T$6:$T$205,$L49))</f>
-        <v/>
-      </c>
-      <c r="I49" s="84">
-        <f>IF($L49="","",INDEX('①企画一覧・審査'!$U$6:$U$205,$L49)&amp;"")</f>
-        <v/>
-      </c>
-      <c r="J49" s="93">
-        <f>IF($L49="","",INDEX('①企画一覧・審査'!$F$6:$F$205,$L49)&amp;"")</f>
-        <v/>
-      </c>
-      <c r="L49">
-        <f>IF(A49="","",MATCH(LARGE('①企画一覧・審査'!$W$6:$W$205,32),'①企画一覧・審査'!$W$6:$W$205,0))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="50" ht="30" customHeight="1" s="35">
-      <c r="A50" s="84">
-        <f>IF(COUNT('①企画一覧・審査'!$W$6:$W$205)&lt;33,"",33)</f>
-        <v/>
-      </c>
-      <c r="B50" s="84">
-        <f>IF($L50="","",INDEX('①企画一覧・審査'!$B$6:$B$205,$L50)&amp;"")</f>
-        <v/>
-      </c>
-      <c r="C50" s="93">
-        <f>IF($L50="","",INDEX('①企画一覧・審査'!$C$6:$C$205,$L50)&amp;"")</f>
-        <v/>
-      </c>
-      <c r="D50" s="93">
-        <f>IF($L50="","",INDEX('①企画一覧・審査'!$I$6:$I$205,$L50)&amp;"")</f>
-        <v/>
-      </c>
-      <c r="E50" s="84">
-        <f>IF($L50="","",INDEX('①企画一覧・審査'!$Q$6:$Q$205,$L50))</f>
-        <v/>
-      </c>
-      <c r="F50" s="84">
-        <f>IF($L50="","",INDEX('①企画一覧・審査'!$R$6:$R$205,$L50))</f>
-        <v/>
-      </c>
-      <c r="G50" s="84">
-        <f>IF($L50="","",INDEX('①企画一覧・審査'!$S$6:$S$205,$L50))</f>
-        <v/>
-      </c>
-      <c r="H50" s="84">
-        <f>IF($L50="","",INDEX('①企画一覧・審査'!$T$6:$T$205,$L50))</f>
-        <v/>
-      </c>
-      <c r="I50" s="84">
-        <f>IF($L50="","",INDEX('①企画一覧・審査'!$U$6:$U$205,$L50)&amp;"")</f>
-        <v/>
-      </c>
-      <c r="J50" s="93">
-        <f>IF($L50="","",INDEX('①企画一覧・審査'!$F$6:$F$205,$L50)&amp;"")</f>
-        <v/>
-      </c>
-      <c r="L50">
-        <f>IF(A50="","",MATCH(LARGE('①企画一覧・審査'!$W$6:$W$205,33),'①企画一覧・審査'!$W$6:$W$205,0))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="51" ht="30" customHeight="1" s="35">
-      <c r="A51" s="84">
-        <f>IF(COUNT('①企画一覧・審査'!$W$6:$W$205)&lt;34,"",34)</f>
-        <v/>
-      </c>
-      <c r="B51" s="84">
-        <f>IF($L51="","",INDEX('①企画一覧・審査'!$B$6:$B$205,$L51)&amp;"")</f>
-        <v/>
-      </c>
-      <c r="C51" s="93">
-        <f>IF($L51="","",INDEX('①企画一覧・審査'!$C$6:$C$205,$L51)&amp;"")</f>
-        <v/>
-      </c>
-      <c r="D51" s="93">
-        <f>IF($L51="","",INDEX('①企画一覧・審査'!$I$6:$I$205,$L51)&amp;"")</f>
-        <v/>
-      </c>
-      <c r="E51" s="84">
-        <f>IF($L51="","",INDEX('①企画一覧・審査'!$Q$6:$Q$205,$L51))</f>
-        <v/>
-      </c>
-      <c r="F51" s="84">
-        <f>IF($L51="","",INDEX('①企画一覧・審査'!$R$6:$R$205,$L51))</f>
-        <v/>
-      </c>
-      <c r="G51" s="84">
-        <f>IF($L51="","",INDEX('①企画一覧・審査'!$S$6:$S$205,$L51))</f>
-        <v/>
-      </c>
-      <c r="H51" s="84">
-        <f>IF($L51="","",INDEX('①企画一覧・審査'!$T$6:$T$205,$L51))</f>
-        <v/>
-      </c>
-      <c r="I51" s="84">
-        <f>IF($L51="","",INDEX('①企画一覧・審査'!$U$6:$U$205,$L51)&amp;"")</f>
-        <v/>
-      </c>
-      <c r="J51" s="93">
-        <f>IF($L51="","",INDEX('①企画一覧・審査'!$F$6:$F$205,$L51)&amp;"")</f>
-        <v/>
-      </c>
-      <c r="L51">
-        <f>IF(A51="","",MATCH(LARGE('①企画一覧・審査'!$W$6:$W$205,34),'①企画一覧・審査'!$W$6:$W$205,0))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="52" ht="30" customHeight="1" s="35">
-      <c r="A52" s="84">
-        <f>IF(COUNT('①企画一覧・審査'!$W$6:$W$205)&lt;35,"",35)</f>
-        <v/>
-      </c>
-      <c r="B52" s="84">
-        <f>IF($L52="","",INDEX('①企画一覧・審査'!$B$6:$B$205,$L52)&amp;"")</f>
-        <v/>
-      </c>
-      <c r="C52" s="93">
-        <f>IF($L52="","",INDEX('①企画一覧・審査'!$C$6:$C$205,$L52)&amp;"")</f>
-        <v/>
-      </c>
-      <c r="D52" s="93">
-        <f>IF($L52="","",INDEX('①企画一覧・審査'!$I$6:$I$205,$L52)&amp;"")</f>
-        <v/>
-      </c>
-      <c r="E52" s="84">
-        <f>IF($L52="","",INDEX('①企画一覧・審査'!$Q$6:$Q$205,$L52))</f>
-        <v/>
-      </c>
-      <c r="F52" s="84">
-        <f>IF($L52="","",INDEX('①企画一覧・審査'!$R$6:$R$205,$L52))</f>
-        <v/>
-      </c>
-      <c r="G52" s="84">
-        <f>IF($L52="","",INDEX('①企画一覧・審査'!$S$6:$S$205,$L52))</f>
-        <v/>
-      </c>
-      <c r="H52" s="84">
-        <f>IF($L52="","",INDEX('①企画一覧・審査'!$T$6:$T$205,$L52))</f>
-        <v/>
-      </c>
-      <c r="I52" s="84">
-        <f>IF($L52="","",INDEX('①企画一覧・審査'!$U$6:$U$205,$L52)&amp;"")</f>
-        <v/>
-      </c>
-      <c r="J52" s="93">
-        <f>IF($L52="","",INDEX('①企画一覧・審査'!$F$6:$F$205,$L52)&amp;"")</f>
-        <v/>
-      </c>
-      <c r="L52">
-        <f>IF(A52="","",MATCH(LARGE('①企画一覧・審査'!$W$6:$W$205,35),'①企画一覧・審査'!$W$6:$W$205,0))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="53" ht="30" customHeight="1" s="35">
-      <c r="A53" s="84">
-        <f>IF(COUNT('①企画一覧・審査'!$W$6:$W$205)&lt;36,"",36)</f>
-        <v/>
-      </c>
-      <c r="B53" s="84">
-        <f>IF($L53="","",INDEX('①企画一覧・審査'!$B$6:$B$205,$L53)&amp;"")</f>
-        <v/>
-      </c>
-      <c r="C53" s="93">
-        <f>IF($L53="","",INDEX('①企画一覧・審査'!$C$6:$C$205,$L53)&amp;"")</f>
-        <v/>
-      </c>
-      <c r="D53" s="93">
-        <f>IF($L53="","",INDEX('①企画一覧・審査'!$I$6:$I$205,$L53)&amp;"")</f>
-        <v/>
-      </c>
-      <c r="E53" s="84">
-        <f>IF($L53="","",INDEX('①企画一覧・審査'!$Q$6:$Q$205,$L53))</f>
-        <v/>
-      </c>
-      <c r="F53" s="84">
-        <f>IF($L53="","",INDEX('①企画一覧・審査'!$R$6:$R$205,$L53))</f>
-        <v/>
-      </c>
-      <c r="G53" s="84">
-        <f>IF($L53="","",INDEX('①企画一覧・審査'!$S$6:$S$205,$L53))</f>
-        <v/>
-      </c>
-      <c r="H53" s="84">
-        <f>IF($L53="","",INDEX('①企画一覧・審査'!$T$6:$T$205,$L53))</f>
-        <v/>
-      </c>
-      <c r="I53" s="84">
-        <f>IF($L53="","",INDEX('①企画一覧・審査'!$U$6:$U$205,$L53)&amp;"")</f>
-        <v/>
-      </c>
-      <c r="J53" s="93">
-        <f>IF($L53="","",INDEX('①企画一覧・審査'!$F$6:$F$205,$L53)&amp;"")</f>
-        <v/>
-      </c>
-      <c r="L53">
-        <f>IF(A53="","",MATCH(LARGE('①企画一覧・審査'!$W$6:$W$205,36),'①企画一覧・審査'!$W$6:$W$205,0))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="54" ht="30" customHeight="1" s="35">
-      <c r="A54" s="84">
-        <f>IF(COUNT('①企画一覧・審査'!$W$6:$W$205)&lt;37,"",37)</f>
-        <v/>
-      </c>
-      <c r="B54" s="84">
-        <f>IF($L54="","",INDEX('①企画一覧・審査'!$B$6:$B$205,$L54)&amp;"")</f>
-        <v/>
-      </c>
-      <c r="C54" s="93">
-        <f>IF($L54="","",INDEX('①企画一覧・審査'!$C$6:$C$205,$L54)&amp;"")</f>
-        <v/>
-      </c>
-      <c r="D54" s="93">
-        <f>IF($L54="","",INDEX('①企画一覧・審査'!$I$6:$I$205,$L54)&amp;"")</f>
-        <v/>
-      </c>
-      <c r="E54" s="84">
-        <f>IF($L54="","",INDEX('①企画一覧・審査'!$Q$6:$Q$205,$L54))</f>
-        <v/>
-      </c>
-      <c r="F54" s="84">
-        <f>IF($L54="","",INDEX('①企画一覧・審査'!$R$6:$R$205,$L54))</f>
-        <v/>
-      </c>
-      <c r="G54" s="84">
-        <f>IF($L54="","",INDEX('①企画一覧・審査'!$S$6:$S$205,$L54))</f>
-        <v/>
-      </c>
-      <c r="H54" s="84">
-        <f>IF($L54="","",INDEX('①企画一覧・審査'!$T$6:$T$205,$L54))</f>
-        <v/>
-      </c>
-      <c r="I54" s="84">
-        <f>IF($L54="","",INDEX('①企画一覧・審査'!$U$6:$U$205,$L54)&amp;"")</f>
-        <v/>
-      </c>
-      <c r="J54" s="93">
-        <f>IF($L54="","",INDEX('①企画一覧・審査'!$F$6:$F$205,$L54)&amp;"")</f>
-        <v/>
-      </c>
-      <c r="L54">
-        <f>IF(A54="","",MATCH(LARGE('①企画一覧・審査'!$W$6:$W$205,37),'①企画一覧・審査'!$W$6:$W$205,0))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="55" ht="30" customHeight="1" s="35">
-      <c r="A55" s="84">
-        <f>IF(COUNT('①企画一覧・審査'!$W$6:$W$205)&lt;38,"",38)</f>
-        <v/>
-      </c>
-      <c r="B55" s="84">
-        <f>IF($L55="","",INDEX('①企画一覧・審査'!$B$6:$B$205,$L55)&amp;"")</f>
-        <v/>
-      </c>
-      <c r="C55" s="93">
-        <f>IF($L55="","",INDEX('①企画一覧・審査'!$C$6:$C$205,$L55)&amp;"")</f>
-        <v/>
-      </c>
-      <c r="D55" s="93">
-        <f>IF($L55="","",INDEX('①企画一覧・審査'!$I$6:$I$205,$L55)&amp;"")</f>
-        <v/>
-      </c>
-      <c r="E55" s="84">
-        <f>IF($L55="","",INDEX('①企画一覧・審査'!$Q$6:$Q$205,$L55))</f>
-        <v/>
-      </c>
-      <c r="F55" s="84">
-        <f>IF($L55="","",INDEX('①企画一覧・審査'!$R$6:$R$205,$L55))</f>
-        <v/>
-      </c>
-      <c r="G55" s="84">
-        <f>IF($L55="","",INDEX('①企画一覧・審査'!$S$6:$S$205,$L55))</f>
-        <v/>
-      </c>
-      <c r="H55" s="84">
-        <f>IF($L55="","",INDEX('①企画一覧・審査'!$T$6:$T$205,$L55))</f>
-        <v/>
-      </c>
-      <c r="I55" s="84">
-        <f>IF($L55="","",INDEX('①企画一覧・審査'!$U$6:$U$205,$L55)&amp;"")</f>
-        <v/>
-      </c>
-      <c r="J55" s="93">
-        <f>IF($L55="","",INDEX('①企画一覧・審査'!$F$6:$F$205,$L55)&amp;"")</f>
-        <v/>
-      </c>
-      <c r="L55">
-        <f>IF(A55="","",MATCH(LARGE('①企画一覧・審査'!$W$6:$W$205,38),'①企画一覧・審査'!$W$6:$W$205,0))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="56" ht="30" customHeight="1" s="35">
-      <c r="A56" s="84">
-        <f>IF(COUNT('①企画一覧・審査'!$W$6:$W$205)&lt;39,"",39)</f>
-        <v/>
-      </c>
-      <c r="B56" s="84">
-        <f>IF($L56="","",INDEX('①企画一覧・審査'!$B$6:$B$205,$L56)&amp;"")</f>
-        <v/>
-      </c>
-      <c r="C56" s="93">
-        <f>IF($L56="","",INDEX('①企画一覧・審査'!$C$6:$C$205,$L56)&amp;"")</f>
-        <v/>
-      </c>
-      <c r="D56" s="93">
-        <f>IF($L56="","",INDEX('①企画一覧・審査'!$I$6:$I$205,$L56)&amp;"")</f>
-        <v/>
-      </c>
-      <c r="E56" s="84">
-        <f>IF($L56="","",INDEX('①企画一覧・審査'!$Q$6:$Q$205,$L56))</f>
-        <v/>
-      </c>
-      <c r="F56" s="84">
-        <f>IF($L56="","",INDEX('①企画一覧・審査'!$R$6:$R$205,$L56))</f>
-        <v/>
-      </c>
-      <c r="G56" s="84">
-        <f>IF($L56="","",INDEX('①企画一覧・審査'!$S$6:$S$205,$L56))</f>
-        <v/>
-      </c>
-      <c r="H56" s="84">
-        <f>IF($L56="","",INDEX('①企画一覧・審査'!$T$6:$T$205,$L56))</f>
-        <v/>
-      </c>
-      <c r="I56" s="84">
-        <f>IF($L56="","",INDEX('①企画一覧・審査'!$U$6:$U$205,$L56)&amp;"")</f>
-        <v/>
-      </c>
-      <c r="J56" s="93">
-        <f>IF($L56="","",INDEX('①企画一覧・審査'!$F$6:$F$205,$L56)&amp;"")</f>
-        <v/>
-      </c>
-      <c r="L56">
-        <f>IF(A56="","",MATCH(LARGE('①企画一覧・審査'!$W$6:$W$205,39),'①企画一覧・審査'!$W$6:$W$205,0))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="57" ht="30" customHeight="1" s="35">
-      <c r="A57" s="84">
-        <f>IF(COUNT('①企画一覧・審査'!$W$6:$W$205)&lt;40,"",40)</f>
-        <v/>
-      </c>
-      <c r="B57" s="84">
-        <f>IF($L57="","",INDEX('①企画一覧・審査'!$B$6:$B$205,$L57)&amp;"")</f>
-        <v/>
-      </c>
-      <c r="C57" s="93">
-        <f>IF($L57="","",INDEX('①企画一覧・審査'!$C$6:$C$205,$L57)&amp;"")</f>
-        <v/>
-      </c>
-      <c r="D57" s="93">
-        <f>IF($L57="","",INDEX('①企画一覧・審査'!$I$6:$I$205,$L57)&amp;"")</f>
-        <v/>
-      </c>
-      <c r="E57" s="84">
-        <f>IF($L57="","",INDEX('①企画一覧・審査'!$Q$6:$Q$205,$L57))</f>
-        <v/>
-      </c>
-      <c r="F57" s="84">
-        <f>IF($L57="","",INDEX('①企画一覧・審査'!$R$6:$R$205,$L57))</f>
-        <v/>
-      </c>
-      <c r="G57" s="84">
-        <f>IF($L57="","",INDEX('①企画一覧・審査'!$S$6:$S$205,$L57))</f>
-        <v/>
-      </c>
-      <c r="H57" s="84">
-        <f>IF($L57="","",INDEX('①企画一覧・審査'!$T$6:$T$205,$L57))</f>
-        <v/>
-      </c>
-      <c r="I57" s="84">
-        <f>IF($L57="","",INDEX('①企画一覧・審査'!$U$6:$U$205,$L57)&amp;"")</f>
-        <v/>
-      </c>
-      <c r="J57" s="93">
-        <f>IF($L57="","",INDEX('①企画一覧・審査'!$F$6:$F$205,$L57)&amp;"")</f>
-        <v/>
-      </c>
-      <c r="L57">
-        <f>IF(A57="","",MATCH(LARGE('①企画一覧・審査'!$W$6:$W$205,40),'①企画一覧・審査'!$W$6:$W$205,0))</f>
+        <f>IF(A47="","",MATCH(LARGE('①企画一覧・審査'!$W$6:$W$105,30),'①企画一覧・審査'!$W$6:$W$105,0))</f>
         <v/>
       </c>
     </row>
@@ -12183,7 +8023,7 @@
     <mergeCell ref="F12:H12"/>
     <mergeCell ref="A2:J2"/>
   </mergeCells>
-  <conditionalFormatting sqref="A18:J57">
+  <conditionalFormatting sqref="A18:J47">
     <cfRule type="expression" priority="1" dxfId="8">
       <formula>AND($A18&lt;&gt;"",$A18&lt;=$C$6)</formula>
     </cfRule>
